--- a/data/trending_integrated_20261030_11.xlsx
+++ b/data/trending_integrated_20261030_11.xlsx
@@ -567,24 +567,24 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>18100</v>
+        <v>19520</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>'+101.11%</t>
+          <t>'+116.89%</t>
         </is>
       </c>
       <c r="D2" t="n">
         <v>0</v>
       </c>
       <c r="E2" t="n">
-        <v>249</v>
+        <v>275</v>
       </c>
       <c r="F2" t="n">
-        <v>160</v>
+        <v>165</v>
       </c>
       <c r="G2" t="n">
-        <v>357</v>
+        <v>370</v>
       </c>
       <c r="H2" t="n">
         <v>1.98</v>
@@ -610,7 +610,7 @@
         <v>0</v>
       </c>
       <c r="O2" t="n">
-        <v>265329619145</v>
+        <v>297773348260</v>
       </c>
       <c r="P2" t="n">
         <v>21700</v>
@@ -626,16 +626,16 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>신규 상장주에 대한 부정적인 전망과 함께, 반복적인 하락 패턴에 대한 실망감을 표현. 일부 긍정적 뉴스가 있으나 전반적인 분위기는 하락세.</t>
+          <t>신규 상장주 특유의 급등락 패턴 반복. 매수세 부재 및 투자 주의 당부.</t>
         </is>
       </c>
       <c r="U2" t="inlineStr"/>
       <c r="V2" t="n">
-        <v>0.2</v>
+        <v>0</v>
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>['신규 상장주', '하락 패턴', '흑자']</t>
+          <t>['신규상장주', '급등락', '패턴']</t>
         </is>
       </c>
       <c r="X2" t="n">
@@ -659,24 +659,24 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>3020</v>
+        <v>2970</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>'+23.27%</t>
+          <t>'+21.22%</t>
         </is>
       </c>
       <c r="D3" t="n">
         <v>0.16</v>
       </c>
       <c r="E3" t="n">
-        <v>47</v>
+        <v>51</v>
       </c>
       <c r="F3" t="n">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="G3" t="n">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="H3" t="n">
         <v>0.79</v>
@@ -702,7 +702,7 @@
         <v>0.63</v>
       </c>
       <c r="O3" t="n">
-        <v>10007666598</v>
+        <v>10415377274</v>
       </c>
       <c r="P3" t="n">
         <v>3170</v>
@@ -751,24 +751,24 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>19030</v>
+        <v>19010</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>'+14.29%</t>
+          <t>'+14.17%</t>
         </is>
       </c>
       <c r="D4" t="n">
         <v>-0.75</v>
       </c>
       <c r="E4" t="n">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="F4" t="n">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="G4" t="n">
-        <v>100</v>
+        <v>103</v>
       </c>
       <c r="H4" t="n">
         <v>3.6</v>
@@ -794,7 +794,7 @@
         <v>4.35</v>
       </c>
       <c r="O4" t="n">
-        <v>80694475205</v>
+        <v>82651645930</v>
       </c>
       <c r="P4" t="n">
         <v>22450</v>
@@ -843,24 +843,24 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>12670</v>
+        <v>12660</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>'+13.12%</t>
+          <t>'+13.04%</t>
         </is>
       </c>
       <c r="D5" t="n">
         <v>-0.04</v>
       </c>
       <c r="E5" t="n">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="F5" t="n">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="G5" t="n">
-        <v>684</v>
+        <v>685</v>
       </c>
       <c r="H5" t="n">
         <v>15.04</v>
@@ -886,7 +886,7 @@
         <v>15.08</v>
       </c>
       <c r="O5" t="n">
-        <v>37475732755</v>
+        <v>38208777625</v>
       </c>
       <c r="P5" t="n">
         <v>18960</v>
@@ -935,24 +935,24 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>8650</v>
+        <v>8590</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>'+12.34%</t>
+          <t>'+11.56%</t>
         </is>
       </c>
       <c r="D6" t="n">
         <v>0.37</v>
       </c>
       <c r="E6" t="n">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="F6" t="n">
         <v>37</v>
       </c>
       <c r="G6" t="n">
-        <v>108</v>
+        <v>111</v>
       </c>
       <c r="H6" t="n">
         <v>13.29</v>
@@ -972,13 +972,13 @@
         <v>9500</v>
       </c>
       <c r="M6" t="n">
-        <v>8610</v>
+        <v>8430</v>
       </c>
       <c r="N6" t="n">
         <v>12.92</v>
       </c>
       <c r="O6" t="n">
-        <v>6609665580</v>
+        <v>6962154870</v>
       </c>
       <c r="P6" t="n">
         <v>13670</v>
@@ -1027,18 +1027,18 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>6630</v>
+        <v>6550</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>'+6.25%</t>
+          <t>'+4.97%</t>
         </is>
       </c>
       <c r="D7" t="n">
         <v>0</v>
       </c>
       <c r="E7" t="n">
-        <v>59</v>
+        <v>63</v>
       </c>
       <c r="F7" t="n">
         <v>26</v>
@@ -1070,7 +1070,7 @@
         <v>0</v>
       </c>
       <c r="O7" t="n">
-        <v>13764019320</v>
+        <v>13981775500</v>
       </c>
       <c r="P7" t="n">
         <v>16620</v>
@@ -1119,24 +1119,24 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>29250</v>
+        <v>29400</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>'+4.28%</t>
+          <t>'+4.81%</t>
         </is>
       </c>
       <c r="D8" t="n">
         <v>-0.36</v>
       </c>
       <c r="E8" t="n">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="F8" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="G8" t="n">
-        <v>194</v>
+        <v>201</v>
       </c>
       <c r="H8" t="n">
         <v>4.69</v>
@@ -1162,7 +1162,7 @@
         <v>5.05</v>
       </c>
       <c r="O8" t="n">
-        <v>99083503750</v>
+        <v>102509373625</v>
       </c>
       <c r="P8" t="n">
         <v>50600</v>
@@ -1207,31 +1207,31 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>양지사</t>
+          <t>루닛</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>6900</v>
+        <v>15510</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>'+3.92%</t>
+          <t>'+3.54%</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>-0.05</v>
+        <v>-0.9</v>
       </c>
       <c r="E9" t="n">
-        <v>50</v>
+        <v>62</v>
       </c>
       <c r="F9" t="n">
-        <v>30</v>
+        <v>48</v>
       </c>
       <c r="G9" t="n">
-        <v>52</v>
+        <v>244</v>
       </c>
       <c r="H9" t="n">
-        <v>0.85</v>
+        <v>7.15</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
@@ -1239,38 +1239,38 @@
         </is>
       </c>
       <c r="J9" t="n">
-        <v>6640</v>
+        <v>14980</v>
       </c>
       <c r="K9" t="n">
-        <v>7210</v>
+        <v>14980</v>
       </c>
       <c r="L9" t="n">
-        <v>7500</v>
+        <v>16150</v>
       </c>
       <c r="M9" t="n">
-        <v>6730</v>
+        <v>14610</v>
       </c>
       <c r="N9" t="n">
-        <v>0.9</v>
+        <v>8.050000000000001</v>
       </c>
       <c r="O9" t="n">
-        <v>28169511565</v>
+        <v>40679318870</v>
       </c>
       <c r="P9" t="n">
-        <v>9820</v>
+        <v>49800</v>
       </c>
       <c r="Q9" t="n">
-        <v>4000</v>
+        <v>8180</v>
       </c>
       <c r="R9" t="n">
-        <v>-63000</v>
+        <v>109000</v>
       </c>
       <c r="S9" t="n">
-        <v>0</v>
+        <v>168000</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>미국 시장 급등에 따른 주가 상승 기대감. 594억 규모 공급 계약 사실 확인.</t>
+          <t>유방암 위험 예측 솔루션 FDA 승인 신청 및 AI 신약개발 기대감. 5,000억 원 가치 평가.</t>
         </is>
       </c>
       <c r="U9" t="inlineStr"/>
@@ -1279,11 +1279,11 @@
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>['공급 계약', '유통 물량', '주포']</t>
+          <t>['AI 신약개발', 'FDA 승인', '암 진단']</t>
         </is>
       </c>
       <c r="X9" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="Y9" t="inlineStr">
         <is>
@@ -1292,130 +1292,130 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>030960</t>
+          <t>328130</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>한화비전</t>
+          <t>서울바이오시스</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>51000</v>
+        <v>8830</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>'+3.87%</t>
+          <t>'+2.91%</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>-0.82</v>
+        <v>0.01</v>
       </c>
       <c r="E10" t="n">
-        <v>85</v>
+        <v>77</v>
       </c>
       <c r="F10" t="n">
-        <v>55</v>
+        <v>47</v>
       </c>
       <c r="G10" t="n">
-        <v>176</v>
+        <v>203</v>
       </c>
       <c r="H10" t="n">
-        <v>23.82</v>
+        <v>2.67</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J10" t="n">
-        <v>49100</v>
+        <v>8580</v>
       </c>
       <c r="K10" t="n">
-        <v>49450</v>
+        <v>11090</v>
       </c>
       <c r="L10" t="n">
-        <v>52000</v>
+        <v>11150</v>
       </c>
       <c r="M10" t="n">
-        <v>48050</v>
+        <v>8400</v>
       </c>
       <c r="N10" t="n">
-        <v>24.64</v>
+        <v>2.66</v>
       </c>
       <c r="O10" t="n">
-        <v>44378374100</v>
+        <v>25109902365</v>
       </c>
       <c r="P10" t="n">
-        <v>97900</v>
+        <v>19270</v>
       </c>
       <c r="Q10" t="n">
-        <v>30950</v>
+        <v>2135</v>
       </c>
       <c r="R10" t="n">
-        <v>-37000</v>
+        <v>-363000</v>
       </c>
       <c r="S10" t="n">
-        <v>55000</v>
+        <v>-2000</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>최대 실적 발표에도 불구하고 주가 상승이 미미한 것에 대한 의문 제기. TC본더 매출 본격화 및 HBM 수요 증가에 따른 향후 주가 상승 기대.</t>
+          <t>서울반도체와 동반 상승 기대. 광통신 사업 연계 및 매출 조 단위 전망.</t>
         </is>
       </c>
       <c r="U10" t="inlineStr"/>
       <c r="V10" t="n">
-        <v>0.6</v>
+        <v>0</v>
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>['실적', 'HBM', 'TC본더']</t>
+          <t>['광통신', '신기술', '매출']</t>
         </is>
       </c>
       <c r="X10" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>활성</t>
+          <t>추적</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>489790</t>
+          <t>092190</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>빛과전자</t>
+          <t>양지사</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>4155</v>
+        <v>6790</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>'+2.85%</t>
+          <t>'+2.26%</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>-0.77</v>
+        <v>-0.05</v>
       </c>
       <c r="E11" t="n">
-        <v>45</v>
+        <v>52</v>
       </c>
       <c r="F11" t="n">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="G11" t="n">
-        <v>119</v>
+        <v>57</v>
       </c>
       <c r="H11" t="n">
-        <v>1.43</v>
+        <v>0.85</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>
@@ -1423,38 +1423,38 @@
         </is>
       </c>
       <c r="J11" t="n">
-        <v>4040</v>
+        <v>6640</v>
       </c>
       <c r="K11" t="n">
-        <v>3925</v>
+        <v>7210</v>
       </c>
       <c r="L11" t="n">
-        <v>4265</v>
+        <v>7500</v>
       </c>
       <c r="M11" t="n">
-        <v>3880</v>
+        <v>6730</v>
       </c>
       <c r="N11" t="n">
-        <v>2.2</v>
+        <v>0.9</v>
       </c>
       <c r="O11" t="n">
-        <v>60805109814</v>
+        <v>28547885235</v>
       </c>
       <c r="P11" t="n">
-        <v>8100</v>
+        <v>9820</v>
       </c>
       <c r="Q11" t="n">
-        <v>592</v>
+        <v>4000</v>
       </c>
       <c r="R11" t="n">
-        <v>-37000</v>
+        <v>-63000</v>
       </c>
       <c r="S11" t="n">
         <v>0</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>상승 기대감과 함께 급등 가능성 언급. 외국인 및 프로그램 매수세 확인되나, '개잡주'라는 부정적 표현도 혼재.</t>
+          <t>미국 시장 급등에 따른 주가 상승 기대감. 594억 규모 공급 계약 사실 확인.</t>
         </is>
       </c>
       <c r="U11" t="inlineStr"/>
@@ -1463,11 +1463,11 @@
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>['급등 기대', '외국인 매수', '개잡주']</t>
+          <t>['공급 계약', '유통 물량', '주포']</t>
         </is>
       </c>
       <c r="X11" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="Y11" t="inlineStr">
         <is>
@@ -1476,130 +1476,130 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>069540</t>
+          <t>030960</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>루닛</t>
+          <t>한화비전</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>15300</v>
+        <v>50100</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>'+2.14%</t>
+          <t>'+2.04%</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>-0.9</v>
+        <v>-0.82</v>
       </c>
       <c r="E12" t="n">
-        <v>60</v>
+        <v>88</v>
       </c>
       <c r="F12" t="n">
-        <v>48</v>
+        <v>57</v>
       </c>
       <c r="G12" t="n">
-        <v>243</v>
+        <v>180</v>
       </c>
       <c r="H12" t="n">
-        <v>7.15</v>
+        <v>23.82</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J12" t="n">
-        <v>14980</v>
+        <v>49100</v>
       </c>
       <c r="K12" t="n">
-        <v>14980</v>
+        <v>49450</v>
       </c>
       <c r="L12" t="n">
-        <v>16150</v>
+        <v>52000</v>
       </c>
       <c r="M12" t="n">
-        <v>14610</v>
+        <v>48050</v>
       </c>
       <c r="N12" t="n">
-        <v>8.050000000000001</v>
+        <v>24.64</v>
       </c>
       <c r="O12" t="n">
-        <v>39934023525</v>
+        <v>45420491900</v>
       </c>
       <c r="P12" t="n">
-        <v>49800</v>
+        <v>97900</v>
       </c>
       <c r="Q12" t="n">
-        <v>8180</v>
+        <v>30950</v>
       </c>
       <c r="R12" t="n">
-        <v>109000</v>
+        <v>-37000</v>
       </c>
       <c r="S12" t="n">
-        <v>168000</v>
+        <v>55000</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>유방암 위험 예측 솔루션 FDA 승인 신청 및 AI 신약개발 기대감. 5,000억 원 가치 평가.</t>
+          <t>최대 실적 발표 후 상승 기대. TC본더 매출 본격화 및 HBM 시대 재부각.</t>
         </is>
       </c>
       <c r="U12" t="inlineStr"/>
       <c r="V12" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>['AI 신약개발', 'FDA 승인', '암 진단']</t>
+          <t>['실적', 'TC본더', 'HBM']</t>
         </is>
       </c>
       <c r="X12" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>추적</t>
+          <t>활성</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>328130</t>
+          <t>489790</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>서울바이오시스</t>
+          <t>빛과전자</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>8700</v>
+        <v>4065</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>'+1.40%</t>
+          <t>'+0.62%</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>0.01</v>
+        <v>-0.77</v>
       </c>
       <c r="E13" t="n">
-        <v>76</v>
+        <v>57</v>
       </c>
       <c r="F13" t="n">
-        <v>47</v>
+        <v>38</v>
       </c>
       <c r="G13" t="n">
-        <v>199</v>
+        <v>120</v>
       </c>
       <c r="H13" t="n">
-        <v>2.67</v>
+        <v>1.43</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
@@ -1607,38 +1607,38 @@
         </is>
       </c>
       <c r="J13" t="n">
-        <v>8580</v>
+        <v>4040</v>
       </c>
       <c r="K13" t="n">
-        <v>11090</v>
+        <v>3925</v>
       </c>
       <c r="L13" t="n">
-        <v>11150</v>
+        <v>4265</v>
       </c>
       <c r="M13" t="n">
-        <v>8400</v>
+        <v>3880</v>
       </c>
       <c r="N13" t="n">
-        <v>2.66</v>
+        <v>2.2</v>
       </c>
       <c r="O13" t="n">
-        <v>24737501145</v>
+        <v>65692796644</v>
       </c>
       <c r="P13" t="n">
-        <v>19270</v>
+        <v>8100</v>
       </c>
       <c r="Q13" t="n">
-        <v>2135</v>
+        <v>592</v>
       </c>
       <c r="R13" t="n">
-        <v>-363000</v>
+        <v>-37000</v>
       </c>
       <c r="S13" t="n">
-        <v>-2000</v>
+        <v>0</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>서울반도체와 동반 상승 기대. 광통신 사업 연계 및 매출 조 단위 전망.</t>
+          <t>상승 기대감과 함께 급등 가능성 언급. 외국인 및 프로그램 매수세 확인되나, '개잡주'라는 부정적 표현도 혼재.</t>
         </is>
       </c>
       <c r="U13" t="inlineStr"/>
@@ -1647,11 +1647,11 @@
       </c>
       <c r="W13" t="inlineStr">
         <is>
-          <t>['광통신', '신기술', '매출']</t>
+          <t>['급등 기대', '외국인 매수', '개잡주']</t>
         </is>
       </c>
       <c r="X13" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="Y13" t="inlineStr">
         <is>
@@ -1660,7 +1660,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>092190</t>
+          <t>069540</t>
         </is>
       </c>
     </row>
@@ -1671,24 +1671,24 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>15810</v>
+        <v>15780</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>'+0.57%</t>
+          <t>'+0.38%</t>
         </is>
       </c>
       <c r="D14" t="n">
         <v>0.06</v>
       </c>
       <c r="E14" t="n">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="F14" t="n">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="G14" t="n">
-        <v>215</v>
+        <v>213</v>
       </c>
       <c r="H14" t="n">
         <v>28.13</v>
@@ -1714,7 +1714,7 @@
         <v>28.07</v>
       </c>
       <c r="O14" t="n">
-        <v>33066759470</v>
+        <v>34267484925</v>
       </c>
       <c r="P14" t="n">
         <v>35350</v>
@@ -1730,16 +1730,16 @@
       </c>
       <c r="T14" t="inlineStr">
         <is>
-          <t>미국 조선주 상승과 대비되는 국내 조선주 흐름에 대한 실망감. 단기 차익 실현보다는 장기적인 큰 수익을 기대하는 의견.</t>
+          <t>미국 조선주 강세 속 국내 증시 부진. 증권사 리포트 및 기대감 존재.</t>
         </is>
       </c>
       <c r="U14" t="inlineStr"/>
       <c r="V14" t="n">
-        <v>0.2</v>
+        <v>0.4</v>
       </c>
       <c r="W14" t="inlineStr">
         <is>
-          <t>['조선주', '실적', '기관']</t>
+          <t>['조선주', '증권사리포트', ' 기대']</t>
         </is>
       </c>
       <c r="X14" t="n">
@@ -1763,24 +1763,24 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>7310</v>
+        <v>7320</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>'-1.88%</t>
+          <t>'-1.74%</t>
         </is>
       </c>
       <c r="D15" t="n">
         <v>-0.02</v>
       </c>
       <c r="E15" t="n">
-        <v>48</v>
+        <v>52</v>
       </c>
       <c r="F15" t="n">
         <v>25</v>
       </c>
       <c r="G15" t="n">
-        <v>118</v>
+        <v>129</v>
       </c>
       <c r="H15" t="n">
         <v>25.3</v>
@@ -1800,13 +1800,13 @@
         <v>7570</v>
       </c>
       <c r="M15" t="n">
-        <v>7290</v>
+        <v>7280</v>
       </c>
       <c r="N15" t="n">
         <v>25.32</v>
       </c>
       <c r="O15" t="n">
-        <v>6608840890</v>
+        <v>6954200050</v>
       </c>
       <c r="P15" t="n">
         <v>17950</v>
@@ -1855,24 +1855,24 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>61000</v>
+        <v>61100</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>'-2.87%</t>
+          <t>'-2.71%</t>
         </is>
       </c>
       <c r="D16" t="n">
         <v>0.21</v>
       </c>
       <c r="E16" t="n">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="F16" t="n">
         <v>30</v>
       </c>
       <c r="G16" t="n">
-        <v>237</v>
+        <v>240</v>
       </c>
       <c r="H16" t="n">
         <v>41.76</v>
@@ -1898,7 +1898,7 @@
         <v>41.55</v>
       </c>
       <c r="O16" t="n">
-        <v>56252405600</v>
+        <v>58626011750</v>
       </c>
       <c r="P16" t="n">
         <v>67300</v>
@@ -1947,24 +1947,24 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>54100</v>
+        <v>54200</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>'-4.59%</t>
+          <t>'-4.41%</t>
         </is>
       </c>
       <c r="D17" t="n">
         <v>-0.2</v>
       </c>
       <c r="E17" t="n">
-        <v>227</v>
+        <v>240</v>
       </c>
       <c r="F17" t="n">
-        <v>157</v>
+        <v>166</v>
       </c>
       <c r="G17" t="n">
-        <v>767</v>
+        <v>782</v>
       </c>
       <c r="H17" t="n">
         <v>22.14</v>
@@ -1990,7 +1990,7 @@
         <v>22.34</v>
       </c>
       <c r="O17" t="n">
-        <v>53241659800</v>
+        <v>54946909600</v>
       </c>
       <c r="P17" t="n">
         <v>139200</v>
@@ -2039,24 +2039,24 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>10990</v>
+        <v>11000</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>'-5.42%</t>
+          <t>'-5.34%</t>
         </is>
       </c>
       <c r="D18" t="n">
         <v>0.13</v>
       </c>
       <c r="E18" t="n">
-        <v>283</v>
+        <v>293</v>
       </c>
       <c r="F18" t="n">
-        <v>146</v>
+        <v>149</v>
       </c>
       <c r="G18" t="n">
-        <v>908</v>
+        <v>926</v>
       </c>
       <c r="H18" t="n">
         <v>9.73</v>
@@ -2082,7 +2082,7 @@
         <v>9.6</v>
       </c>
       <c r="O18" t="n">
-        <v>39091436400</v>
+        <v>40380142540</v>
       </c>
       <c r="P18" t="n">
         <v>40350</v>
@@ -2145,10 +2145,10 @@
         <v>800</v>
       </c>
       <c r="F19" t="n">
-        <v>519</v>
+        <v>537</v>
       </c>
       <c r="G19" t="n">
-        <v>1264</v>
+        <v>1243</v>
       </c>
       <c r="H19" t="n">
         <v>46.17</v>
@@ -2174,7 +2174,7 @@
         <v>46.19</v>
       </c>
       <c r="O19" t="n">
-        <v>1746774014000</v>
+        <v>1801254010750</v>
       </c>
       <c r="P19" t="n">
         <v>374500</v>
@@ -2190,7 +2190,7 @@
       </c>
       <c r="T19" t="inlineStr">
         <is>
-          <t>주주 환원 발표 기대에도 불구하고, 이재용 관련 정치적 언급과 주가 하락에 대한 불만이 혼재하는 내용. 공매도 금지 관련 언급은 타 종목과 연관된 것으로 보임.</t>
+          <t>이재용 주주환원 발표 기대감 속 정치적 언급 혼재. 국장 및 개인 매수세 집중.</t>
         </is>
       </c>
       <c r="U19" t="inlineStr"/>
@@ -2199,7 +2199,7 @@
       </c>
       <c r="W19" t="inlineStr">
         <is>
-          <t>['주주환원', '이재용', '주가 하락']</t>
+          <t>['주주환원', '정치', '개인매수']</t>
         </is>
       </c>
       <c r="X19" t="n">
@@ -2223,24 +2223,24 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>21850</v>
+        <v>21750</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>'-7.42%</t>
+          <t>'-7.84%</t>
         </is>
       </c>
       <c r="D20" t="n">
         <v>-0.63</v>
       </c>
       <c r="E20" t="n">
-        <v>182</v>
+        <v>189</v>
       </c>
       <c r="F20" t="n">
-        <v>141</v>
+        <v>145</v>
       </c>
       <c r="G20" t="n">
-        <v>423</v>
+        <v>441</v>
       </c>
       <c r="H20" t="n">
         <v>11.6</v>
@@ -2266,7 +2266,7 @@
         <v>12.23</v>
       </c>
       <c r="O20" t="n">
-        <v>62690318325</v>
+        <v>64892996050</v>
       </c>
       <c r="P20" t="n">
         <v>59300</v>
@@ -2282,16 +2282,16 @@
       </c>
       <c r="T20" t="inlineStr">
         <is>
-          <t>태양광 사업 관련 긍정적 뉴스 언급 있으나, 주가 하락세에 대한 우려가 지배적. 주가 누르기 의혹 제기.</t>
+          <t>김동원 부회장 주가 누르기 의혹 제기. 태양광 수혜 기대와 대규모 주가 하락.</t>
         </is>
       </c>
       <c r="U20" t="inlineStr"/>
       <c r="V20" t="n">
-        <v>0.3</v>
+        <v>0.2</v>
       </c>
       <c r="W20" t="inlineStr">
         <is>
-          <t>['태양광', '주가 하락', '주가 조작']</t>
+          <t>['주가누르기', '태양광', '카터스빌']</t>
         </is>
       </c>
       <c r="X20" t="n">
@@ -2311,184 +2311,184 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>대한광통신</t>
+          <t>삼성전자우</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>13860</v>
+        <v>169100</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>'-7.78%</t>
+          <t>'-8.05%</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>-0.2</v>
+        <v>-0.13</v>
       </c>
       <c r="E21" t="n">
-        <v>88</v>
+        <v>47</v>
       </c>
       <c r="F21" t="n">
-        <v>48</v>
+        <v>39</v>
       </c>
       <c r="G21" t="n">
-        <v>296</v>
+        <v>145</v>
       </c>
       <c r="H21" t="n">
-        <v>3.13</v>
+        <v>74.87</v>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J21" t="n">
-        <v>15030</v>
+        <v>183900</v>
       </c>
       <c r="K21" t="n">
-        <v>14500</v>
+        <v>176800</v>
       </c>
       <c r="L21" t="n">
-        <v>14570</v>
+        <v>179000</v>
       </c>
       <c r="M21" t="n">
-        <v>13760</v>
+        <v>168100</v>
       </c>
       <c r="N21" t="n">
-        <v>3.33</v>
+        <v>75</v>
       </c>
       <c r="O21" t="n">
-        <v>32854948200</v>
+        <v>422250738500</v>
       </c>
       <c r="P21" t="n">
-        <v>31500</v>
+        <v>243500</v>
       </c>
       <c r="Q21" t="n">
-        <v>1830</v>
+        <v>71000</v>
       </c>
       <c r="R21" t="n">
-        <v>-118000</v>
+        <v>-416000</v>
       </c>
       <c r="S21" t="n">
-        <v>-23000</v>
+        <v>-18000</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
-          <t>미국 광통신주 하락세와 대비되는 국내 광통신주 흐름에 대한 우려. 일부 긍정적인 언급도 있으나 전반적으로 하락 조정에 대한 예상.</t>
+          <t>주가 조작 및 증여세 관련 부정적 언급과 함께 시장 대폭락에 대한 우려가 존재. 우선주 소각 및 반등 기대도 일부.</t>
         </is>
       </c>
       <c r="U21" t="inlineStr"/>
       <c r="V21" t="n">
-        <v>0.3</v>
+        <v>0</v>
       </c>
       <c r="W21" t="inlineStr">
         <is>
-          <t>['광통신주', '미국 시장', '조정']</t>
+          <t>['주가 조작', '증여세', '우선주 소각']</t>
         </is>
       </c>
       <c r="X21" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>활성</t>
+          <t>추적</t>
         </is>
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>010170</t>
+          <t>005935</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>삼성전자우</t>
+          <t>대한광통신</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>169300</v>
+        <v>13790</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>'-7.94%</t>
+          <t>'-8.25%</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>-0.13</v>
+        <v>-0.2</v>
       </c>
       <c r="E22" t="n">
-        <v>44</v>
+        <v>95</v>
       </c>
       <c r="F22" t="n">
-        <v>38</v>
+        <v>53</v>
       </c>
       <c r="G22" t="n">
-        <v>135</v>
+        <v>330</v>
       </c>
       <c r="H22" t="n">
-        <v>74.87</v>
+        <v>3.13</v>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J22" t="n">
-        <v>183900</v>
+        <v>15030</v>
       </c>
       <c r="K22" t="n">
-        <v>176800</v>
+        <v>14500</v>
       </c>
       <c r="L22" t="n">
-        <v>179000</v>
+        <v>14570</v>
       </c>
       <c r="M22" t="n">
-        <v>168400</v>
+        <v>13740</v>
       </c>
       <c r="N22" t="n">
-        <v>75</v>
+        <v>3.33</v>
       </c>
       <c r="O22" t="n">
-        <v>401302653900</v>
+        <v>34237175265</v>
       </c>
       <c r="P22" t="n">
-        <v>243500</v>
+        <v>31500</v>
       </c>
       <c r="Q22" t="n">
-        <v>71000</v>
+        <v>1830</v>
       </c>
       <c r="R22" t="n">
-        <v>-416000</v>
+        <v>-118000</v>
       </c>
       <c r="S22" t="n">
-        <v>-18000</v>
+        <v>-23000</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
-          <t>주가 조작 및 증여세 관련 부정적 언급과 함께 시장 대폭락에 대한 우려가 존재. 우선주 소각 및 반등 기대도 일부.</t>
+          <t>미국 광통신주 강세에 따른 기대감. 특허 보유 및 추가 수주 가능성 언급.</t>
         </is>
       </c>
       <c r="U22" t="inlineStr"/>
       <c r="V22" t="n">
-        <v>0</v>
+        <v>0.3</v>
       </c>
       <c r="W22" t="inlineStr">
         <is>
-          <t>['주가 조작', '증여세', '우선주 소각']</t>
+          <t>['광통신', '특허', '수주']</t>
         </is>
       </c>
       <c r="X22" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>추적</t>
+          <t>활성</t>
         </is>
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>005935</t>
+          <t>010170</t>
         </is>
       </c>
     </row>
@@ -2499,11 +2499,11 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>1395000</v>
+        <v>1396000</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>'-8.58%</t>
+          <t>'-8.52%</t>
         </is>
       </c>
       <c r="D23" t="n">
@@ -2513,10 +2513,10 @@
         <v>800</v>
       </c>
       <c r="F23" t="n">
-        <v>545</v>
+        <v>535</v>
       </c>
       <c r="G23" t="n">
-        <v>1191</v>
+        <v>1248</v>
       </c>
       <c r="H23" t="n">
         <v>48.72</v>
@@ -2542,7 +2542,7 @@
         <v>48.66</v>
       </c>
       <c r="O23" t="n">
-        <v>2148223247000</v>
+        <v>2239863483500</v>
       </c>
       <c r="P23" t="n">
         <v>2987000</v>
@@ -2558,7 +2558,7 @@
       </c>
       <c r="T23" t="inlineStr">
         <is>
-          <t>주가 하락에 대한 정치적 원인 분석과 더불어, 외국인 및 기관의 공매도에 대한 불만 표출. 단기 대응 및 매도 의견이 지배적.</t>
+          <t>연이은 주가 하락에 대한 불만. 정치적 언급과 함께 단타 대응 촉구.</t>
         </is>
       </c>
       <c r="U23" t="inlineStr"/>
@@ -2567,7 +2567,7 @@
       </c>
       <c r="W23" t="inlineStr">
         <is>
-          <t>['주가 하락', '공매도', '외국인']</t>
+          <t>['주가하락', '단타', '외국인']</t>
         </is>
       </c>
       <c r="X23" t="n">
@@ -2591,24 +2591,24 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>7180</v>
+        <v>7140</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>'-9.11%</t>
+          <t>'-9.62%</t>
         </is>
       </c>
       <c r="D24" t="n">
         <v>-0.03</v>
       </c>
       <c r="E24" t="n">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="F24" t="n">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="G24" t="n">
-        <v>91</v>
+        <v>98</v>
       </c>
       <c r="H24" t="n">
         <v>0.39</v>
@@ -2634,7 +2634,7 @@
         <v>0.42</v>
       </c>
       <c r="O24" t="n">
-        <v>13873404435</v>
+        <v>14128300455</v>
       </c>
       <c r="P24" t="n">
         <v>10300</v>
@@ -2683,24 +2683,24 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>117400</v>
+        <v>116800</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>'-15.05%</t>
+          <t>'-15.48%</t>
         </is>
       </c>
       <c r="D25" t="n">
         <v>-0.26</v>
       </c>
       <c r="E25" t="n">
-        <v>97</v>
+        <v>107</v>
       </c>
       <c r="F25" t="n">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="G25" t="n">
-        <v>217</v>
+        <v>240</v>
       </c>
       <c r="H25" t="n">
         <v>14.2</v>
@@ -2720,13 +2720,13 @@
         <v>132900</v>
       </c>
       <c r="M25" t="n">
-        <v>117000</v>
+        <v>116500</v>
       </c>
       <c r="N25" t="n">
         <v>14.46</v>
       </c>
       <c r="O25" t="n">
-        <v>105559651700</v>
+        <v>110737723700</v>
       </c>
       <c r="P25" t="n">
         <v>198000</v>
@@ -2742,16 +2742,16 @@
       </c>
       <c r="T25" t="inlineStr">
         <is>
-          <t>실적 호조 기대에도 불구하고 큰 폭의 하락세 기록. 기관 매도세 및 수급 불안정 우려 속에 저점 매수 기회 모색.</t>
+          <t>SK하이닉스 물량 확대 관련 기대감 속 급락. 실적 대비 주가 하락에 대한 불만.</t>
         </is>
       </c>
       <c r="U25" t="inlineStr"/>
       <c r="V25" t="n">
-        <v>0.3</v>
+        <v>0.4</v>
       </c>
       <c r="W25" t="inlineStr">
         <is>
-          <t>['실적', '기관', '수급']</t>
+          <t>['SK하이닉스', '실적', '기판주']</t>
         </is>
       </c>
       <c r="X25" t="n">
@@ -2775,11 +2775,11 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>13350</v>
+        <v>13320</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>'-21.47%</t>
+          <t>'-21.65%</t>
         </is>
       </c>
       <c r="D26" t="n">
@@ -2789,10 +2789,10 @@
         <v>152</v>
       </c>
       <c r="F26" t="n">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="G26" t="n">
-        <v>116</v>
+        <v>120</v>
       </c>
       <c r="H26" t="n">
         <v>0.66</v>
@@ -2818,7 +2818,7 @@
         <v>0.65</v>
       </c>
       <c r="O26" t="n">
-        <v>28216690115</v>
+        <v>28718618425</v>
       </c>
       <c r="P26" t="n">
         <v>28800</v>
@@ -2834,16 +2834,16 @@
       </c>
       <c r="T26" t="inlineStr">
         <is>
-          <t>보호예수 물량 해제 및 반도체 업황 회복 기대감 속 등락 반복. 기술적 반등 및 급등 전망과 급락 우려 공존.</t>
+          <t>보호예수 해제 후 급락. 기술적 반등 및 향후 매집 기회 언급.</t>
         </is>
       </c>
       <c r="U26" t="inlineStr"/>
       <c r="V26" t="n">
-        <v>0.2</v>
+        <v>0.3</v>
       </c>
       <c r="W26" t="inlineStr">
         <is>
-          <t>['보호예수', '반도체', '기술적 반등']</t>
+          <t>['보호예수', '급락', '매집']</t>
         </is>
       </c>
       <c r="X26" t="n">
@@ -2867,21 +2867,21 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>1863</v>
+        <v>1842</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>'-27.65%</t>
+          <t>'-28.47%</t>
         </is>
       </c>
       <c r="D27" t="n">
         <v>1.45</v>
       </c>
       <c r="E27" t="n">
-        <v>51</v>
+        <v>55</v>
       </c>
       <c r="F27" t="n">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="G27" t="n">
         <v>28</v>
@@ -2910,7 +2910,7 @@
         <v>3.35</v>
       </c>
       <c r="O27" t="n">
-        <v>6187021131</v>
+        <v>6307226549</v>
       </c>
       <c r="P27" t="n">
         <v>5700</v>
@@ -2959,24 +2959,24 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>10350</v>
+        <v>10500</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>'-31.00%</t>
+          <t>'-30.00%</t>
         </is>
       </c>
       <c r="D28" t="n">
         <v>0</v>
       </c>
       <c r="E28" t="n">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="F28" t="n">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="G28" t="n">
-        <v>496</v>
+        <v>500</v>
       </c>
       <c r="H28" t="n">
         <v>3.05</v>
@@ -3002,7 +3002,7 @@
         <v>0</v>
       </c>
       <c r="O28" t="n">
-        <v>92260860295</v>
+        <v>93738263290</v>
       </c>
       <c r="P28" t="n">
         <v>12700</v>
@@ -3018,16 +3018,16 @@
       </c>
       <c r="T28" t="inlineStr">
         <is>
-          <t>상장 직후 유통 물량 소화 및 손바뀜을 거치며 향후 주가 상승에 대한 기대감. 국내외 실내 골프 대회 개최 및 대중화에 따른 수혜 전망.</t>
+          <t>상장 초기 급락 후 반등 기대. 유통물량 적고 높은 당기순이익으로 인한 기대감.</t>
         </is>
       </c>
       <c r="U28" t="inlineStr"/>
       <c r="V28" t="n">
-        <v>0.5</v>
+        <v>0.4</v>
       </c>
       <c r="W28" t="inlineStr">
         <is>
-          <t>['실내 골프', '유통 물량', '주포']</t>
+          <t>['유통물량', '당기순이익', '골프주']</t>
         </is>
       </c>
       <c r="X28" t="n">

--- a/data/trending_integrated_20261030_11.xlsx
+++ b/data/trending_integrated_20261030_11.xlsx
@@ -567,24 +567,24 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>19520</v>
+        <v>18620</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>'+116.89%</t>
+          <t>'+106.89%</t>
         </is>
       </c>
       <c r="D2" t="n">
         <v>0</v>
       </c>
       <c r="E2" t="n">
-        <v>275</v>
+        <v>316</v>
       </c>
       <c r="F2" t="n">
-        <v>165</v>
+        <v>184</v>
       </c>
       <c r="G2" t="n">
-        <v>370</v>
+        <v>422</v>
       </c>
       <c r="H2" t="n">
         <v>1.98</v>
@@ -610,7 +610,7 @@
         <v>0</v>
       </c>
       <c r="O2" t="n">
-        <v>297773348260</v>
+        <v>322858728215</v>
       </c>
       <c r="P2" t="n">
         <v>21700</v>
@@ -626,16 +626,16 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>신규 상장주 특유의 급등락 패턴 반복. 매수세 부재 및 투자 주의 당부.</t>
+          <t>단기 급등 후 하락 반복 패턴 지적. 신규 상장주 투자 위험성 및 목표가 제시.</t>
         </is>
       </c>
       <c r="U2" t="inlineStr"/>
       <c r="V2" t="n">
-        <v>0</v>
+        <v>0.3</v>
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>['신규상장주', '급등락', '패턴']</t>
+          <t>['신규상장주', '단기급등', '패턴']</t>
         </is>
       </c>
       <c r="X2" t="n">
@@ -659,24 +659,24 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>2970</v>
+        <v>2870</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>'+21.22%</t>
+          <t>'+17.14%</t>
         </is>
       </c>
       <c r="D3" t="n">
         <v>0.16</v>
       </c>
       <c r="E3" t="n">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="F3" t="n">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="G3" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="H3" t="n">
         <v>0.79</v>
@@ -702,7 +702,7 @@
         <v>0.63</v>
       </c>
       <c r="O3" t="n">
-        <v>10415377274</v>
+        <v>10876987972</v>
       </c>
       <c r="P3" t="n">
         <v>3170</v>
@@ -751,24 +751,24 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>19010</v>
+        <v>19360</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>'+14.17%</t>
+          <t>'+16.28%</t>
         </is>
       </c>
       <c r="D4" t="n">
         <v>-0.75</v>
       </c>
       <c r="E4" t="n">
-        <v>73</v>
+        <v>79</v>
       </c>
       <c r="F4" t="n">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="G4" t="n">
-        <v>103</v>
+        <v>113</v>
       </c>
       <c r="H4" t="n">
         <v>3.6</v>
@@ -794,7 +794,7 @@
         <v>4.35</v>
       </c>
       <c r="O4" t="n">
-        <v>82651645930</v>
+        <v>85549529695</v>
       </c>
       <c r="P4" t="n">
         <v>22450</v>
@@ -843,24 +843,24 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>12660</v>
+        <v>12680</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>'+13.04%</t>
+          <t>'+13.21%</t>
         </is>
       </c>
       <c r="D5" t="n">
         <v>-0.04</v>
       </c>
       <c r="E5" t="n">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="F5" t="n">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="G5" t="n">
-        <v>685</v>
+        <v>692</v>
       </c>
       <c r="H5" t="n">
         <v>15.04</v>
@@ -886,7 +886,7 @@
         <v>15.08</v>
       </c>
       <c r="O5" t="n">
-        <v>38208777625</v>
+        <v>38811347020</v>
       </c>
       <c r="P5" t="n">
         <v>18960</v>
@@ -902,7 +902,7 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>세계 최초 희토류 없는 백색 LED 개발 성공 및 100억 달러 시장 석권 가능성에 대한 높은 기대감. 공매도에 대한 언급과 함께 주가 상승 전망.</t>
+          <t>세계 최초 희토류 없는 백색 LED 개발 등 기술력 기반의 주가 상승 전망. 10만원 목표가 제시.</t>
         </is>
       </c>
       <c r="U5" t="inlineStr"/>
@@ -911,7 +911,7 @@
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>['백색 LED', '희토류', '공매도']</t>
+          <t>['백색LED', '희토류', '기술개발']</t>
         </is>
       </c>
       <c r="X5" t="n">
@@ -935,11 +935,11 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>8590</v>
+        <v>8630</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>'+11.56%</t>
+          <t>'+12.08%</t>
         </is>
       </c>
       <c r="D6" t="n">
@@ -952,7 +952,7 @@
         <v>37</v>
       </c>
       <c r="G6" t="n">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="H6" t="n">
         <v>13.29</v>
@@ -978,7 +978,7 @@
         <v>12.92</v>
       </c>
       <c r="O6" t="n">
-        <v>6962154870</v>
+        <v>7035178305</v>
       </c>
       <c r="P6" t="n">
         <v>13670</v>
@@ -1027,24 +1027,24 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>6550</v>
+        <v>6630</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>'+4.97%</t>
+          <t>'+6.25%</t>
         </is>
       </c>
       <c r="D7" t="n">
         <v>0</v>
       </c>
       <c r="E7" t="n">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="F7" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="G7" t="n">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="H7" t="n">
         <v>0</v>
@@ -1070,7 +1070,7 @@
         <v>0</v>
       </c>
       <c r="O7" t="n">
-        <v>13981775500</v>
+        <v>14196770680</v>
       </c>
       <c r="P7" t="n">
         <v>16620</v>
@@ -1130,13 +1130,13 @@
         <v>-0.36</v>
       </c>
       <c r="E8" t="n">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="F8" t="n">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="G8" t="n">
-        <v>201</v>
+        <v>207</v>
       </c>
       <c r="H8" t="n">
         <v>4.69</v>
@@ -1162,7 +1162,7 @@
         <v>5.05</v>
       </c>
       <c r="O8" t="n">
-        <v>102509373625</v>
+        <v>104256380600</v>
       </c>
       <c r="P8" t="n">
         <v>50600</v>
@@ -1211,24 +1211,24 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>15510</v>
+        <v>15630</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>'+3.54%</t>
+          <t>'+4.34%</t>
         </is>
       </c>
       <c r="D9" t="n">
         <v>-0.9</v>
       </c>
       <c r="E9" t="n">
-        <v>62</v>
+        <v>67</v>
       </c>
       <c r="F9" t="n">
-        <v>48</v>
+        <v>52</v>
       </c>
       <c r="G9" t="n">
-        <v>244</v>
+        <v>263</v>
       </c>
       <c r="H9" t="n">
         <v>7.15</v>
@@ -1254,7 +1254,7 @@
         <v>8.050000000000001</v>
       </c>
       <c r="O9" t="n">
-        <v>40679318870</v>
+        <v>41564327910</v>
       </c>
       <c r="P9" t="n">
         <v>49800</v>
@@ -1303,24 +1303,24 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>8830</v>
+        <v>8840</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>'+2.91%</t>
+          <t>'+3.03%</t>
         </is>
       </c>
       <c r="D10" t="n">
         <v>0.01</v>
       </c>
       <c r="E10" t="n">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="F10" t="n">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="G10" t="n">
-        <v>203</v>
+        <v>209</v>
       </c>
       <c r="H10" t="n">
         <v>2.67</v>
@@ -1346,7 +1346,7 @@
         <v>2.66</v>
       </c>
       <c r="O10" t="n">
-        <v>25109902365</v>
+        <v>25413234625</v>
       </c>
       <c r="P10" t="n">
         <v>19270</v>
@@ -1391,123 +1391,123 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>양지사</t>
+          <t>한화비전</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>6790</v>
+        <v>50300</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>'+2.26%</t>
+          <t>'+2.44%</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>-0.05</v>
+        <v>-0.82</v>
       </c>
       <c r="E11" t="n">
-        <v>52</v>
+        <v>90</v>
       </c>
       <c r="F11" t="n">
-        <v>30</v>
+        <v>58</v>
       </c>
       <c r="G11" t="n">
-        <v>57</v>
+        <v>188</v>
       </c>
       <c r="H11" t="n">
-        <v>0.85</v>
+        <v>23.82</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J11" t="n">
-        <v>6640</v>
+        <v>49100</v>
       </c>
       <c r="K11" t="n">
-        <v>7210</v>
+        <v>49450</v>
       </c>
       <c r="L11" t="n">
-        <v>7500</v>
+        <v>52000</v>
       </c>
       <c r="M11" t="n">
-        <v>6730</v>
+        <v>48050</v>
       </c>
       <c r="N11" t="n">
-        <v>0.9</v>
+        <v>24.64</v>
       </c>
       <c r="O11" t="n">
-        <v>28547885235</v>
+        <v>46217872800</v>
       </c>
       <c r="P11" t="n">
-        <v>9820</v>
+        <v>97900</v>
       </c>
       <c r="Q11" t="n">
-        <v>4000</v>
+        <v>30950</v>
       </c>
       <c r="R11" t="n">
-        <v>-63000</v>
+        <v>-37000</v>
       </c>
       <c r="S11" t="n">
-        <v>0</v>
+        <v>55000</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>미국 시장 급등에 따른 주가 상승 기대감. 594억 규모 공급 계약 사실 확인.</t>
+          <t>최대 실적 발표 후, TC본더 매출 본격화 및 사이버 보안 수혜 기대감. 공매도 청산 및 5만/6만 비전 탈환 목표.</t>
         </is>
       </c>
       <c r="U11" t="inlineStr"/>
       <c r="V11" t="n">
-        <v>0</v>
+        <v>0.4</v>
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>['공급 계약', '유통 물량', '주포']</t>
+          <t>['실적', 'TC본더', '공매도']</t>
         </is>
       </c>
       <c r="X11" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>추적</t>
+          <t>활성</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>030960</t>
+          <t>489790</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>한화비전</t>
+          <t>삼성중공업</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>50100</v>
+        <v>15760</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>'+2.04%</t>
+          <t>'+0.25%</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>-0.82</v>
+        <v>0.06</v>
       </c>
       <c r="E12" t="n">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="F12" t="n">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="G12" t="n">
-        <v>180</v>
+        <v>220</v>
       </c>
       <c r="H12" t="n">
-        <v>23.82</v>
+        <v>28.13</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
@@ -1515,51 +1515,51 @@
         </is>
       </c>
       <c r="J12" t="n">
-        <v>49100</v>
+        <v>15720</v>
       </c>
       <c r="K12" t="n">
-        <v>49450</v>
+        <v>15420</v>
       </c>
       <c r="L12" t="n">
-        <v>52000</v>
+        <v>16050</v>
       </c>
       <c r="M12" t="n">
-        <v>48050</v>
+        <v>15320</v>
       </c>
       <c r="N12" t="n">
-        <v>24.64</v>
+        <v>28.07</v>
       </c>
       <c r="O12" t="n">
-        <v>45420491900</v>
+        <v>35175586345</v>
       </c>
       <c r="P12" t="n">
-        <v>97900</v>
+        <v>35350</v>
       </c>
       <c r="Q12" t="n">
-        <v>30950</v>
+        <v>15320</v>
       </c>
       <c r="R12" t="n">
-        <v>-37000</v>
+        <v>345000</v>
       </c>
       <c r="S12" t="n">
-        <v>55000</v>
+        <v>35000</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>최대 실적 발표 후 상승 기대. TC본더 매출 본격화 및 HBM 시대 재부각.</t>
+          <t>미국 조선주 강세 속 국내 증시 부진. 증권사 리포트 및 기대감 존재.</t>
         </is>
       </c>
       <c r="U12" t="inlineStr"/>
       <c r="V12" t="n">
-        <v>0.5</v>
+        <v>0.4</v>
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>['실적', 'TC본더', 'HBM']</t>
+          <t>['조선주', '증권사리포트', ' 기대']</t>
         </is>
       </c>
       <c r="X12" t="n">
-        <v>2</v>
+        <v>17</v>
       </c>
       <c r="Y12" t="inlineStr">
         <is>
@@ -1568,38 +1568,38 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>489790</t>
+          <t>010140</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>빛과전자</t>
+          <t>양지사</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>4065</v>
+        <v>6620</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>'+0.62%</t>
+          <t>'-0.30%</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>-0.77</v>
+        <v>-0.05</v>
       </c>
       <c r="E13" t="n">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="F13" t="n">
-        <v>38</v>
+        <v>32</v>
       </c>
       <c r="G13" t="n">
-        <v>120</v>
+        <v>59</v>
       </c>
       <c r="H13" t="n">
-        <v>1.43</v>
+        <v>0.85</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
@@ -1607,38 +1607,38 @@
         </is>
       </c>
       <c r="J13" t="n">
-        <v>4040</v>
+        <v>6640</v>
       </c>
       <c r="K13" t="n">
-        <v>3925</v>
+        <v>7210</v>
       </c>
       <c r="L13" t="n">
-        <v>4265</v>
+        <v>7500</v>
       </c>
       <c r="M13" t="n">
-        <v>3880</v>
+        <v>6600</v>
       </c>
       <c r="N13" t="n">
-        <v>2.2</v>
+        <v>0.9</v>
       </c>
       <c r="O13" t="n">
-        <v>65692796644</v>
+        <v>29227064255</v>
       </c>
       <c r="P13" t="n">
-        <v>8100</v>
+        <v>9820</v>
       </c>
       <c r="Q13" t="n">
-        <v>592</v>
+        <v>4000</v>
       </c>
       <c r="R13" t="n">
-        <v>-37000</v>
+        <v>-63000</v>
       </c>
       <c r="S13" t="n">
         <v>0</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>상승 기대감과 함께 급등 가능성 언급. 외국인 및 프로그램 매수세 확인되나, '개잡주'라는 부정적 표현도 혼재.</t>
+          <t>미국 시장 급등에 따른 주가 상승 기대감. 594억 규모 공급 계약 사실 확인.</t>
         </is>
       </c>
       <c r="U13" t="inlineStr"/>
@@ -1647,11 +1647,11 @@
       </c>
       <c r="W13" t="inlineStr">
         <is>
-          <t>['급등 기대', '외국인 매수', '개잡주']</t>
+          <t>['공급 계약', '유통 물량', '주포']</t>
         </is>
       </c>
       <c r="X13" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="Y13" t="inlineStr">
         <is>
@@ -1660,99 +1660,99 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>069540</t>
+          <t>030960</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>삼성중공업</t>
+          <t>빛과전자</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>15780</v>
+        <v>3985</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>'+0.38%</t>
+          <t>'-1.36%</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>0.06</v>
+        <v>-0.77</v>
       </c>
       <c r="E14" t="n">
-        <v>86</v>
+        <v>63</v>
       </c>
       <c r="F14" t="n">
-        <v>55</v>
+        <v>43</v>
       </c>
       <c r="G14" t="n">
-        <v>213</v>
+        <v>125</v>
       </c>
       <c r="H14" t="n">
-        <v>28.13</v>
+        <v>1.43</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J14" t="n">
-        <v>15720</v>
+        <v>4040</v>
       </c>
       <c r="K14" t="n">
-        <v>15420</v>
+        <v>3925</v>
       </c>
       <c r="L14" t="n">
-        <v>16050</v>
+        <v>4265</v>
       </c>
       <c r="M14" t="n">
-        <v>15320</v>
+        <v>3880</v>
       </c>
       <c r="N14" t="n">
-        <v>28.07</v>
+        <v>2.2</v>
       </c>
       <c r="O14" t="n">
-        <v>34267484925</v>
+        <v>67958265955</v>
       </c>
       <c r="P14" t="n">
-        <v>35350</v>
+        <v>8100</v>
       </c>
       <c r="Q14" t="n">
-        <v>15320</v>
+        <v>592</v>
       </c>
       <c r="R14" t="n">
-        <v>345000</v>
+        <v>-37000</v>
       </c>
       <c r="S14" t="n">
-        <v>35000</v>
+        <v>0</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
-          <t>미국 조선주 강세 속 국내 증시 부진. 증권사 리포트 및 기대감 존재.</t>
+          <t>상승 기대감과 함께 급등 가능성 언급. 외국인 및 프로그램 매수세 확인되나, '개잡주'라는 부정적 표현도 혼재.</t>
         </is>
       </c>
       <c r="U14" t="inlineStr"/>
       <c r="V14" t="n">
-        <v>0.4</v>
+        <v>0</v>
       </c>
       <c r="W14" t="inlineStr">
         <is>
-          <t>['조선주', '증권사리포트', ' 기대']</t>
+          <t>['급등 기대', '외국인 매수', '개잡주']</t>
         </is>
       </c>
       <c r="X14" t="n">
-        <v>17</v>
+        <v>3</v>
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>활성</t>
+          <t>추적</t>
         </is>
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>010140</t>
+          <t>069540</t>
         </is>
       </c>
     </row>
@@ -1763,24 +1763,24 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>7320</v>
+        <v>7300</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>'-1.74%</t>
+          <t>'-2.01%</t>
         </is>
       </c>
       <c r="D15" t="n">
         <v>-0.02</v>
       </c>
       <c r="E15" t="n">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="F15" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="G15" t="n">
-        <v>129</v>
+        <v>143</v>
       </c>
       <c r="H15" t="n">
         <v>25.3</v>
@@ -1806,7 +1806,7 @@
         <v>25.32</v>
       </c>
       <c r="O15" t="n">
-        <v>6954200050</v>
+        <v>7068847170</v>
       </c>
       <c r="P15" t="n">
         <v>17950</v>
@@ -1855,24 +1855,24 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>61100</v>
+        <v>61200</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>'-2.71%</t>
+          <t>'-2.55%</t>
         </is>
       </c>
       <c r="D16" t="n">
         <v>0.21</v>
       </c>
       <c r="E16" t="n">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="F16" t="n">
         <v>30</v>
       </c>
       <c r="G16" t="n">
-        <v>240</v>
+        <v>244</v>
       </c>
       <c r="H16" t="n">
         <v>41.76</v>
@@ -1898,7 +1898,7 @@
         <v>41.55</v>
       </c>
       <c r="O16" t="n">
-        <v>58626011750</v>
+        <v>60393451600</v>
       </c>
       <c r="P16" t="n">
         <v>67300</v>
@@ -1947,24 +1947,24 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>54200</v>
+        <v>54100</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>'-4.41%</t>
+          <t>'-4.59%</t>
         </is>
       </c>
       <c r="D17" t="n">
         <v>-0.2</v>
       </c>
       <c r="E17" t="n">
-        <v>240</v>
+        <v>247</v>
       </c>
       <c r="F17" t="n">
-        <v>166</v>
+        <v>171</v>
       </c>
       <c r="G17" t="n">
-        <v>782</v>
+        <v>789</v>
       </c>
       <c r="H17" t="n">
         <v>22.14</v>
@@ -1990,7 +1990,7 @@
         <v>22.34</v>
       </c>
       <c r="O17" t="n">
-        <v>54946909600</v>
+        <v>56654412600</v>
       </c>
       <c r="P17" t="n">
         <v>139200</v>
@@ -2006,7 +2006,7 @@
       </c>
       <c r="T17" t="inlineStr">
         <is>
-          <t>미국 뉴스케일파워 SMR 원자로 수주 성공 및 실적 개선에 대한 긍정적 분석. 체코 원전 사업 관련 언급도 포함.</t>
+          <t>미국 뉴스케일파워 SMR 원자로 수주 사실 기반 실적 개선 기대. 체코 원전 사업 언급.</t>
         </is>
       </c>
       <c r="U17" t="inlineStr"/>
@@ -2015,7 +2015,7 @@
       </c>
       <c r="W17" t="inlineStr">
         <is>
-          <t>['SMR', '원자로 수주', '실적']</t>
+          <t>['SMR', '뉴스케일파워', '원전']</t>
         </is>
       </c>
       <c r="X17" t="n">
@@ -2039,24 +2039,24 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>11000</v>
+        <v>10980</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>'-5.34%</t>
+          <t>'-5.51%</t>
         </is>
       </c>
       <c r="D18" t="n">
         <v>0.13</v>
       </c>
       <c r="E18" t="n">
-        <v>293</v>
+        <v>305</v>
       </c>
       <c r="F18" t="n">
-        <v>149</v>
+        <v>153</v>
       </c>
       <c r="G18" t="n">
-        <v>926</v>
+        <v>952</v>
       </c>
       <c r="H18" t="n">
         <v>9.73</v>
@@ -2082,7 +2082,7 @@
         <v>9.6</v>
       </c>
       <c r="O18" t="n">
-        <v>40380142540</v>
+        <v>41165156595</v>
       </c>
       <c r="P18" t="n">
         <v>40350</v>
@@ -2098,12 +2098,12 @@
       </c>
       <c r="T18" t="inlineStr">
         <is>
-          <t>윤석열 대통령의 원전, 가덕도 사업 증액 및 공매도 금지 조치가 호재로 작용할 것이라는 기대감. 러시아-우크라이나 재건 사업 수주 가능성에 대한 언급.</t>
+          <t>원전, 가덕도 증액, 공매도 금지 등 정부 정책 수혜 기대감. 재건 사업 참여 가능성 언급.</t>
         </is>
       </c>
       <c r="U18" t="inlineStr"/>
       <c r="V18" t="n">
-        <v>0.3</v>
+        <v>0.4</v>
       </c>
       <c r="W18" t="inlineStr">
         <is>
@@ -2131,11 +2131,11 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>218000</v>
+        <v>218500</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>'-6.03%</t>
+          <t>'-5.82%</t>
         </is>
       </c>
       <c r="D19" t="n">
@@ -2145,10 +2145,10 @@
         <v>800</v>
       </c>
       <c r="F19" t="n">
-        <v>537</v>
+        <v>546</v>
       </c>
       <c r="G19" t="n">
-        <v>1243</v>
+        <v>1278</v>
       </c>
       <c r="H19" t="n">
         <v>46.17</v>
@@ -2174,7 +2174,7 @@
         <v>46.19</v>
       </c>
       <c r="O19" t="n">
-        <v>1801254010750</v>
+        <v>1847580976500</v>
       </c>
       <c r="P19" t="n">
         <v>374500</v>
@@ -2190,7 +2190,7 @@
       </c>
       <c r="T19" t="inlineStr">
         <is>
-          <t>이재용 주주환원 발표 기대감 속 정치적 언급 혼재. 국장 및 개인 매수세 집중.</t>
+          <t>이재용 주주환원 발표 기대감 속, 정치적 언급과 함께 주가 하락에 대한 불만 표출. 개인 매수세 유입 확인.</t>
         </is>
       </c>
       <c r="U19" t="inlineStr"/>
@@ -2199,7 +2199,7 @@
       </c>
       <c r="W19" t="inlineStr">
         <is>
-          <t>['주주환원', '정치', '개인매수']</t>
+          <t>['주주환원', '상속세', '개인매수']</t>
         </is>
       </c>
       <c r="X19" t="n">
@@ -2219,31 +2219,31 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>한화솔루션</t>
+          <t>삼성전자우</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>21750</v>
+        <v>169800</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>'-7.84%</t>
+          <t>'-7.67%</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>-0.63</v>
+        <v>-0.13</v>
       </c>
       <c r="E20" t="n">
-        <v>189</v>
+        <v>50</v>
       </c>
       <c r="F20" t="n">
-        <v>145</v>
+        <v>42</v>
       </c>
       <c r="G20" t="n">
-        <v>441</v>
+        <v>150</v>
       </c>
       <c r="H20" t="n">
-        <v>11.6</v>
+        <v>74.87</v>
       </c>
       <c r="I20" t="inlineStr">
         <is>
@@ -2251,91 +2251,91 @@
         </is>
       </c>
       <c r="J20" t="n">
-        <v>23600</v>
+        <v>183900</v>
       </c>
       <c r="K20" t="n">
-        <v>22650</v>
+        <v>176800</v>
       </c>
       <c r="L20" t="n">
-        <v>22700</v>
+        <v>179000</v>
       </c>
       <c r="M20" t="n">
-        <v>21100</v>
+        <v>168100</v>
       </c>
       <c r="N20" t="n">
-        <v>12.23</v>
+        <v>75</v>
       </c>
       <c r="O20" t="n">
-        <v>64892996050</v>
+        <v>433030218550</v>
       </c>
       <c r="P20" t="n">
-        <v>59300</v>
+        <v>243500</v>
       </c>
       <c r="Q20" t="n">
-        <v>21100</v>
+        <v>71000</v>
       </c>
       <c r="R20" t="n">
-        <v>-580000</v>
+        <v>-416000</v>
       </c>
       <c r="S20" t="n">
-        <v>-192000</v>
+        <v>-18000</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
-          <t>김동원 부회장 주가 누르기 의혹 제기. 태양광 수혜 기대와 대규모 주가 하락.</t>
+          <t>주가 조작 및 증여세 관련 부정적 언급과 함께 시장 대폭락에 대한 우려가 존재. 우선주 소각 및 반등 기대도 일부.</t>
         </is>
       </c>
       <c r="U20" t="inlineStr"/>
       <c r="V20" t="n">
-        <v>0.2</v>
+        <v>0</v>
       </c>
       <c r="W20" t="inlineStr">
         <is>
-          <t>['주가누르기', '태양광', '카터스빌']</t>
+          <t>['주가 조작', '증여세', '우선주 소각']</t>
         </is>
       </c>
       <c r="X20" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>활성</t>
+          <t>추적</t>
         </is>
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>009830</t>
+          <t>005935</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>삼성전자우</t>
+          <t>한화솔루션</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>169100</v>
+        <v>21750</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>'-8.05%</t>
+          <t>'-7.84%</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>-0.13</v>
+        <v>-0.63</v>
       </c>
       <c r="E21" t="n">
-        <v>47</v>
+        <v>194</v>
       </c>
       <c r="F21" t="n">
-        <v>39</v>
+        <v>147</v>
       </c>
       <c r="G21" t="n">
-        <v>145</v>
+        <v>447</v>
       </c>
       <c r="H21" t="n">
-        <v>74.87</v>
+        <v>11.6</v>
       </c>
       <c r="I21" t="inlineStr">
         <is>
@@ -2343,143 +2343,143 @@
         </is>
       </c>
       <c r="J21" t="n">
-        <v>183900</v>
+        <v>23600</v>
       </c>
       <c r="K21" t="n">
-        <v>176800</v>
+        <v>22650</v>
       </c>
       <c r="L21" t="n">
-        <v>179000</v>
+        <v>22700</v>
       </c>
       <c r="M21" t="n">
-        <v>168100</v>
+        <v>21100</v>
       </c>
       <c r="N21" t="n">
-        <v>75</v>
+        <v>12.23</v>
       </c>
       <c r="O21" t="n">
-        <v>422250738500</v>
+        <v>65916494750</v>
       </c>
       <c r="P21" t="n">
-        <v>243500</v>
+        <v>59300</v>
       </c>
       <c r="Q21" t="n">
-        <v>71000</v>
+        <v>21100</v>
       </c>
       <c r="R21" t="n">
-        <v>-416000</v>
+        <v>-580000</v>
       </c>
       <c r="S21" t="n">
-        <v>-18000</v>
+        <v>-192000</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
-          <t>주가 조작 및 증여세 관련 부정적 언급과 함께 시장 대폭락에 대한 우려가 존재. 우선주 소각 및 반등 기대도 일부.</t>
+          <t>김동원 부회장 주가 누르기 의혹 제기. 태양광 수혜 기대와 대규모 주가 하락.</t>
         </is>
       </c>
       <c r="U21" t="inlineStr"/>
       <c r="V21" t="n">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="W21" t="inlineStr">
         <is>
-          <t>['주가 조작', '증여세', '우선주 소각']</t>
+          <t>['주가누르기', '태양광', '카터스빌']</t>
         </is>
       </c>
       <c r="X21" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>추적</t>
+          <t>활성</t>
         </is>
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>005935</t>
+          <t>009830</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>대한광통신</t>
+          <t>SK하이닉스</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>13790</v>
+        <v>1398000</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>'-8.25%</t>
+          <t>'-8.39%</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>-0.2</v>
+        <v>0.06</v>
       </c>
       <c r="E22" t="n">
-        <v>95</v>
+        <v>800</v>
       </c>
       <c r="F22" t="n">
-        <v>53</v>
+        <v>538</v>
       </c>
       <c r="G22" t="n">
-        <v>330</v>
+        <v>1307</v>
       </c>
       <c r="H22" t="n">
-        <v>3.13</v>
+        <v>48.72</v>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J22" t="n">
-        <v>15030</v>
+        <v>1526000</v>
       </c>
       <c r="K22" t="n">
-        <v>14500</v>
+        <v>1444000</v>
       </c>
       <c r="L22" t="n">
-        <v>14570</v>
+        <v>1446000</v>
       </c>
       <c r="M22" t="n">
-        <v>13740</v>
+        <v>1381000</v>
       </c>
       <c r="N22" t="n">
-        <v>3.33</v>
+        <v>48.66</v>
       </c>
       <c r="O22" t="n">
-        <v>34237175265</v>
+        <v>2302273477500</v>
       </c>
       <c r="P22" t="n">
-        <v>31500</v>
+        <v>2987000</v>
       </c>
       <c r="Q22" t="n">
-        <v>1830</v>
+        <v>501000</v>
       </c>
       <c r="R22" t="n">
-        <v>-118000</v>
+        <v>-165000</v>
       </c>
       <c r="S22" t="n">
-        <v>-23000</v>
+        <v>-76000</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
-          <t>미국 광통신주 강세에 따른 기대감. 특허 보유 및 추가 수주 가능성 언급.</t>
+          <t>주가 급락에 대한 불만 표출 및 정치적 요인 언급. 엔비디아 회복세와 함께 단기 대응 필요성 제기.</t>
         </is>
       </c>
       <c r="U22" t="inlineStr"/>
       <c r="V22" t="n">
-        <v>0.3</v>
+        <v>0.2</v>
       </c>
       <c r="W22" t="inlineStr">
         <is>
-          <t>['광통신', '특허', '수주']</t>
+          <t>['주가급락', '단기대응', '엔비디아']</t>
         </is>
       </c>
       <c r="X22" t="n">
-        <v>7</v>
+        <v>21</v>
       </c>
       <c r="Y22" t="inlineStr">
         <is>
@@ -2488,90 +2488,90 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>010170</t>
+          <t>000660</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>SK하이닉스</t>
+          <t>대한광통신</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>1396000</v>
+        <v>13760</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>'-8.52%</t>
+          <t>'-8.45%</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>0.06</v>
+        <v>-0.2</v>
       </c>
       <c r="E23" t="n">
-        <v>800</v>
+        <v>99</v>
       </c>
       <c r="F23" t="n">
-        <v>535</v>
+        <v>54</v>
       </c>
       <c r="G23" t="n">
-        <v>1248</v>
+        <v>357</v>
       </c>
       <c r="H23" t="n">
-        <v>48.72</v>
+        <v>3.13</v>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J23" t="n">
-        <v>1526000</v>
+        <v>15030</v>
       </c>
       <c r="K23" t="n">
-        <v>1444000</v>
+        <v>14500</v>
       </c>
       <c r="L23" t="n">
-        <v>1446000</v>
+        <v>14570</v>
       </c>
       <c r="M23" t="n">
-        <v>1381000</v>
+        <v>13710</v>
       </c>
       <c r="N23" t="n">
-        <v>48.66</v>
+        <v>3.33</v>
       </c>
       <c r="O23" t="n">
-        <v>2239863483500</v>
+        <v>35522194980</v>
       </c>
       <c r="P23" t="n">
-        <v>2987000</v>
+        <v>31500</v>
       </c>
       <c r="Q23" t="n">
-        <v>501000</v>
+        <v>1830</v>
       </c>
       <c r="R23" t="n">
-        <v>-165000</v>
+        <v>-118000</v>
       </c>
       <c r="S23" t="n">
-        <v>-76000</v>
+        <v>-23000</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
-          <t>연이은 주가 하락에 대한 불만. 정치적 언급과 함께 단타 대응 촉구.</t>
+          <t>정부 정책 불신에도 불구하고 광통신, 특허 등 호재 기반 상승 기대. 3만원 전고점 돌파 전망.</t>
         </is>
       </c>
       <c r="U23" t="inlineStr"/>
       <c r="V23" t="n">
-        <v>0.1</v>
+        <v>0.3</v>
       </c>
       <c r="W23" t="inlineStr">
         <is>
-          <t>['주가하락', '단타', '외국인']</t>
+          <t>['광통신', '특허', '호재']</t>
         </is>
       </c>
       <c r="X23" t="n">
-        <v>21</v>
+        <v>7</v>
       </c>
       <c r="Y23" t="inlineStr">
         <is>
@@ -2580,7 +2580,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>000660</t>
+          <t>010170</t>
         </is>
       </c>
     </row>
@@ -2591,24 +2591,24 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>7140</v>
+        <v>7180</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>'-9.62%</t>
+          <t>'-9.11%</t>
         </is>
       </c>
       <c r="D24" t="n">
         <v>-0.03</v>
       </c>
       <c r="E24" t="n">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="F24" t="n">
         <v>28</v>
       </c>
       <c r="G24" t="n">
-        <v>98</v>
+        <v>104</v>
       </c>
       <c r="H24" t="n">
         <v>0.39</v>
@@ -2634,7 +2634,7 @@
         <v>0.42</v>
       </c>
       <c r="O24" t="n">
-        <v>14128300455</v>
+        <v>14217514875</v>
       </c>
       <c r="P24" t="n">
         <v>10300</v>
@@ -2683,24 +2683,24 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>116800</v>
+        <v>116900</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>'-15.48%</t>
+          <t>'-15.41%</t>
         </is>
       </c>
       <c r="D25" t="n">
         <v>-0.26</v>
       </c>
       <c r="E25" t="n">
-        <v>107</v>
+        <v>117</v>
       </c>
       <c r="F25" t="n">
-        <v>70</v>
+        <v>76</v>
       </c>
       <c r="G25" t="n">
-        <v>240</v>
+        <v>288</v>
       </c>
       <c r="H25" t="n">
         <v>14.2</v>
@@ -2726,7 +2726,7 @@
         <v>14.46</v>
       </c>
       <c r="O25" t="n">
-        <v>110737723700</v>
+        <v>112710135800</v>
       </c>
       <c r="P25" t="n">
         <v>198000</v>
@@ -2742,16 +2742,16 @@
       </c>
       <c r="T25" t="inlineStr">
         <is>
-          <t>SK하이닉스 물량 확대 관련 기대감 속 급락. 실적 대비 주가 하락에 대한 불만.</t>
+          <t>급격한 주가 하락에 대한 불만 표출. 실적 기반 상승 기대 속에서 의문 제기.</t>
         </is>
       </c>
       <c r="U25" t="inlineStr"/>
       <c r="V25" t="n">
-        <v>0.4</v>
+        <v>0.2</v>
       </c>
       <c r="W25" t="inlineStr">
         <is>
-          <t>['SK하이닉스', '실적', '기판주']</t>
+          <t>['주가하락', '실적', '반도체']</t>
         </is>
       </c>
       <c r="X25" t="n">
@@ -2775,24 +2775,24 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>13320</v>
+        <v>13340</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>'-21.65%</t>
+          <t>'-21.53%</t>
         </is>
       </c>
       <c r="D26" t="n">
         <v>0.01</v>
       </c>
       <c r="E26" t="n">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="F26" t="n">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="G26" t="n">
-        <v>120</v>
+        <v>123</v>
       </c>
       <c r="H26" t="n">
         <v>0.66</v>
@@ -2818,7 +2818,7 @@
         <v>0.65</v>
       </c>
       <c r="O26" t="n">
-        <v>28718618425</v>
+        <v>29119193755</v>
       </c>
       <c r="P26" t="n">
         <v>28800</v>
@@ -2834,16 +2834,16 @@
       </c>
       <c r="T26" t="inlineStr">
         <is>
-          <t>보호예수 해제 후 급락. 기술적 반등 및 향후 매집 기회 언급.</t>
+          <t>보호예수 물량 해제 후 주가 급락에 대한 실망감 표출. 마이크론 퀠테스트 통과 관련 기술력 언급.</t>
         </is>
       </c>
       <c r="U26" t="inlineStr"/>
       <c r="V26" t="n">
-        <v>0.3</v>
+        <v>0.4</v>
       </c>
       <c r="W26" t="inlineStr">
         <is>
-          <t>['보호예수', '급락', '매집']</t>
+          <t>['보호예수', '퀠테스트', '반도체']</t>
         </is>
       </c>
       <c r="X26" t="n">
@@ -2867,11 +2867,11 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>1842</v>
+        <v>1903</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>'-28.47%</t>
+          <t>'-26.10%</t>
         </is>
       </c>
       <c r="D27" t="n">
@@ -2884,7 +2884,7 @@
         <v>33</v>
       </c>
       <c r="G27" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="H27" t="n">
         <v>4.8</v>
@@ -2910,7 +2910,7 @@
         <v>3.35</v>
       </c>
       <c r="O27" t="n">
-        <v>6307226549</v>
+        <v>6428036791</v>
       </c>
       <c r="P27" t="n">
         <v>5700</v>
@@ -2959,24 +2959,24 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>10500</v>
+        <v>10370</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>'-30.00%</t>
+          <t>'-30.87%</t>
         </is>
       </c>
       <c r="D28" t="n">
         <v>0</v>
       </c>
       <c r="E28" t="n">
-        <v>299</v>
+        <v>308</v>
       </c>
       <c r="F28" t="n">
-        <v>144</v>
+        <v>147</v>
       </c>
       <c r="G28" t="n">
-        <v>500</v>
+        <v>533</v>
       </c>
       <c r="H28" t="n">
         <v>3.05</v>
@@ -3002,7 +3002,7 @@
         <v>0</v>
       </c>
       <c r="O28" t="n">
-        <v>93738263290</v>
+        <v>95579333105</v>
       </c>
       <c r="P28" t="n">
         <v>12700</v>
@@ -3018,16 +3018,16 @@
       </c>
       <c r="T28" t="inlineStr">
         <is>
-          <t>상장 초기 급락 후 반등 기대. 유통물량 적고 높은 당기순이익으로 인한 기대감.</t>
+          <t>상장 초기 급락 후 반등 가능성 언급. 유통 물량 감소 및 당기순이익 기반 상승 기대.</t>
         </is>
       </c>
       <c r="U28" t="inlineStr"/>
       <c r="V28" t="n">
-        <v>0.4</v>
+        <v>0.3</v>
       </c>
       <c r="W28" t="inlineStr">
         <is>
-          <t>['유통물량', '당기순이익', '골프주']</t>
+          <t>['당기순이익', '유통물량', '골프주']</t>
         </is>
       </c>
       <c r="X28" t="n">

--- a/data/trending_integrated_20261030_11.xlsx
+++ b/data/trending_integrated_20261030_11.xlsx
@@ -567,24 +567,24 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>18620</v>
+        <v>18640</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>'+106.89%</t>
+          <t>'+107.11%</t>
         </is>
       </c>
       <c r="D2" t="n">
         <v>0</v>
       </c>
       <c r="E2" t="n">
-        <v>316</v>
+        <v>336</v>
       </c>
       <c r="F2" t="n">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="G2" t="n">
-        <v>422</v>
+        <v>436</v>
       </c>
       <c r="H2" t="n">
         <v>1.98</v>
@@ -610,7 +610,7 @@
         <v>0</v>
       </c>
       <c r="O2" t="n">
-        <v>322858728215</v>
+        <v>337168940235</v>
       </c>
       <c r="P2" t="n">
         <v>21700</v>
@@ -626,7 +626,7 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>단기 급등 후 하락 반복 패턴 지적. 신규 상장주 투자 위험성 및 목표가 제시.</t>
+          <t>신규 상장주로서 높은 변동성을 보이며, 단기적인 등락에 대한 기대와 주의가 공존.</t>
         </is>
       </c>
       <c r="U2" t="inlineStr"/>
@@ -635,7 +635,7 @@
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>['신규상장주', '단기급등', '패턴']</t>
+          <t>['신규상장', '단타', '변동성']</t>
         </is>
       </c>
       <c r="X2" t="n">
@@ -659,18 +659,18 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>2870</v>
+        <v>2890</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>'+17.14%</t>
+          <t>'+17.96%</t>
         </is>
       </c>
       <c r="D3" t="n">
         <v>0.16</v>
       </c>
       <c r="E3" t="n">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="F3" t="n">
         <v>38</v>
@@ -702,7 +702,7 @@
         <v>0.63</v>
       </c>
       <c r="O3" t="n">
-        <v>10876987972</v>
+        <v>11100876135</v>
       </c>
       <c r="P3" t="n">
         <v>3170</v>
@@ -751,24 +751,24 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>19360</v>
+        <v>19200</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>'+16.28%</t>
+          <t>'+15.32%</t>
         </is>
       </c>
       <c r="D4" t="n">
         <v>-0.75</v>
       </c>
       <c r="E4" t="n">
-        <v>79</v>
+        <v>83</v>
       </c>
       <c r="F4" t="n">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="G4" t="n">
-        <v>113</v>
+        <v>122</v>
       </c>
       <c r="H4" t="n">
         <v>3.6</v>
@@ -794,7 +794,7 @@
         <v>4.35</v>
       </c>
       <c r="O4" t="n">
-        <v>85549529695</v>
+        <v>90342710955</v>
       </c>
       <c r="P4" t="n">
         <v>22450</v>
@@ -810,16 +810,16 @@
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>해킹 사태 및 양자 보안법 시행 관련 최대 수혜주로 언급. 기술력과 시장 지배력에 대한 긍정적 평가.</t>
+          <t>양자 관련법 시행 및 보안주로서의 수혜 기대감과 해킹 사태 관련 긍정적 언급이 나타남.</t>
         </is>
       </c>
       <c r="U4" t="inlineStr"/>
       <c r="V4" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>['보안주', '양자 보안', '해킹']</t>
+          <t>['양자보안', '해킹', '보안주']</t>
         </is>
       </c>
       <c r="X4" t="n">
@@ -827,7 +827,7 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>추적</t>
+          <t>활성</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
@@ -843,24 +843,24 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>12680</v>
+        <v>12540</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>'+13.21%</t>
+          <t>'+11.96%</t>
         </is>
       </c>
       <c r="D5" t="n">
         <v>-0.04</v>
       </c>
       <c r="E5" t="n">
-        <v>239</v>
+        <v>243</v>
       </c>
       <c r="F5" t="n">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="G5" t="n">
-        <v>692</v>
+        <v>706</v>
       </c>
       <c r="H5" t="n">
         <v>15.04</v>
@@ -886,7 +886,7 @@
         <v>15.08</v>
       </c>
       <c r="O5" t="n">
-        <v>38811347020</v>
+        <v>39486905045</v>
       </c>
       <c r="P5" t="n">
         <v>18960</v>
@@ -902,7 +902,7 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>세계 최초 희토류 없는 백색 LED 개발 등 기술력 기반의 주가 상승 전망. 10만원 목표가 제시.</t>
+          <t>세계 최초 희토류 없는 백색 LED 개발 및 1위 기업으로서의 기술력과 시장 석권에 대한 강한 긍정 전망.</t>
         </is>
       </c>
       <c r="U5" t="inlineStr"/>
@@ -935,24 +935,24 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>8630</v>
+        <v>8600</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>'+12.08%</t>
+          <t>'+11.69%</t>
         </is>
       </c>
       <c r="D6" t="n">
         <v>0.37</v>
       </c>
       <c r="E6" t="n">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="F6" t="n">
         <v>37</v>
       </c>
       <c r="G6" t="n">
-        <v>110</v>
+        <v>114</v>
       </c>
       <c r="H6" t="n">
         <v>13.29</v>
@@ -978,7 +978,7 @@
         <v>12.92</v>
       </c>
       <c r="O6" t="n">
-        <v>7035178305</v>
+        <v>7109298060</v>
       </c>
       <c r="P6" t="n">
         <v>13670</v>
@@ -1027,24 +1027,24 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>6630</v>
+        <v>6720</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>'+6.25%</t>
+          <t>'+7.69%</t>
         </is>
       </c>
       <c r="D7" t="n">
         <v>0</v>
       </c>
       <c r="E7" t="n">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="F7" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="G7" t="n">
-        <v>120</v>
+        <v>127</v>
       </c>
       <c r="H7" t="n">
         <v>0</v>
@@ -1070,7 +1070,7 @@
         <v>0</v>
       </c>
       <c r="O7" t="n">
-        <v>14196770680</v>
+        <v>15228509320</v>
       </c>
       <c r="P7" t="n">
         <v>16620</v>
@@ -1115,31 +1115,31 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>원익홀딩스</t>
+          <t>루닛</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>29400</v>
+        <v>15610</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>'+4.81%</t>
+          <t>'+4.21%</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>-0.36</v>
+        <v>-0.9</v>
       </c>
       <c r="E8" t="n">
-        <v>56</v>
+        <v>70</v>
       </c>
       <c r="F8" t="n">
-        <v>38</v>
+        <v>54</v>
       </c>
       <c r="G8" t="n">
-        <v>207</v>
+        <v>315</v>
       </c>
       <c r="H8" t="n">
-        <v>4.69</v>
+        <v>7.15</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
@@ -1147,38 +1147,38 @@
         </is>
       </c>
       <c r="J8" t="n">
-        <v>28050</v>
+        <v>14980</v>
       </c>
       <c r="K8" t="n">
-        <v>27850</v>
+        <v>14980</v>
       </c>
       <c r="L8" t="n">
-        <v>30400</v>
+        <v>16150</v>
       </c>
       <c r="M8" t="n">
-        <v>27650</v>
+        <v>14610</v>
       </c>
       <c r="N8" t="n">
-        <v>5.05</v>
+        <v>8.050000000000001</v>
       </c>
       <c r="O8" t="n">
-        <v>104256380600</v>
+        <v>42202684580</v>
       </c>
       <c r="P8" t="n">
-        <v>50600</v>
+        <v>49800</v>
       </c>
       <c r="Q8" t="n">
-        <v>13210</v>
+        <v>8180</v>
       </c>
       <c r="R8" t="n">
-        <v>-45000</v>
+        <v>109000</v>
       </c>
       <c r="S8" t="n">
-        <v>95000</v>
+        <v>168000</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>로봇 관련 기대감 속 3만원 돌파 시도. 정밀 엑추에이터 시장 진입 뉴스 확인.</t>
+          <t>유방암 위험 예측 솔루션 FDA 승인 신청 및 AI 신약개발 기대감. 5,000억 원 가치 평가.</t>
         </is>
       </c>
       <c r="U8" t="inlineStr"/>
@@ -1187,11 +1187,11 @@
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>['로봇', '엑추에이터', '반도체']</t>
+          <t>['AI 신약개발', 'FDA 승인', '암 진단']</t>
         </is>
       </c>
       <c r="X8" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="Y8" t="inlineStr">
         <is>
@@ -1200,38 +1200,38 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>030530</t>
+          <t>328130</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>루닛</t>
+          <t>원익홀딩스</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>15630</v>
+        <v>29200</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>'+4.34%</t>
+          <t>'+4.10%</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>-0.9</v>
+        <v>-0.36</v>
       </c>
       <c r="E9" t="n">
-        <v>67</v>
+        <v>58</v>
       </c>
       <c r="F9" t="n">
-        <v>52</v>
+        <v>39</v>
       </c>
       <c r="G9" t="n">
-        <v>263</v>
+        <v>214</v>
       </c>
       <c r="H9" t="n">
-        <v>7.15</v>
+        <v>4.69</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
@@ -1239,38 +1239,38 @@
         </is>
       </c>
       <c r="J9" t="n">
-        <v>14980</v>
+        <v>28050</v>
       </c>
       <c r="K9" t="n">
-        <v>14980</v>
+        <v>27850</v>
       </c>
       <c r="L9" t="n">
-        <v>16150</v>
+        <v>30400</v>
       </c>
       <c r="M9" t="n">
-        <v>14610</v>
+        <v>27650</v>
       </c>
       <c r="N9" t="n">
-        <v>8.050000000000001</v>
+        <v>5.05</v>
       </c>
       <c r="O9" t="n">
-        <v>41564327910</v>
+        <v>105660197750</v>
       </c>
       <c r="P9" t="n">
-        <v>49800</v>
+        <v>50600</v>
       </c>
       <c r="Q9" t="n">
-        <v>8180</v>
+        <v>13210</v>
       </c>
       <c r="R9" t="n">
-        <v>109000</v>
+        <v>-45000</v>
       </c>
       <c r="S9" t="n">
-        <v>168000</v>
+        <v>95000</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>유방암 위험 예측 솔루션 FDA 승인 신청 및 AI 신약개발 기대감. 5,000억 원 가치 평가.</t>
+          <t>로봇 관련 기대감 속 3만원 돌파 시도. 정밀 엑추에이터 시장 진입 뉴스 확인.</t>
         </is>
       </c>
       <c r="U9" t="inlineStr"/>
@@ -1279,11 +1279,11 @@
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>['AI 신약개발', 'FDA 승인', '암 진단']</t>
+          <t>['로봇', '엑추에이터', '반도체']</t>
         </is>
       </c>
       <c r="X9" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="Y9" t="inlineStr">
         <is>
@@ -1292,182 +1292,182 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>328130</t>
+          <t>030530</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>서울바이오시스</t>
+          <t>한화비전</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>8840</v>
+        <v>50300</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>'+3.03%</t>
+          <t>'+2.44%</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>0.01</v>
+        <v>-0.82</v>
       </c>
       <c r="E10" t="n">
-        <v>78</v>
+        <v>90</v>
       </c>
       <c r="F10" t="n">
-        <v>48</v>
+        <v>58</v>
       </c>
       <c r="G10" t="n">
-        <v>209</v>
+        <v>187</v>
       </c>
       <c r="H10" t="n">
-        <v>2.67</v>
+        <v>23.82</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J10" t="n">
-        <v>8580</v>
+        <v>49100</v>
       </c>
       <c r="K10" t="n">
-        <v>11090</v>
+        <v>49450</v>
       </c>
       <c r="L10" t="n">
-        <v>11150</v>
+        <v>52000</v>
       </c>
       <c r="M10" t="n">
-        <v>8400</v>
+        <v>48050</v>
       </c>
       <c r="N10" t="n">
-        <v>2.66</v>
+        <v>24.64</v>
       </c>
       <c r="O10" t="n">
-        <v>25413234625</v>
+        <v>47096527650</v>
       </c>
       <c r="P10" t="n">
-        <v>19270</v>
+        <v>97900</v>
       </c>
       <c r="Q10" t="n">
-        <v>2135</v>
+        <v>30950</v>
       </c>
       <c r="R10" t="n">
-        <v>-363000</v>
+        <v>-37000</v>
       </c>
       <c r="S10" t="n">
-        <v>-2000</v>
+        <v>55000</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>서울반도체와 동반 상승 기대. 광통신 사업 연계 및 매출 조 단위 전망.</t>
+          <t>최대 실적 발표 후, TC본더 매출 본격화 및 사이버 보안 수혜 기대감. 공매도 청산 및 5만/6만 비전 탈환 목표.</t>
         </is>
       </c>
       <c r="U10" t="inlineStr"/>
       <c r="V10" t="n">
-        <v>0</v>
+        <v>0.4</v>
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>['광통신', '신기술', '매출']</t>
+          <t>['실적', 'TC본더', '공매도']</t>
         </is>
       </c>
       <c r="X10" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>추적</t>
+          <t>활성</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>092190</t>
+          <t>489790</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>한화비전</t>
+          <t>서울바이오시스</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>50300</v>
+        <v>8780</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>'+2.44%</t>
+          <t>'+2.33%</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>-0.82</v>
+        <v>0.01</v>
       </c>
       <c r="E11" t="n">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="F11" t="n">
-        <v>58</v>
+        <v>50</v>
       </c>
       <c r="G11" t="n">
-        <v>188</v>
+        <v>211</v>
       </c>
       <c r="H11" t="n">
-        <v>23.82</v>
+        <v>2.67</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J11" t="n">
-        <v>49100</v>
+        <v>8580</v>
       </c>
       <c r="K11" t="n">
-        <v>49450</v>
+        <v>11090</v>
       </c>
       <c r="L11" t="n">
-        <v>52000</v>
+        <v>11150</v>
       </c>
       <c r="M11" t="n">
-        <v>48050</v>
+        <v>8400</v>
       </c>
       <c r="N11" t="n">
-        <v>24.64</v>
+        <v>2.66</v>
       </c>
       <c r="O11" t="n">
-        <v>46217872800</v>
+        <v>25581552770</v>
       </c>
       <c r="P11" t="n">
-        <v>97900</v>
+        <v>19270</v>
       </c>
       <c r="Q11" t="n">
-        <v>30950</v>
+        <v>2135</v>
       </c>
       <c r="R11" t="n">
-        <v>-37000</v>
+        <v>-363000</v>
       </c>
       <c r="S11" t="n">
-        <v>55000</v>
+        <v>-2000</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>최대 실적 발표 후, TC본더 매출 본격화 및 사이버 보안 수혜 기대감. 공매도 청산 및 5만/6만 비전 탈환 목표.</t>
+          <t>서울바이오시스의 영업이익 및 기술력 비교, 광통신 사업 가세 전망. 환기 해제 시 기관 매수 기대.</t>
         </is>
       </c>
       <c r="U11" t="inlineStr"/>
       <c r="V11" t="n">
-        <v>0.4</v>
+        <v>0.2</v>
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>['실적', 'TC본더', '공매도']</t>
+          <t>['영업이익', '광통신', '환기']</t>
         </is>
       </c>
       <c r="X11" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Y11" t="inlineStr">
         <is>
@@ -1476,191 +1476,191 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>489790</t>
+          <t>092190</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>삼성중공업</t>
+          <t>양지사</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>15760</v>
+        <v>6730</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>'+0.25%</t>
+          <t>'+1.36%</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>0.06</v>
+        <v>-0.05</v>
       </c>
       <c r="E12" t="n">
-        <v>90</v>
+        <v>59</v>
       </c>
       <c r="F12" t="n">
-        <v>56</v>
+        <v>33</v>
       </c>
       <c r="G12" t="n">
-        <v>220</v>
+        <v>65</v>
       </c>
       <c r="H12" t="n">
-        <v>28.13</v>
+        <v>0.85</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J12" t="n">
-        <v>15720</v>
+        <v>6640</v>
       </c>
       <c r="K12" t="n">
-        <v>15420</v>
+        <v>7210</v>
       </c>
       <c r="L12" t="n">
-        <v>16050</v>
+        <v>7500</v>
       </c>
       <c r="M12" t="n">
-        <v>15320</v>
+        <v>6580</v>
       </c>
       <c r="N12" t="n">
-        <v>28.07</v>
+        <v>0.9</v>
       </c>
       <c r="O12" t="n">
-        <v>35175586345</v>
+        <v>29527277485</v>
       </c>
       <c r="P12" t="n">
-        <v>35350</v>
+        <v>9820</v>
       </c>
       <c r="Q12" t="n">
-        <v>15320</v>
+        <v>4000</v>
       </c>
       <c r="R12" t="n">
-        <v>345000</v>
+        <v>-63000</v>
       </c>
       <c r="S12" t="n">
-        <v>35000</v>
+        <v>0</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>미국 조선주 강세 속 국내 증시 부진. 증권사 리포트 및 기대감 존재.</t>
+          <t>미국 시장 급등에 따른 주가 상승 기대감. 594억 규모 공급 계약 사실 확인.</t>
         </is>
       </c>
       <c r="U12" t="inlineStr"/>
       <c r="V12" t="n">
-        <v>0.4</v>
+        <v>0</v>
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>['조선주', '증권사리포트', ' 기대']</t>
+          <t>['공급 계약', '유통 물량', '주포']</t>
         </is>
       </c>
       <c r="X12" t="n">
-        <v>17</v>
+        <v>1</v>
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>활성</t>
+          <t>추적</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>010140</t>
+          <t>030960</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>양지사</t>
+          <t>삼성중공업</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>6620</v>
+        <v>15760</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>'-0.30%</t>
+          <t>'+0.25%</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>-0.05</v>
+        <v>0.06</v>
       </c>
       <c r="E13" t="n">
+        <v>91</v>
+      </c>
+      <c r="F13" t="n">
         <v>56</v>
       </c>
-      <c r="F13" t="n">
-        <v>32</v>
-      </c>
       <c r="G13" t="n">
-        <v>59</v>
+        <v>223</v>
       </c>
       <c r="H13" t="n">
-        <v>0.85</v>
+        <v>28.13</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J13" t="n">
-        <v>6640</v>
+        <v>15720</v>
       </c>
       <c r="K13" t="n">
-        <v>7210</v>
+        <v>15420</v>
       </c>
       <c r="L13" t="n">
-        <v>7500</v>
+        <v>16050</v>
       </c>
       <c r="M13" t="n">
-        <v>6600</v>
+        <v>15320</v>
       </c>
       <c r="N13" t="n">
-        <v>0.9</v>
+        <v>28.07</v>
       </c>
       <c r="O13" t="n">
-        <v>29227064255</v>
+        <v>36326399890</v>
       </c>
       <c r="P13" t="n">
-        <v>9820</v>
+        <v>35350</v>
       </c>
       <c r="Q13" t="n">
-        <v>4000</v>
+        <v>15320</v>
       </c>
       <c r="R13" t="n">
-        <v>-63000</v>
+        <v>345000</v>
       </c>
       <c r="S13" t="n">
-        <v>0</v>
+        <v>35000</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>미국 시장 급등에 따른 주가 상승 기대감. 594억 규모 공급 계약 사실 확인.</t>
+          <t>미국 조선주 강세 속 국내 증시 부진. 증권사 리포트 및 기대감 존재.</t>
         </is>
       </c>
       <c r="U13" t="inlineStr"/>
       <c r="V13" t="n">
-        <v>0</v>
+        <v>0.4</v>
       </c>
       <c r="W13" t="inlineStr">
         <is>
-          <t>['공급 계약', '유통 물량', '주포']</t>
+          <t>['조선주', '증권사리포트', ' 기대']</t>
         </is>
       </c>
       <c r="X13" t="n">
-        <v>1</v>
+        <v>17</v>
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>추적</t>
+          <t>활성</t>
         </is>
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>030960</t>
+          <t>010140</t>
         </is>
       </c>
     </row>
@@ -1688,7 +1688,7 @@
         <v>43</v>
       </c>
       <c r="G14" t="n">
-        <v>125</v>
+        <v>140</v>
       </c>
       <c r="H14" t="n">
         <v>1.43</v>
@@ -1714,7 +1714,7 @@
         <v>2.2</v>
       </c>
       <c r="O14" t="n">
-        <v>67958265955</v>
+        <v>69905806231</v>
       </c>
       <c r="P14" t="n">
         <v>8100</v>
@@ -1763,24 +1763,24 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>7300</v>
+        <v>7290</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>'-2.01%</t>
+          <t>'-2.15%</t>
         </is>
       </c>
       <c r="D15" t="n">
         <v>-0.02</v>
       </c>
       <c r="E15" t="n">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="F15" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="G15" t="n">
-        <v>143</v>
+        <v>164</v>
       </c>
       <c r="H15" t="n">
         <v>25.3</v>
@@ -1806,7 +1806,7 @@
         <v>25.32</v>
       </c>
       <c r="O15" t="n">
-        <v>7068847170</v>
+        <v>7330287700</v>
       </c>
       <c r="P15" t="n">
         <v>17950</v>
@@ -1855,21 +1855,21 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>61200</v>
+        <v>61000</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>'-2.55%</t>
+          <t>'-2.87%</t>
         </is>
       </c>
       <c r="D16" t="n">
         <v>0.21</v>
       </c>
       <c r="E16" t="n">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="F16" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="G16" t="n">
         <v>244</v>
@@ -1898,7 +1898,7 @@
         <v>41.55</v>
       </c>
       <c r="O16" t="n">
-        <v>60393451600</v>
+        <v>62137439350</v>
       </c>
       <c r="P16" t="n">
         <v>67300</v>
@@ -1947,24 +1947,24 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>54100</v>
+        <v>54000</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>'-4.59%</t>
+          <t>'-4.76%</t>
         </is>
       </c>
       <c r="D17" t="n">
         <v>-0.2</v>
       </c>
       <c r="E17" t="n">
-        <v>247</v>
+        <v>249</v>
       </c>
       <c r="F17" t="n">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="G17" t="n">
-        <v>789</v>
+        <v>833</v>
       </c>
       <c r="H17" t="n">
         <v>22.14</v>
@@ -1990,7 +1990,7 @@
         <v>22.34</v>
       </c>
       <c r="O17" t="n">
-        <v>56654412600</v>
+        <v>58294947750</v>
       </c>
       <c r="P17" t="n">
         <v>139200</v>
@@ -2006,16 +2006,16 @@
       </c>
       <c r="T17" t="inlineStr">
         <is>
-          <t>미국 뉴스케일파워 SMR 원자로 수주 사실 기반 실적 개선 기대. 체코 원전 사업 언급.</t>
+          <t>미국 뉴스케일파워 SMR 원자로 수주 및 실적 개선에 대한 긍정적 언급이 주를 이룸.</t>
         </is>
       </c>
       <c r="U17" t="inlineStr"/>
       <c r="V17" t="n">
-        <v>0.5</v>
+        <v>0.6</v>
       </c>
       <c r="W17" t="inlineStr">
         <is>
-          <t>['SMR', '뉴스케일파워', '원전']</t>
+          <t>['SMR', '뉴스케일파워', '수주']</t>
         </is>
       </c>
       <c r="X17" t="n">
@@ -2039,24 +2039,24 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>10980</v>
+        <v>10930</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>'-5.51%</t>
+          <t>'-5.94%</t>
         </is>
       </c>
       <c r="D18" t="n">
         <v>0.13</v>
       </c>
       <c r="E18" t="n">
-        <v>305</v>
+        <v>316</v>
       </c>
       <c r="F18" t="n">
-        <v>153</v>
+        <v>156</v>
       </c>
       <c r="G18" t="n">
-        <v>952</v>
+        <v>1011</v>
       </c>
       <c r="H18" t="n">
         <v>9.73</v>
@@ -2082,7 +2082,7 @@
         <v>9.6</v>
       </c>
       <c r="O18" t="n">
-        <v>41165156595</v>
+        <v>42168695555</v>
       </c>
       <c r="P18" t="n">
         <v>40350</v>
@@ -2098,12 +2098,12 @@
       </c>
       <c r="T18" t="inlineStr">
         <is>
-          <t>원전, 가덕도 증액, 공매도 금지 등 정부 정책 수혜 기대감. 재건 사업 참여 가능성 언급.</t>
+          <t>원전, 가덕도 증액, 공매도 금지 등 호재성 뉴스가 언급되나, 정부 비판과 함께 나타남.</t>
         </is>
       </c>
       <c r="U18" t="inlineStr"/>
       <c r="V18" t="n">
-        <v>0.4</v>
+        <v>0.3</v>
       </c>
       <c r="W18" t="inlineStr">
         <is>
@@ -2131,11 +2131,11 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>218500</v>
+        <v>217750</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>'-5.82%</t>
+          <t>'-6.14%</t>
         </is>
       </c>
       <c r="D19" t="n">
@@ -2145,10 +2145,10 @@
         <v>800</v>
       </c>
       <c r="F19" t="n">
-        <v>546</v>
+        <v>554</v>
       </c>
       <c r="G19" t="n">
-        <v>1278</v>
+        <v>1317</v>
       </c>
       <c r="H19" t="n">
         <v>46.17</v>
@@ -2174,7 +2174,7 @@
         <v>46.19</v>
       </c>
       <c r="O19" t="n">
-        <v>1847580976500</v>
+        <v>1901923387000</v>
       </c>
       <c r="P19" t="n">
         <v>374500</v>
@@ -2190,7 +2190,7 @@
       </c>
       <c r="T19" t="inlineStr">
         <is>
-          <t>이재용 주주환원 발표 기대감 속, 정치적 언급과 함께 주가 하락에 대한 불만 표출. 개인 매수세 유입 확인.</t>
+          <t>이재용 관련 언급과 주주환원 기대가 있으나, 정치적 비난이 주를 이룸.</t>
         </is>
       </c>
       <c r="U19" t="inlineStr"/>
@@ -2199,7 +2199,7 @@
       </c>
       <c r="W19" t="inlineStr">
         <is>
-          <t>['주주환원', '상속세', '개인매수']</t>
+          <t>['주주환원', '이재용', '정치']</t>
         </is>
       </c>
       <c r="X19" t="n">
@@ -2219,31 +2219,31 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>삼성전자우</t>
+          <t>한화솔루션</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>169800</v>
+        <v>21800</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>'-7.67%</t>
+          <t>'-7.63%</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>-0.13</v>
+        <v>-0.63</v>
       </c>
       <c r="E20" t="n">
-        <v>50</v>
+        <v>198</v>
       </c>
       <c r="F20" t="n">
-        <v>42</v>
+        <v>149</v>
       </c>
       <c r="G20" t="n">
-        <v>150</v>
+        <v>463</v>
       </c>
       <c r="H20" t="n">
-        <v>74.87</v>
+        <v>11.6</v>
       </c>
       <c r="I20" t="inlineStr">
         <is>
@@ -2251,91 +2251,91 @@
         </is>
       </c>
       <c r="J20" t="n">
-        <v>183900</v>
+        <v>23600</v>
       </c>
       <c r="K20" t="n">
-        <v>176800</v>
+        <v>22650</v>
       </c>
       <c r="L20" t="n">
-        <v>179000</v>
+        <v>22700</v>
       </c>
       <c r="M20" t="n">
-        <v>168100</v>
+        <v>21100</v>
       </c>
       <c r="N20" t="n">
-        <v>75</v>
+        <v>12.23</v>
       </c>
       <c r="O20" t="n">
-        <v>433030218550</v>
+        <v>66935903625</v>
       </c>
       <c r="P20" t="n">
-        <v>243500</v>
+        <v>59300</v>
       </c>
       <c r="Q20" t="n">
-        <v>71000</v>
+        <v>21100</v>
       </c>
       <c r="R20" t="n">
-        <v>-416000</v>
+        <v>-580000</v>
       </c>
       <c r="S20" t="n">
-        <v>-18000</v>
+        <v>-192000</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
-          <t>주가 조작 및 증여세 관련 부정적 언급과 함께 시장 대폭락에 대한 우려가 존재. 우선주 소각 및 반등 기대도 일부.</t>
+          <t>태양광 물량 완판 뉴스가 있으나, 주가 누르기 의혹과 급락으로 인한 부정적 여론이 지배적.</t>
         </is>
       </c>
       <c r="U20" t="inlineStr"/>
       <c r="V20" t="n">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="W20" t="inlineStr">
         <is>
-          <t>['주가 조작', '증여세', '우선주 소각']</t>
+          <t>['태양광', '주가 누르기', '급락']</t>
         </is>
       </c>
       <c r="X20" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>추적</t>
+          <t>활성</t>
         </is>
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>005935</t>
+          <t>009830</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>한화솔루션</t>
+          <t>삼성전자우</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>21750</v>
+        <v>169800</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>'-7.84%</t>
+          <t>'-7.67%</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>-0.63</v>
+        <v>-0.13</v>
       </c>
       <c r="E21" t="n">
-        <v>194</v>
+        <v>49</v>
       </c>
       <c r="F21" t="n">
-        <v>147</v>
+        <v>41</v>
       </c>
       <c r="G21" t="n">
-        <v>447</v>
+        <v>161</v>
       </c>
       <c r="H21" t="n">
-        <v>11.6</v>
+        <v>74.87</v>
       </c>
       <c r="I21" t="inlineStr">
         <is>
@@ -2343,152 +2343,152 @@
         </is>
       </c>
       <c r="J21" t="n">
-        <v>23600</v>
+        <v>183900</v>
       </c>
       <c r="K21" t="n">
-        <v>22650</v>
+        <v>176800</v>
       </c>
       <c r="L21" t="n">
-        <v>22700</v>
+        <v>179000</v>
       </c>
       <c r="M21" t="n">
-        <v>21100</v>
+        <v>168100</v>
       </c>
       <c r="N21" t="n">
-        <v>12.23</v>
+        <v>75</v>
       </c>
       <c r="O21" t="n">
-        <v>65916494750</v>
+        <v>442323344100</v>
       </c>
       <c r="P21" t="n">
-        <v>59300</v>
+        <v>243500</v>
       </c>
       <c r="Q21" t="n">
-        <v>21100</v>
+        <v>71000</v>
       </c>
       <c r="R21" t="n">
-        <v>-580000</v>
+        <v>-416000</v>
       </c>
       <c r="S21" t="n">
-        <v>-192000</v>
+        <v>-18000</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
-          <t>김동원 부회장 주가 누르기 의혹 제기. 태양광 수혜 기대와 대규모 주가 하락.</t>
+          <t>주가 조작 및 증여세 관련 부정적 언급과 함께 시장 대폭락에 대한 우려가 존재. 우선주 소각 및 반등 기대도 일부.</t>
         </is>
       </c>
       <c r="U21" t="inlineStr"/>
       <c r="V21" t="n">
-        <v>0.2</v>
+        <v>0</v>
       </c>
       <c r="W21" t="inlineStr">
         <is>
-          <t>['주가누르기', '태양광', '카터스빌']</t>
+          <t>['주가 조작', '증여세', '우선주 소각']</t>
         </is>
       </c>
       <c r="X21" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>활성</t>
+          <t>추적</t>
         </is>
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>009830</t>
+          <t>005935</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>SK하이닉스</t>
+          <t>서산</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>1398000</v>
+        <v>7240</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>'-8.39%</t>
+          <t>'-8.35%</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>0.06</v>
+        <v>-0.03</v>
       </c>
       <c r="E22" t="n">
-        <v>800</v>
+        <v>59</v>
       </c>
       <c r="F22" t="n">
-        <v>538</v>
+        <v>30</v>
       </c>
       <c r="G22" t="n">
-        <v>1307</v>
+        <v>106</v>
       </c>
       <c r="H22" t="n">
-        <v>48.72</v>
+        <v>0.39</v>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J22" t="n">
-        <v>1526000</v>
+        <v>7900</v>
       </c>
       <c r="K22" t="n">
-        <v>1444000</v>
+        <v>7790</v>
       </c>
       <c r="L22" t="n">
-        <v>1446000</v>
+        <v>8130</v>
       </c>
       <c r="M22" t="n">
-        <v>1381000</v>
+        <v>7100</v>
       </c>
       <c r="N22" t="n">
-        <v>48.66</v>
+        <v>0.42</v>
       </c>
       <c r="O22" t="n">
-        <v>2302273477500</v>
+        <v>14324965455</v>
       </c>
       <c r="P22" t="n">
-        <v>2987000</v>
+        <v>10300</v>
       </c>
       <c r="Q22" t="n">
-        <v>501000</v>
+        <v>952</v>
       </c>
       <c r="R22" t="n">
-        <v>-165000</v>
+        <v>1000</v>
       </c>
       <c r="S22" t="n">
-        <v>-76000</v>
+        <v>0</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
-          <t>주가 급락에 대한 불만 표출 및 정치적 요인 언급. 엔비디아 회복세와 함께 단기 대응 필요성 제기.</t>
+          <t>서산, 594억 공급 계약 재료를 바탕으로 한 긍정적 전망. 다만, 시장 전체 하락세 및 개미 투자자 심리 불안감 존재.</t>
         </is>
       </c>
       <c r="U22" t="inlineStr"/>
       <c r="V22" t="n">
-        <v>0.2</v>
+        <v>0</v>
       </c>
       <c r="W22" t="inlineStr">
         <is>
-          <t>['주가급락', '단기대응', '엔비디아']</t>
+          <t>['공급계약', '재료', '주가']</t>
         </is>
       </c>
       <c r="X22" t="n">
-        <v>21</v>
+        <v>2</v>
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>활성</t>
+          <t>추적</t>
         </is>
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>000660</t>
+          <t>079650</t>
         </is>
       </c>
     </row>
@@ -2499,24 +2499,24 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>13760</v>
+        <v>13720</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>'-8.45%</t>
+          <t>'-8.72%</t>
         </is>
       </c>
       <c r="D23" t="n">
         <v>-0.2</v>
       </c>
       <c r="E23" t="n">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="F23" t="n">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="G23" t="n">
-        <v>357</v>
+        <v>364</v>
       </c>
       <c r="H23" t="n">
         <v>3.13</v>
@@ -2542,7 +2542,7 @@
         <v>3.33</v>
       </c>
       <c r="O23" t="n">
-        <v>35522194980</v>
+        <v>36499677200</v>
       </c>
       <c r="P23" t="n">
         <v>31500</v>
@@ -2587,92 +2587,92 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>서산</t>
+          <t>SK하이닉스</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>7180</v>
+        <v>1393000</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>'-9.11%</t>
+          <t>'-8.72%</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>-0.03</v>
+        <v>0.06</v>
       </c>
       <c r="E24" t="n">
-        <v>57</v>
+        <v>800</v>
       </c>
       <c r="F24" t="n">
-        <v>28</v>
+        <v>532</v>
       </c>
       <c r="G24" t="n">
-        <v>104</v>
+        <v>1315</v>
       </c>
       <c r="H24" t="n">
-        <v>0.39</v>
+        <v>48.72</v>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J24" t="n">
-        <v>7900</v>
+        <v>1526000</v>
       </c>
       <c r="K24" t="n">
-        <v>7790</v>
+        <v>1444000</v>
       </c>
       <c r="L24" t="n">
-        <v>8130</v>
+        <v>1446000</v>
       </c>
       <c r="M24" t="n">
-        <v>7100</v>
+        <v>1381000</v>
       </c>
       <c r="N24" t="n">
-        <v>0.42</v>
+        <v>48.66</v>
       </c>
       <c r="O24" t="n">
-        <v>14217514875</v>
+        <v>2356489420000</v>
       </c>
       <c r="P24" t="n">
-        <v>10300</v>
+        <v>2987000</v>
       </c>
       <c r="Q24" t="n">
-        <v>952</v>
+        <v>501000</v>
       </c>
       <c r="R24" t="n">
-        <v>1000</v>
+        <v>-165000</v>
       </c>
       <c r="S24" t="n">
-        <v>0</v>
+        <v>-76000</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
-          <t>서산, 594억 공급 계약 재료를 바탕으로 한 긍정적 전망. 다만, 시장 전체 하락세 및 개미 투자자 심리 불안감 존재.</t>
+          <t>엔비디아 회복세 언급에도 불구하고, 정치적 요인으로 인한 증시 폭락에 대한 불만이 압도적.</t>
         </is>
       </c>
       <c r="U24" t="inlineStr"/>
       <c r="V24" t="n">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="W24" t="inlineStr">
         <is>
-          <t>['공급계약', '재료', '주가']</t>
+          <t>['엔비디아', '폭락', '정치']</t>
         </is>
       </c>
       <c r="X24" t="n">
-        <v>2</v>
+        <v>21</v>
       </c>
       <c r="Y24" t="inlineStr">
         <is>
-          <t>추적</t>
+          <t>활성</t>
         </is>
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>079650</t>
+          <t>000660</t>
         </is>
       </c>
     </row>
@@ -2683,24 +2683,24 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>116900</v>
+        <v>116500</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>'-15.41%</t>
+          <t>'-15.70%</t>
         </is>
       </c>
       <c r="D25" t="n">
         <v>-0.26</v>
       </c>
       <c r="E25" t="n">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="F25" t="n">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="G25" t="n">
-        <v>288</v>
+        <v>300</v>
       </c>
       <c r="H25" t="n">
         <v>14.2</v>
@@ -2726,7 +2726,7 @@
         <v>14.46</v>
       </c>
       <c r="O25" t="n">
-        <v>112710135800</v>
+        <v>116595625300</v>
       </c>
       <c r="P25" t="n">
         <v>198000</v>
@@ -2742,7 +2742,7 @@
       </c>
       <c r="T25" t="inlineStr">
         <is>
-          <t>급격한 주가 하락에 대한 불만 표출. 실적 기반 상승 기대 속에서 의문 제기.</t>
+          <t>실적 호조 기대에도 불구하고 급락하는 주가에 대한 불만과 의아함이 나타남.</t>
         </is>
       </c>
       <c r="U25" t="inlineStr"/>
@@ -2751,7 +2751,7 @@
       </c>
       <c r="W25" t="inlineStr">
         <is>
-          <t>['주가하락', '실적', '반도체']</t>
+          <t>['실적', '기판주', '급락']</t>
         </is>
       </c>
       <c r="X25" t="n">
@@ -2775,24 +2775,24 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>13340</v>
+        <v>13240</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>'-21.53%</t>
+          <t>'-22.12%</t>
         </is>
       </c>
       <c r="D26" t="n">
         <v>0.01</v>
       </c>
       <c r="E26" t="n">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="F26" t="n">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="G26" t="n">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="H26" t="n">
         <v>0.66</v>
@@ -2818,7 +2818,7 @@
         <v>0.65</v>
       </c>
       <c r="O26" t="n">
-        <v>29119193755</v>
+        <v>29526471460</v>
       </c>
       <c r="P26" t="n">
         <v>28800</v>
@@ -2834,16 +2834,16 @@
       </c>
       <c r="T26" t="inlineStr">
         <is>
-          <t>보호예수 물량 해제 후 주가 급락에 대한 실망감 표출. 마이크론 퀠테스트 통과 관련 기술력 언급.</t>
+          <t>보호예수 물량 해제 이후 주가 변동성 발생. 마이크론 퀠테스트 통과 종목에 대한 매수세 언급.</t>
         </is>
       </c>
       <c r="U26" t="inlineStr"/>
       <c r="V26" t="n">
-        <v>0.4</v>
+        <v>0.1</v>
       </c>
       <c r="W26" t="inlineStr">
         <is>
-          <t>['보호예수', '퀠테스트', '반도체']</t>
+          <t>['보호예수', '퀠테스트', '매집']</t>
         </is>
       </c>
       <c r="X26" t="n">
@@ -2867,11 +2867,11 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>1903</v>
+        <v>1851</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>'-26.10%</t>
+          <t>'-28.12%</t>
         </is>
       </c>
       <c r="D27" t="n">
@@ -2884,7 +2884,7 @@
         <v>33</v>
       </c>
       <c r="G27" t="n">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="H27" t="n">
         <v>4.8</v>
@@ -2910,7 +2910,7 @@
         <v>3.35</v>
       </c>
       <c r="O27" t="n">
-        <v>6428036791</v>
+        <v>6517787721</v>
       </c>
       <c r="P27" t="n">
         <v>5700</v>
@@ -2959,24 +2959,24 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>10370</v>
+        <v>10290</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>'-30.87%</t>
+          <t>'-31.40%</t>
         </is>
       </c>
       <c r="D28" t="n">
         <v>0</v>
       </c>
       <c r="E28" t="n">
-        <v>308</v>
+        <v>311</v>
       </c>
       <c r="F28" t="n">
         <v>147</v>
       </c>
       <c r="G28" t="n">
-        <v>533</v>
+        <v>545</v>
       </c>
       <c r="H28" t="n">
         <v>3.05</v>
@@ -3002,7 +3002,7 @@
         <v>0</v>
       </c>
       <c r="O28" t="n">
-        <v>95579333105</v>
+        <v>96671808405</v>
       </c>
       <c r="P28" t="n">
         <v>12700</v>
@@ -3018,16 +3018,16 @@
       </c>
       <c r="T28" t="inlineStr">
         <is>
-          <t>상장 초기 급락 후 반등 가능성 언급. 유통 물량 감소 및 당기순이익 기반 상승 기대.</t>
+          <t>신규 상장주로서 상한가 및 급등 기대감이 높으나, 주가 하락에 대한 우려도 존재.</t>
         </is>
       </c>
       <c r="U28" t="inlineStr"/>
       <c r="V28" t="n">
-        <v>0.3</v>
+        <v>0.4</v>
       </c>
       <c r="W28" t="inlineStr">
         <is>
-          <t>['당기순이익', '유통물량', '골프주']</t>
+          <t>['신규상장', '골프주', '급등']</t>
         </is>
       </c>
       <c r="X28" t="n">

--- a/data/trending_integrated_20261030_11.xlsx
+++ b/data/trending_integrated_20261030_11.xlsx
@@ -567,24 +567,24 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>18640</v>
+        <v>19690</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>'+107.11%</t>
+          <t>'+118.78%</t>
         </is>
       </c>
       <c r="D2" t="n">
         <v>0</v>
       </c>
       <c r="E2" t="n">
-        <v>336</v>
+        <v>364</v>
       </c>
       <c r="F2" t="n">
-        <v>186</v>
+        <v>192</v>
       </c>
       <c r="G2" t="n">
-        <v>436</v>
+        <v>464</v>
       </c>
       <c r="H2" t="n">
         <v>1.98</v>
@@ -610,7 +610,7 @@
         <v>0</v>
       </c>
       <c r="O2" t="n">
-        <v>337168940235</v>
+        <v>353568842325</v>
       </c>
       <c r="P2" t="n">
         <v>21700</v>
@@ -626,16 +626,16 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>신규 상장주로서 높은 변동성을 보이며, 단기적인 등락에 대한 기대와 주의가 공존.</t>
+          <t>신규 상장주의 높은 변동성 속 당기순이익 250억 기록. 상승 가능성 및 저항선 분석.</t>
         </is>
       </c>
       <c r="U2" t="inlineStr"/>
       <c r="V2" t="n">
-        <v>0.3</v>
+        <v>0.2</v>
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>['신규상장', '단타', '변동성']</t>
+          <t>['신규 상장주', '당기순이익', '변동성']</t>
         </is>
       </c>
       <c r="X2" t="n">
@@ -655,263 +655,263 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>진양화학</t>
+          <t>라온시큐어</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>2890</v>
+        <v>19530</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>'+17.96%</t>
+          <t>'+17.30%</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>0.16</v>
+        <v>-0.75</v>
       </c>
       <c r="E3" t="n">
-        <v>54</v>
+        <v>88</v>
       </c>
       <c r="F3" t="n">
-        <v>38</v>
+        <v>58</v>
       </c>
       <c r="G3" t="n">
-        <v>31</v>
+        <v>132</v>
       </c>
       <c r="H3" t="n">
-        <v>0.79</v>
+        <v>3.6</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J3" t="n">
-        <v>2450</v>
+        <v>16650</v>
       </c>
       <c r="K3" t="n">
-        <v>2460</v>
+        <v>16830</v>
       </c>
       <c r="L3" t="n">
-        <v>3110</v>
+        <v>19750</v>
       </c>
       <c r="M3" t="n">
-        <v>2335</v>
+        <v>16750</v>
       </c>
       <c r="N3" t="n">
-        <v>0.63</v>
+        <v>4.35</v>
       </c>
       <c r="O3" t="n">
-        <v>11100876135</v>
+        <v>93242337875</v>
       </c>
       <c r="P3" t="n">
-        <v>3170</v>
+        <v>22450</v>
       </c>
       <c r="Q3" t="n">
-        <v>880</v>
+        <v>6320</v>
       </c>
       <c r="R3" t="n">
-        <v>-14000</v>
+        <v>94000</v>
       </c>
       <c r="S3" t="n">
-        <v>0</v>
+        <v>17000</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>정치 테마주로 분류되며 차기 대권 관련 언급이 많음. 대법원 판결 및 상폐 우려 관련 부정적 전망도 혼재.</t>
+          <t>양자 관련법 시행 및 국내외 해킹 사태에 따른 최대 수혜 기대. 보안 대장주로서의 주목.</t>
         </is>
       </c>
       <c r="U3" t="inlineStr"/>
       <c r="V3" t="n">
-        <v>0</v>
+        <v>0.4</v>
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>['정치 테마주', '대법원 판결', '상폐 우려']</t>
+          <t>['양자', '보안', '해킹']</t>
         </is>
       </c>
       <c r="X3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>추적</t>
+          <t>활성</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>051630</t>
+          <t>042510</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>라온시큐어</t>
+          <t>진양화학</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>19200</v>
+        <v>2840</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>'+15.32%</t>
+          <t>'+15.92%</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>-0.75</v>
+        <v>0.16</v>
       </c>
       <c r="E4" t="n">
-        <v>83</v>
+        <v>55</v>
       </c>
       <c r="F4" t="n">
-        <v>54</v>
+        <v>38</v>
       </c>
       <c r="G4" t="n">
-        <v>122</v>
+        <v>32</v>
       </c>
       <c r="H4" t="n">
-        <v>3.6</v>
+        <v>0.79</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J4" t="n">
-        <v>16650</v>
+        <v>2450</v>
       </c>
       <c r="K4" t="n">
-        <v>16830</v>
+        <v>2460</v>
       </c>
       <c r="L4" t="n">
-        <v>19750</v>
+        <v>3110</v>
       </c>
       <c r="M4" t="n">
-        <v>16750</v>
+        <v>2335</v>
       </c>
       <c r="N4" t="n">
-        <v>4.35</v>
+        <v>0.63</v>
       </c>
       <c r="O4" t="n">
-        <v>90342710955</v>
+        <v>11344848077</v>
       </c>
       <c r="P4" t="n">
-        <v>22450</v>
+        <v>3170</v>
       </c>
       <c r="Q4" t="n">
-        <v>6320</v>
+        <v>880</v>
       </c>
       <c r="R4" t="n">
-        <v>94000</v>
+        <v>-14000</v>
       </c>
       <c r="S4" t="n">
-        <v>17000</v>
+        <v>0</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>양자 관련법 시행 및 보안주로서의 수혜 기대감과 해킹 사태 관련 긍정적 언급이 나타남.</t>
+          <t>정치 테마주로 분류되며 차기 대권 관련 언급이 많음. 대법원 판결 및 상폐 우려 관련 부정적 전망도 혼재.</t>
         </is>
       </c>
       <c r="U4" t="inlineStr"/>
       <c r="V4" t="n">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>['양자보안', '해킹', '보안주']</t>
+          <t>['정치 테마주', '대법원 판결', '상폐 우려']</t>
         </is>
       </c>
       <c r="X4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>활성</t>
+          <t>추적</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>042510</t>
+          <t>051630</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>서울반도체</t>
+          <t>대원제약</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>12540</v>
+        <v>8740</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>'+11.96%</t>
+          <t>'+13.51%</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>-0.04</v>
+        <v>0.37</v>
       </c>
       <c r="E5" t="n">
-        <v>243</v>
+        <v>50</v>
       </c>
       <c r="F5" t="n">
-        <v>153</v>
+        <v>37</v>
       </c>
       <c r="G5" t="n">
-        <v>706</v>
+        <v>116</v>
       </c>
       <c r="H5" t="n">
-        <v>15.04</v>
+        <v>13.29</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J5" t="n">
-        <v>11200</v>
+        <v>7700</v>
       </c>
       <c r="K5" t="n">
-        <v>13500</v>
+        <v>9360</v>
       </c>
       <c r="L5" t="n">
-        <v>13710</v>
+        <v>9500</v>
       </c>
       <c r="M5" t="n">
-        <v>12100</v>
+        <v>8430</v>
       </c>
       <c r="N5" t="n">
-        <v>15.08</v>
+        <v>12.92</v>
       </c>
       <c r="O5" t="n">
-        <v>39486905045</v>
+        <v>7235720815</v>
       </c>
       <c r="P5" t="n">
-        <v>18960</v>
+        <v>13670</v>
       </c>
       <c r="Q5" t="n">
-        <v>5730</v>
+        <v>7060</v>
       </c>
       <c r="R5" t="n">
-        <v>-275000</v>
+        <v>-25000</v>
       </c>
       <c r="S5" t="n">
         <v>0</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>세계 최초 희토류 없는 백색 LED 개발 및 1위 기업으로서의 기술력과 시장 석권에 대한 강한 긍정 전망.</t>
+          <t>임상 3상 성공에도 불구하고 주가 부진. 시장 규모 및 경쟁 업체 고려 시 큰 호재 아님.</t>
         </is>
       </c>
       <c r="U5" t="inlineStr"/>
       <c r="V5" t="n">
-        <v>0.7</v>
+        <v>0</v>
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>['백색LED', '희토류', '기술개발']</t>
+          <t>['임상 3상', '위식도염', '시장 규모']</t>
         </is>
       </c>
       <c r="X5" t="n">
@@ -919,91 +919,91 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>활성</t>
+          <t>추적</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>046890</t>
+          <t>003220</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>대원제약</t>
+          <t>서울반도체</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>8600</v>
+        <v>12550</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>'+11.69%</t>
+          <t>'+12.05%</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>0.37</v>
+        <v>-0.04</v>
       </c>
       <c r="E6" t="n">
-        <v>50</v>
+        <v>250</v>
       </c>
       <c r="F6" t="n">
-        <v>37</v>
+        <v>158</v>
       </c>
       <c r="G6" t="n">
-        <v>114</v>
+        <v>726</v>
       </c>
       <c r="H6" t="n">
-        <v>13.29</v>
+        <v>15.04</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J6" t="n">
-        <v>7700</v>
+        <v>11200</v>
       </c>
       <c r="K6" t="n">
-        <v>9360</v>
+        <v>13500</v>
       </c>
       <c r="L6" t="n">
-        <v>9500</v>
+        <v>13710</v>
       </c>
       <c r="M6" t="n">
-        <v>8430</v>
+        <v>12100</v>
       </c>
       <c r="N6" t="n">
-        <v>12.92</v>
+        <v>15.08</v>
       </c>
       <c r="O6" t="n">
-        <v>7109298060</v>
+        <v>39988822035</v>
       </c>
       <c r="P6" t="n">
-        <v>13670</v>
+        <v>18960</v>
       </c>
       <c r="Q6" t="n">
-        <v>7060</v>
+        <v>5730</v>
       </c>
       <c r="R6" t="n">
-        <v>-25000</v>
+        <v>-275000</v>
       </c>
       <c r="S6" t="n">
         <v>0</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>임상 3상 성공에도 불구하고 주가 부진. 시장 규모 및 경쟁 업체 고려 시 큰 호재 아님.</t>
+          <t>세계 최초 희토류 없는 백색 LED 개발 성공. 100억 달러 백색 LED 시장 석권 전망.</t>
         </is>
       </c>
       <c r="U6" t="inlineStr"/>
       <c r="V6" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>['임상 3상', '위식도염', '시장 규모']</t>
+          <t>['LED', '희토류', '백색']</t>
         </is>
       </c>
       <c r="X6" t="n">
@@ -1011,12 +1011,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>추적</t>
+          <t>활성</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>003220</t>
+          <t>046890</t>
         </is>
       </c>
     </row>
@@ -1027,24 +1027,24 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>6720</v>
+        <v>6580</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>'+7.69%</t>
+          <t>'+5.45%</t>
         </is>
       </c>
       <c r="D7" t="n">
         <v>0</v>
       </c>
       <c r="E7" t="n">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="F7" t="n">
         <v>28</v>
       </c>
       <c r="G7" t="n">
-        <v>127</v>
+        <v>130</v>
       </c>
       <c r="H7" t="n">
         <v>0</v>
@@ -1070,7 +1070,7 @@
         <v>0</v>
       </c>
       <c r="O7" t="n">
-        <v>15228509320</v>
+        <v>15438264840</v>
       </c>
       <c r="P7" t="n">
         <v>16620</v>
@@ -1115,31 +1115,31 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>루닛</t>
+          <t>원익홀딩스</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>15610</v>
+        <v>29300</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>'+4.21%</t>
+          <t>'+4.46%</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>-0.9</v>
+        <v>-0.36</v>
       </c>
       <c r="E8" t="n">
-        <v>70</v>
+        <v>59</v>
       </c>
       <c r="F8" t="n">
-        <v>54</v>
+        <v>40</v>
       </c>
       <c r="G8" t="n">
-        <v>315</v>
+        <v>247</v>
       </c>
       <c r="H8" t="n">
-        <v>7.15</v>
+        <v>4.69</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
@@ -1147,38 +1147,38 @@
         </is>
       </c>
       <c r="J8" t="n">
-        <v>14980</v>
+        <v>28050</v>
       </c>
       <c r="K8" t="n">
-        <v>14980</v>
+        <v>27850</v>
       </c>
       <c r="L8" t="n">
-        <v>16150</v>
+        <v>30400</v>
       </c>
       <c r="M8" t="n">
-        <v>14610</v>
+        <v>27650</v>
       </c>
       <c r="N8" t="n">
-        <v>8.050000000000001</v>
+        <v>5.05</v>
       </c>
       <c r="O8" t="n">
-        <v>42202684580</v>
+        <v>106944197750</v>
       </c>
       <c r="P8" t="n">
-        <v>49800</v>
+        <v>50600</v>
       </c>
       <c r="Q8" t="n">
-        <v>8180</v>
+        <v>13210</v>
       </c>
       <c r="R8" t="n">
-        <v>109000</v>
+        <v>-45000</v>
       </c>
       <c r="S8" t="n">
-        <v>168000</v>
+        <v>95000</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>유방암 위험 예측 솔루션 FDA 승인 신청 및 AI 신약개발 기대감. 5,000억 원 가치 평가.</t>
+          <t>로봇 관련 기대감 속 3만원 돌파 시도. 정밀 엑추에이터 시장 진입 뉴스 확인.</t>
         </is>
       </c>
       <c r="U8" t="inlineStr"/>
@@ -1187,11 +1187,11 @@
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>['AI 신약개발', 'FDA 승인', '암 진단']</t>
+          <t>['로봇', '엑추에이터', '반도체']</t>
         </is>
       </c>
       <c r="X8" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="Y8" t="inlineStr">
         <is>
@@ -1200,38 +1200,38 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>328130</t>
+          <t>030530</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>원익홀딩스</t>
+          <t>루닛</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>29200</v>
+        <v>15550</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>'+4.10%</t>
+          <t>'+3.81%</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>-0.36</v>
+        <v>-0.9</v>
       </c>
       <c r="E9" t="n">
-        <v>58</v>
+        <v>71</v>
       </c>
       <c r="F9" t="n">
-        <v>39</v>
+        <v>55</v>
       </c>
       <c r="G9" t="n">
-        <v>214</v>
+        <v>331</v>
       </c>
       <c r="H9" t="n">
-        <v>4.69</v>
+        <v>7.15</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
@@ -1239,38 +1239,38 @@
         </is>
       </c>
       <c r="J9" t="n">
-        <v>28050</v>
+        <v>14980</v>
       </c>
       <c r="K9" t="n">
-        <v>27850</v>
+        <v>14980</v>
       </c>
       <c r="L9" t="n">
-        <v>30400</v>
+        <v>16150</v>
       </c>
       <c r="M9" t="n">
-        <v>27650</v>
+        <v>14610</v>
       </c>
       <c r="N9" t="n">
-        <v>5.05</v>
+        <v>8.050000000000001</v>
       </c>
       <c r="O9" t="n">
-        <v>105660197750</v>
+        <v>42693537305</v>
       </c>
       <c r="P9" t="n">
-        <v>50600</v>
+        <v>49800</v>
       </c>
       <c r="Q9" t="n">
-        <v>13210</v>
+        <v>8180</v>
       </c>
       <c r="R9" t="n">
-        <v>-45000</v>
+        <v>109000</v>
       </c>
       <c r="S9" t="n">
-        <v>95000</v>
+        <v>168000</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>로봇 관련 기대감 속 3만원 돌파 시도. 정밀 엑추에이터 시장 진입 뉴스 확인.</t>
+          <t>유방암 위험 예측 솔루션 FDA 승인 신청 및 AI 신약개발 기대감. 5,000억 원 가치 평가.</t>
         </is>
       </c>
       <c r="U9" t="inlineStr"/>
@@ -1279,11 +1279,11 @@
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>['로봇', '엑추에이터', '반도체']</t>
+          <t>['AI 신약개발', 'FDA 승인', '암 진단']</t>
         </is>
       </c>
       <c r="X9" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="Y9" t="inlineStr">
         <is>
@@ -1292,7 +1292,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>030530</t>
+          <t>328130</t>
         </is>
       </c>
     </row>
@@ -1303,24 +1303,24 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>50300</v>
+        <v>50200</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>'+2.44%</t>
+          <t>'+2.24%</t>
         </is>
       </c>
       <c r="D10" t="n">
         <v>-0.82</v>
       </c>
       <c r="E10" t="n">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="F10" t="n">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="G10" t="n">
-        <v>187</v>
+        <v>190</v>
       </c>
       <c r="H10" t="n">
         <v>23.82</v>
@@ -1346,7 +1346,7 @@
         <v>24.64</v>
       </c>
       <c r="O10" t="n">
-        <v>47096527650</v>
+        <v>47778087600</v>
       </c>
       <c r="P10" t="n">
         <v>97900</v>
@@ -1362,16 +1362,16 @@
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>최대 실적 발표 후, TC본더 매출 본격화 및 사이버 보안 수혜 기대감. 공매도 청산 및 5만/6만 비전 탈환 목표.</t>
+          <t>사상 최대 실적 발표에도 불구하고 주가 부진. TC본더 매출 본격화 및 HBM 수요 기대.</t>
         </is>
       </c>
       <c r="U10" t="inlineStr"/>
       <c r="V10" t="n">
-        <v>0.4</v>
+        <v>0.3</v>
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>['실적', 'TC본더', '공매도']</t>
+          <t>['실적', 'TC본더', 'HBM']</t>
         </is>
       </c>
       <c r="X10" t="n">
@@ -1395,24 +1395,24 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>8780</v>
+        <v>8680</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>'+2.33%</t>
+          <t>'+1.17%</t>
         </is>
       </c>
       <c r="D11" t="n">
         <v>0.01</v>
       </c>
       <c r="E11" t="n">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="F11" t="n">
         <v>50</v>
       </c>
       <c r="G11" t="n">
-        <v>211</v>
+        <v>219</v>
       </c>
       <c r="H11" t="n">
         <v>2.67</v>
@@ -1438,7 +1438,7 @@
         <v>2.66</v>
       </c>
       <c r="O11" t="n">
-        <v>25581552770</v>
+        <v>25811800180</v>
       </c>
       <c r="P11" t="n">
         <v>19270</v>
@@ -1454,16 +1454,16 @@
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>서울바이오시스의 영업이익 및 기술력 비교, 광통신 사업 가세 전망. 환기 해제 시 기관 매수 기대.</t>
+          <t>서울반도체 대비 높은 영업이익과 세계 최고 기술력 보유. 내년 매출 조단위 및 광통신 사업 가세 전망.</t>
         </is>
       </c>
       <c r="U11" t="inlineStr"/>
       <c r="V11" t="n">
-        <v>0.2</v>
+        <v>0.3</v>
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>['영업이익', '광통신', '환기']</t>
+          <t>['영업이익', '광통신', '기술력']</t>
         </is>
       </c>
       <c r="X11" t="n">
@@ -1483,254 +1483,254 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>양지사</t>
+          <t>삼성중공업</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>6730</v>
+        <v>15790</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>'+1.36%</t>
+          <t>'+0.45%</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>-0.05</v>
+        <v>0.06</v>
       </c>
       <c r="E12" t="n">
-        <v>59</v>
+        <v>92</v>
       </c>
       <c r="F12" t="n">
-        <v>33</v>
+        <v>57</v>
       </c>
       <c r="G12" t="n">
-        <v>65</v>
+        <v>228</v>
       </c>
       <c r="H12" t="n">
-        <v>0.85</v>
+        <v>28.13</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J12" t="n">
-        <v>6640</v>
+        <v>15720</v>
       </c>
       <c r="K12" t="n">
-        <v>7210</v>
+        <v>15420</v>
       </c>
       <c r="L12" t="n">
-        <v>7500</v>
+        <v>16050</v>
       </c>
       <c r="M12" t="n">
-        <v>6580</v>
+        <v>15320</v>
       </c>
       <c r="N12" t="n">
-        <v>0.9</v>
+        <v>28.07</v>
       </c>
       <c r="O12" t="n">
-        <v>29527277485</v>
+        <v>37007991950</v>
       </c>
       <c r="P12" t="n">
-        <v>9820</v>
+        <v>35350</v>
       </c>
       <c r="Q12" t="n">
-        <v>4000</v>
+        <v>15320</v>
       </c>
       <c r="R12" t="n">
-        <v>-63000</v>
+        <v>345000</v>
       </c>
       <c r="S12" t="n">
-        <v>0</v>
+        <v>35000</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>미국 시장 급등에 따른 주가 상승 기대감. 594억 규모 공급 계약 사실 확인.</t>
+          <t>미국 조선주 강세와 대비되는 국내 시장 상황. 자체 호재 및 증권사 리포트 기대.</t>
         </is>
       </c>
       <c r="U12" t="inlineStr"/>
       <c r="V12" t="n">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>['공급 계약', '유통 물량', '주포']</t>
+          <t>['조선주', '호재', '리포트']</t>
         </is>
       </c>
       <c r="X12" t="n">
-        <v>1</v>
+        <v>17</v>
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>추적</t>
+          <t>활성</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>030960</t>
+          <t>010140</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>삼성중공업</t>
+          <t>빛과전자</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>15760</v>
+        <v>4040</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>'+0.25%</t>
+          <t>'+0.00%</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>0.06</v>
+        <v>-0.77</v>
       </c>
       <c r="E13" t="n">
-        <v>91</v>
+        <v>64</v>
       </c>
       <c r="F13" t="n">
-        <v>56</v>
+        <v>43</v>
       </c>
       <c r="G13" t="n">
-        <v>223</v>
+        <v>142</v>
       </c>
       <c r="H13" t="n">
-        <v>28.13</v>
+        <v>1.43</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J13" t="n">
-        <v>15720</v>
+        <v>4040</v>
       </c>
       <c r="K13" t="n">
-        <v>15420</v>
+        <v>3925</v>
       </c>
       <c r="L13" t="n">
-        <v>16050</v>
+        <v>4265</v>
       </c>
       <c r="M13" t="n">
-        <v>15320</v>
+        <v>3880</v>
       </c>
       <c r="N13" t="n">
-        <v>28.07</v>
+        <v>2.2</v>
       </c>
       <c r="O13" t="n">
-        <v>36326399890</v>
+        <v>70846932777</v>
       </c>
       <c r="P13" t="n">
-        <v>35350</v>
+        <v>8100</v>
       </c>
       <c r="Q13" t="n">
-        <v>15320</v>
+        <v>592</v>
       </c>
       <c r="R13" t="n">
-        <v>345000</v>
+        <v>-37000</v>
       </c>
       <c r="S13" t="n">
-        <v>35000</v>
+        <v>0</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>미국 조선주 강세 속 국내 증시 부진. 증권사 리포트 및 기대감 존재.</t>
+          <t>상승 기대감과 함께 급등 가능성 언급. 외국인 및 프로그램 매수세 확인되나, '개잡주'라는 부정적 표현도 혼재.</t>
         </is>
       </c>
       <c r="U13" t="inlineStr"/>
       <c r="V13" t="n">
-        <v>0.4</v>
+        <v>0</v>
       </c>
       <c r="W13" t="inlineStr">
         <is>
-          <t>['조선주', '증권사리포트', ' 기대']</t>
+          <t>['급등 기대', '외국인 매수', '개잡주']</t>
         </is>
       </c>
       <c r="X13" t="n">
-        <v>17</v>
+        <v>3</v>
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>활성</t>
+          <t>추적</t>
         </is>
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>010140</t>
+          <t>069540</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>빛과전자</t>
+          <t>LG디스플레이</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>3985</v>
+        <v>7310</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>'-1.36%</t>
+          <t>'-1.88%</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>-0.77</v>
+        <v>-0.02</v>
       </c>
       <c r="E14" t="n">
-        <v>63</v>
+        <v>59</v>
       </c>
       <c r="F14" t="n">
-        <v>43</v>
+        <v>27</v>
       </c>
       <c r="G14" t="n">
-        <v>140</v>
+        <v>169</v>
       </c>
       <c r="H14" t="n">
-        <v>1.43</v>
+        <v>25.3</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J14" t="n">
-        <v>4040</v>
+        <v>7450</v>
       </c>
       <c r="K14" t="n">
-        <v>3925</v>
+        <v>7350</v>
       </c>
       <c r="L14" t="n">
-        <v>4265</v>
+        <v>7570</v>
       </c>
       <c r="M14" t="n">
-        <v>3880</v>
+        <v>7280</v>
       </c>
       <c r="N14" t="n">
-        <v>2.2</v>
+        <v>25.32</v>
       </c>
       <c r="O14" t="n">
-        <v>69905806231</v>
+        <v>7462337155</v>
       </c>
       <c r="P14" t="n">
-        <v>8100</v>
+        <v>17950</v>
       </c>
       <c r="Q14" t="n">
-        <v>592</v>
+        <v>7010</v>
       </c>
       <c r="R14" t="n">
-        <v>-37000</v>
+        <v>95000</v>
       </c>
       <c r="S14" t="n">
-        <v>0</v>
+        <v>-1000</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
-          <t>상승 기대감과 함께 급등 가능성 언급. 외국인 및 프로그램 매수세 확인되나, '개잡주'라는 부정적 표현도 혼재.</t>
+          <t>임원 자사주 매입 및 칩 인플레이션 해소 관련 긍정적 언급. 주가 하락 및 노조 관련 부정적 의견도 존재.</t>
         </is>
       </c>
       <c r="U14" t="inlineStr"/>
@@ -1739,11 +1739,11 @@
       </c>
       <c r="W14" t="inlineStr">
         <is>
-          <t>['급등 기대', '외국인 매수', '개잡주']</t>
+          <t>['자사주 매입', '칩 인플레이션', '노조']</t>
         </is>
       </c>
       <c r="X14" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="Y14" t="inlineStr">
         <is>
@@ -1752,38 +1752,38 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>069540</t>
+          <t>034220</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>LG디스플레이</t>
+          <t>삼성E&amp;A</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>7290</v>
+        <v>61600</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>'-2.15%</t>
+          <t>'-1.91%</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>-0.02</v>
+        <v>0.21</v>
       </c>
       <c r="E15" t="n">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="F15" t="n">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="G15" t="n">
-        <v>164</v>
+        <v>247</v>
       </c>
       <c r="H15" t="n">
-        <v>25.3</v>
+        <v>41.76</v>
       </c>
       <c r="I15" t="inlineStr">
         <is>
@@ -1791,38 +1791,38 @@
         </is>
       </c>
       <c r="J15" t="n">
-        <v>7450</v>
+        <v>62800</v>
       </c>
       <c r="K15" t="n">
-        <v>7350</v>
+        <v>62300</v>
       </c>
       <c r="L15" t="n">
-        <v>7570</v>
+        <v>62800</v>
       </c>
       <c r="M15" t="n">
-        <v>7280</v>
+        <v>60700</v>
       </c>
       <c r="N15" t="n">
-        <v>25.32</v>
+        <v>41.55</v>
       </c>
       <c r="O15" t="n">
-        <v>7330287700</v>
+        <v>65337053800</v>
       </c>
       <c r="P15" t="n">
-        <v>17950</v>
+        <v>67300</v>
       </c>
       <c r="Q15" t="n">
-        <v>7010</v>
+        <v>23150</v>
       </c>
       <c r="R15" t="n">
-        <v>95000</v>
+        <v>117000</v>
       </c>
       <c r="S15" t="n">
-        <v>-1000</v>
+        <v>-38000</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
-          <t>임원 자사주 매입 및 칩 인플레이션 해소 관련 긍정적 언급. 주가 하락 및 노조 관련 부정적 의견도 존재.</t>
+          <t>자사주 취득 및 중동 대규모 수주 공시 기대감. 외인/프매의 매수세와 함께 긍정적 전망이 일부 나타남.</t>
         </is>
       </c>
       <c r="U15" t="inlineStr"/>
@@ -1831,11 +1831,11 @@
       </c>
       <c r="W15" t="inlineStr">
         <is>
-          <t>['자사주 매입', '칩 인플레이션', '노조']</t>
+          <t>['자사주 취득', '수주 공시', '외인 매수']</t>
         </is>
       </c>
       <c r="X15" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="Y15" t="inlineStr">
         <is>
@@ -1844,77 +1844,77 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>034220</t>
+          <t>028050</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>삼성E&amp;A</t>
+          <t>양지사</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>61000</v>
+        <v>6510</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>'-2.87%</t>
+          <t>'-1.96%</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>0.21</v>
+        <v>-0.05</v>
       </c>
       <c r="E16" t="n">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="F16" t="n">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="G16" t="n">
-        <v>244</v>
+        <v>65</v>
       </c>
       <c r="H16" t="n">
-        <v>41.76</v>
+        <v>0.85</v>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J16" t="n">
-        <v>62800</v>
+        <v>6640</v>
       </c>
       <c r="K16" t="n">
-        <v>62300</v>
+        <v>7210</v>
       </c>
       <c r="L16" t="n">
-        <v>62800</v>
+        <v>7500</v>
       </c>
       <c r="M16" t="n">
-        <v>60700</v>
+        <v>6490</v>
       </c>
       <c r="N16" t="n">
-        <v>41.55</v>
+        <v>0.9</v>
       </c>
       <c r="O16" t="n">
-        <v>62137439350</v>
+        <v>29971885545</v>
       </c>
       <c r="P16" t="n">
-        <v>67300</v>
+        <v>9820</v>
       </c>
       <c r="Q16" t="n">
-        <v>23150</v>
+        <v>4000</v>
       </c>
       <c r="R16" t="n">
-        <v>117000</v>
+        <v>-63000</v>
       </c>
       <c r="S16" t="n">
-        <v>-38000</v>
+        <v>0</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
-          <t>자사주 취득 및 중동 대규모 수주 공시 기대감. 외인/프매의 매수세와 함께 긍정적 전망이 일부 나타남.</t>
+          <t>미국 시장 급등에 따른 주가 상승 기대감. 594억 규모 공급 계약 사실 확인.</t>
         </is>
       </c>
       <c r="U16" t="inlineStr"/>
@@ -1923,11 +1923,11 @@
       </c>
       <c r="W16" t="inlineStr">
         <is>
-          <t>['자사주 취득', '수주 공시', '외인 매수']</t>
+          <t>['공급 계약', '유통 물량', '주포']</t>
         </is>
       </c>
       <c r="X16" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="Y16" t="inlineStr">
         <is>
@@ -1936,7 +1936,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>028050</t>
+          <t>030960</t>
         </is>
       </c>
     </row>
@@ -1947,24 +1947,24 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>54000</v>
+        <v>54200</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>'-4.76%</t>
+          <t>'-4.41%</t>
         </is>
       </c>
       <c r="D17" t="n">
         <v>-0.2</v>
       </c>
       <c r="E17" t="n">
-        <v>249</v>
+        <v>252</v>
       </c>
       <c r="F17" t="n">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="G17" t="n">
-        <v>833</v>
+        <v>850</v>
       </c>
       <c r="H17" t="n">
         <v>22.14</v>
@@ -1990,7 +1990,7 @@
         <v>22.34</v>
       </c>
       <c r="O17" t="n">
-        <v>58294947750</v>
+        <v>59762286500</v>
       </c>
       <c r="P17" t="n">
         <v>139200</v>
@@ -2006,16 +2006,16 @@
       </c>
       <c r="T17" t="inlineStr">
         <is>
-          <t>미국 뉴스케일파워 SMR 원자로 수주 및 실적 개선에 대한 긍정적 언급이 주를 이룸.</t>
+          <t>미국 뉴스케일파워 SMR 원자로 수주 및 실적 호조. 체코 원전 사업 무산에 대한 아쉬움.</t>
         </is>
       </c>
       <c r="U17" t="inlineStr"/>
       <c r="V17" t="n">
-        <v>0.6</v>
+        <v>0.4</v>
       </c>
       <c r="W17" t="inlineStr">
         <is>
-          <t>['SMR', '뉴스케일파워', '수주']</t>
+          <t>['SMR', '수주', '실적']</t>
         </is>
       </c>
       <c r="X17" t="n">
@@ -2039,24 +2039,24 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>10930</v>
+        <v>10990</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>'-5.94%</t>
+          <t>'-5.42%</t>
         </is>
       </c>
       <c r="D18" t="n">
         <v>0.13</v>
       </c>
       <c r="E18" t="n">
-        <v>316</v>
+        <v>328</v>
       </c>
       <c r="F18" t="n">
-        <v>156</v>
+        <v>162</v>
       </c>
       <c r="G18" t="n">
-        <v>1011</v>
+        <v>1029</v>
       </c>
       <c r="H18" t="n">
         <v>9.73</v>
@@ -2082,7 +2082,7 @@
         <v>9.6</v>
       </c>
       <c r="O18" t="n">
-        <v>42168695555</v>
+        <v>43086272630</v>
       </c>
       <c r="P18" t="n">
         <v>40350</v>
@@ -2098,7 +2098,7 @@
       </c>
       <c r="T18" t="inlineStr">
         <is>
-          <t>원전, 가덕도 증액, 공매도 금지 등 호재성 뉴스가 언급되나, 정부 비판과 함께 나타남.</t>
+          <t>가덕도 공사비 증액 및 재건 사업 기대감. 공매도 금지 조치에 따른 영향 분석.</t>
         </is>
       </c>
       <c r="U18" t="inlineStr"/>
@@ -2107,7 +2107,7 @@
       </c>
       <c r="W18" t="inlineStr">
         <is>
-          <t>['원전', '가덕도', '공매도 금지']</t>
+          <t>['가덕도', '공사비', '재건']</t>
         </is>
       </c>
       <c r="X18" t="n">
@@ -2131,11 +2131,11 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>217750</v>
+        <v>219000</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>'-6.14%</t>
+          <t>'-5.60%</t>
         </is>
       </c>
       <c r="D19" t="n">
@@ -2145,10 +2145,10 @@
         <v>800</v>
       </c>
       <c r="F19" t="n">
-        <v>554</v>
+        <v>551</v>
       </c>
       <c r="G19" t="n">
-        <v>1317</v>
+        <v>1291</v>
       </c>
       <c r="H19" t="n">
         <v>46.17</v>
@@ -2174,7 +2174,7 @@
         <v>46.19</v>
       </c>
       <c r="O19" t="n">
-        <v>1901923387000</v>
+        <v>1969988017250</v>
       </c>
       <c r="P19" t="n">
         <v>374500</v>
@@ -2190,7 +2190,7 @@
       </c>
       <c r="T19" t="inlineStr">
         <is>
-          <t>이재용 관련 언급과 주주환원 기대가 있으나, 정치적 비난이 주를 이룸.</t>
+          <t>현 정부 및 경영진에 대한 비판과 함께 주주환원 발표 기대. 기관 연기금의 매도 물량 출회.</t>
         </is>
       </c>
       <c r="U19" t="inlineStr"/>
@@ -2199,7 +2199,7 @@
       </c>
       <c r="W19" t="inlineStr">
         <is>
-          <t>['주주환원', '이재용', '정치']</t>
+          <t>['주주환원', '연기금', '매도']</t>
         </is>
       </c>
       <c r="X19" t="n">
@@ -2219,31 +2219,31 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>한화솔루션</t>
+          <t>삼성전자우</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>21800</v>
+        <v>170300</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>'-7.63%</t>
+          <t>'-7.40%</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>-0.63</v>
+        <v>-0.13</v>
       </c>
       <c r="E20" t="n">
-        <v>198</v>
+        <v>51</v>
       </c>
       <c r="F20" t="n">
-        <v>149</v>
+        <v>43</v>
       </c>
       <c r="G20" t="n">
-        <v>463</v>
+        <v>161</v>
       </c>
       <c r="H20" t="n">
-        <v>11.6</v>
+        <v>74.87</v>
       </c>
       <c r="I20" t="inlineStr">
         <is>
@@ -2251,91 +2251,91 @@
         </is>
       </c>
       <c r="J20" t="n">
-        <v>23600</v>
+        <v>183900</v>
       </c>
       <c r="K20" t="n">
-        <v>22650</v>
+        <v>176800</v>
       </c>
       <c r="L20" t="n">
-        <v>22700</v>
+        <v>179000</v>
       </c>
       <c r="M20" t="n">
-        <v>21100</v>
+        <v>168100</v>
       </c>
       <c r="N20" t="n">
-        <v>12.23</v>
+        <v>75</v>
       </c>
       <c r="O20" t="n">
-        <v>66935903625</v>
+        <v>457593359350</v>
       </c>
       <c r="P20" t="n">
-        <v>59300</v>
+        <v>243500</v>
       </c>
       <c r="Q20" t="n">
-        <v>21100</v>
+        <v>71000</v>
       </c>
       <c r="R20" t="n">
-        <v>-580000</v>
+        <v>-416000</v>
       </c>
       <c r="S20" t="n">
-        <v>-192000</v>
+        <v>-18000</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
-          <t>태양광 물량 완판 뉴스가 있으나, 주가 누르기 의혹과 급락으로 인한 부정적 여론이 지배적.</t>
+          <t>주가 조작 및 증여세 관련 부정적 언급과 함께 시장 대폭락에 대한 우려가 존재. 우선주 소각 및 반등 기대도 일부.</t>
         </is>
       </c>
       <c r="U20" t="inlineStr"/>
       <c r="V20" t="n">
-        <v>0.2</v>
+        <v>0</v>
       </c>
       <c r="W20" t="inlineStr">
         <is>
-          <t>['태양광', '주가 누르기', '급락']</t>
+          <t>['주가 조작', '증여세', '우선주 소각']</t>
         </is>
       </c>
       <c r="X20" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>활성</t>
+          <t>추적</t>
         </is>
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>009830</t>
+          <t>005935</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>삼성전자우</t>
+          <t>한화솔루션</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>169800</v>
+        <v>21850</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>'-7.67%</t>
+          <t>'-7.42%</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>-0.13</v>
+        <v>-0.63</v>
       </c>
       <c r="E21" t="n">
-        <v>49</v>
+        <v>205</v>
       </c>
       <c r="F21" t="n">
-        <v>41</v>
+        <v>151</v>
       </c>
       <c r="G21" t="n">
-        <v>161</v>
+        <v>471</v>
       </c>
       <c r="H21" t="n">
-        <v>74.87</v>
+        <v>11.6</v>
       </c>
       <c r="I21" t="inlineStr">
         <is>
@@ -2343,91 +2343,91 @@
         </is>
       </c>
       <c r="J21" t="n">
-        <v>183900</v>
+        <v>23600</v>
       </c>
       <c r="K21" t="n">
-        <v>176800</v>
+        <v>22650</v>
       </c>
       <c r="L21" t="n">
-        <v>179000</v>
+        <v>22700</v>
       </c>
       <c r="M21" t="n">
-        <v>168100</v>
+        <v>21100</v>
       </c>
       <c r="N21" t="n">
-        <v>75</v>
+        <v>12.23</v>
       </c>
       <c r="O21" t="n">
-        <v>442323344100</v>
+        <v>67964864050</v>
       </c>
       <c r="P21" t="n">
-        <v>243500</v>
+        <v>59300</v>
       </c>
       <c r="Q21" t="n">
-        <v>71000</v>
+        <v>21100</v>
       </c>
       <c r="R21" t="n">
-        <v>-416000</v>
+        <v>-580000</v>
       </c>
       <c r="S21" t="n">
-        <v>-18000</v>
+        <v>-192000</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
-          <t>주가 조작 및 증여세 관련 부정적 언급과 함께 시장 대폭락에 대한 우려가 존재. 우선주 소각 및 반등 기대도 일부.</t>
+          <t>태양광 물량 완판 뉴스가 있으나, 주가 누르기 의혹과 급락으로 인한 부정적 여론이 지배적.</t>
         </is>
       </c>
       <c r="U21" t="inlineStr"/>
       <c r="V21" t="n">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="W21" t="inlineStr">
         <is>
-          <t>['주가 조작', '증여세', '우선주 소각']</t>
+          <t>['태양광', '주가 누르기', '급락']</t>
         </is>
       </c>
       <c r="X21" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>추적</t>
+          <t>활성</t>
         </is>
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>005935</t>
+          <t>009830</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>서산</t>
+          <t>대한광통신</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>7240</v>
+        <v>13840</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>'-8.35%</t>
+          <t>'-7.92%</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>-0.03</v>
+        <v>-0.2</v>
       </c>
       <c r="E22" t="n">
-        <v>59</v>
+        <v>103</v>
       </c>
       <c r="F22" t="n">
-        <v>30</v>
+        <v>56</v>
       </c>
       <c r="G22" t="n">
-        <v>106</v>
+        <v>371</v>
       </c>
       <c r="H22" t="n">
-        <v>0.39</v>
+        <v>3.13</v>
       </c>
       <c r="I22" t="inlineStr">
         <is>
@@ -2435,143 +2435,143 @@
         </is>
       </c>
       <c r="J22" t="n">
-        <v>7900</v>
+        <v>15030</v>
       </c>
       <c r="K22" t="n">
-        <v>7790</v>
+        <v>14500</v>
       </c>
       <c r="L22" t="n">
-        <v>8130</v>
+        <v>14570</v>
       </c>
       <c r="M22" t="n">
-        <v>7100</v>
+        <v>13710</v>
       </c>
       <c r="N22" t="n">
-        <v>0.42</v>
+        <v>3.33</v>
       </c>
       <c r="O22" t="n">
-        <v>14324965455</v>
+        <v>37289303285</v>
       </c>
       <c r="P22" t="n">
-        <v>10300</v>
+        <v>31500</v>
       </c>
       <c r="Q22" t="n">
-        <v>952</v>
+        <v>1830</v>
       </c>
       <c r="R22" t="n">
-        <v>1000</v>
+        <v>-118000</v>
       </c>
       <c r="S22" t="n">
-        <v>0</v>
+        <v>-23000</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
-          <t>서산, 594억 공급 계약 재료를 바탕으로 한 긍정적 전망. 다만, 시장 전체 하락세 및 개미 투자자 심리 불안감 존재.</t>
+          <t>대규모 하락장 속에서 광통신 주식에 대한 투자 심리 위축. 3만 전고점까지 보유 의견 존재.</t>
         </is>
       </c>
       <c r="U22" t="inlineStr"/>
       <c r="V22" t="n">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="W22" t="inlineStr">
         <is>
-          <t>['공급계약', '재료', '주가']</t>
+          <t>['광통신', '하락장', '전고점']</t>
         </is>
       </c>
       <c r="X22" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>추적</t>
+          <t>활성</t>
         </is>
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>079650</t>
+          <t>010170</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>대한광통신</t>
+          <t>SK하이닉스</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>13720</v>
+        <v>1403000</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>'-8.72%</t>
+          <t>'-8.06%</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>-0.2</v>
+        <v>0.06</v>
       </c>
       <c r="E23" t="n">
-        <v>97</v>
+        <v>800</v>
       </c>
       <c r="F23" t="n">
-        <v>52</v>
+        <v>528</v>
       </c>
       <c r="G23" t="n">
-        <v>364</v>
+        <v>1346</v>
       </c>
       <c r="H23" t="n">
-        <v>3.13</v>
+        <v>48.72</v>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J23" t="n">
-        <v>15030</v>
+        <v>1526000</v>
       </c>
       <c r="K23" t="n">
-        <v>14500</v>
+        <v>1444000</v>
       </c>
       <c r="L23" t="n">
-        <v>14570</v>
+        <v>1446000</v>
       </c>
       <c r="M23" t="n">
-        <v>13710</v>
+        <v>1381000</v>
       </c>
       <c r="N23" t="n">
-        <v>3.33</v>
+        <v>48.66</v>
       </c>
       <c r="O23" t="n">
-        <v>36499677200</v>
+        <v>2441374946000</v>
       </c>
       <c r="P23" t="n">
-        <v>31500</v>
+        <v>2987000</v>
       </c>
       <c r="Q23" t="n">
-        <v>1830</v>
+        <v>501000</v>
       </c>
       <c r="R23" t="n">
-        <v>-118000</v>
+        <v>-165000</v>
       </c>
       <c r="S23" t="n">
-        <v>-23000</v>
+        <v>-76000</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
-          <t>정부 정책 불신에도 불구하고 광통신, 특허 등 호재 기반 상승 기대. 3만원 전고점 돌파 전망.</t>
+          <t>코스피 시장 전반의 급락 속 SK하이닉스 하락세. 개미 투자자들의 대규모 매수세 유입.</t>
         </is>
       </c>
       <c r="U23" t="inlineStr"/>
       <c r="V23" t="n">
-        <v>0.3</v>
+        <v>0.1</v>
       </c>
       <c r="W23" t="inlineStr">
         <is>
-          <t>['광통신', '특허', '호재']</t>
+          <t>['코스피', '하락세', '개미']</t>
         </is>
       </c>
       <c r="X23" t="n">
-        <v>7</v>
+        <v>21</v>
       </c>
       <c r="Y23" t="inlineStr">
         <is>
@@ -2580,99 +2580,99 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>010170</t>
+          <t>000660</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>SK하이닉스</t>
+          <t>서산</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>1393000</v>
+        <v>7230</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>'-8.72%</t>
+          <t>'-8.48%</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>0.06</v>
+        <v>-0.03</v>
       </c>
       <c r="E24" t="n">
-        <v>800</v>
+        <v>59</v>
       </c>
       <c r="F24" t="n">
-        <v>532</v>
+        <v>30</v>
       </c>
       <c r="G24" t="n">
-        <v>1315</v>
+        <v>110</v>
       </c>
       <c r="H24" t="n">
-        <v>48.72</v>
+        <v>0.39</v>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J24" t="n">
-        <v>1526000</v>
+        <v>7900</v>
       </c>
       <c r="K24" t="n">
-        <v>1444000</v>
+        <v>7790</v>
       </c>
       <c r="L24" t="n">
-        <v>1446000</v>
+        <v>8130</v>
       </c>
       <c r="M24" t="n">
-        <v>1381000</v>
+        <v>7100</v>
       </c>
       <c r="N24" t="n">
-        <v>48.66</v>
+        <v>0.42</v>
       </c>
       <c r="O24" t="n">
-        <v>2356489420000</v>
+        <v>14443691290</v>
       </c>
       <c r="P24" t="n">
-        <v>2987000</v>
+        <v>10300</v>
       </c>
       <c r="Q24" t="n">
-        <v>501000</v>
+        <v>952</v>
       </c>
       <c r="R24" t="n">
-        <v>-165000</v>
+        <v>1000</v>
       </c>
       <c r="S24" t="n">
-        <v>-76000</v>
+        <v>0</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
-          <t>엔비디아 회복세 언급에도 불구하고, 정치적 요인으로 인한 증시 폭락에 대한 불만이 압도적.</t>
+          <t>서산, 594억 공급 계약 재료를 바탕으로 한 긍정적 전망. 다만, 시장 전체 하락세 및 개미 투자자 심리 불안감 존재.</t>
         </is>
       </c>
       <c r="U24" t="inlineStr"/>
       <c r="V24" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="W24" t="inlineStr">
         <is>
-          <t>['엔비디아', '폭락', '정치']</t>
+          <t>['공급계약', '재료', '주가']</t>
         </is>
       </c>
       <c r="X24" t="n">
-        <v>21</v>
+        <v>2</v>
       </c>
       <c r="Y24" t="inlineStr">
         <is>
-          <t>활성</t>
+          <t>추적</t>
         </is>
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>000660</t>
+          <t>079650</t>
         </is>
       </c>
     </row>
@@ -2683,24 +2683,24 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>116500</v>
+        <v>117100</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>'-15.70%</t>
+          <t>'-15.27%</t>
         </is>
       </c>
       <c r="D25" t="n">
         <v>-0.26</v>
       </c>
       <c r="E25" t="n">
-        <v>119</v>
+        <v>125</v>
       </c>
       <c r="F25" t="n">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="G25" t="n">
-        <v>300</v>
+        <v>318</v>
       </c>
       <c r="H25" t="n">
         <v>14.2</v>
@@ -2720,13 +2720,13 @@
         <v>132900</v>
       </c>
       <c r="M25" t="n">
-        <v>116500</v>
+        <v>116400</v>
       </c>
       <c r="N25" t="n">
         <v>14.46</v>
       </c>
       <c r="O25" t="n">
-        <v>116595625300</v>
+        <v>120516425800</v>
       </c>
       <c r="P25" t="n">
         <v>198000</v>
@@ -2742,7 +2742,7 @@
       </c>
       <c r="T25" t="inlineStr">
         <is>
-          <t>실적 호조 기대에도 불구하고 급락하는 주가에 대한 불만과 의아함이 나타남.</t>
+          <t>급격한 주가 하락에도 불구하고 예상되는 호실적. 기관 및 외국인 매매 동향 주시.</t>
         </is>
       </c>
       <c r="U25" t="inlineStr"/>
@@ -2751,7 +2751,7 @@
       </c>
       <c r="W25" t="inlineStr">
         <is>
-          <t>['실적', '기판주', '급락']</t>
+          <t>['실적', '주가 하락', '기관']</t>
         </is>
       </c>
       <c r="X25" t="n">
@@ -2775,24 +2775,24 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>13240</v>
+        <v>13400</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>'-22.12%</t>
+          <t>'-21.18%</t>
         </is>
       </c>
       <c r="D26" t="n">
         <v>0.01</v>
       </c>
       <c r="E26" t="n">
-        <v>155</v>
+        <v>162</v>
       </c>
       <c r="F26" t="n">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="G26" t="n">
-        <v>124</v>
+        <v>128</v>
       </c>
       <c r="H26" t="n">
         <v>0.66</v>
@@ -2818,7 +2818,7 @@
         <v>0.65</v>
       </c>
       <c r="O26" t="n">
-        <v>29526471460</v>
+        <v>29850534500</v>
       </c>
       <c r="P26" t="n">
         <v>28800</v>
@@ -2834,16 +2834,16 @@
       </c>
       <c r="T26" t="inlineStr">
         <is>
-          <t>보호예수 물량 해제 이후 주가 변동성 발생. 마이크론 퀠테스트 통과 종목에 대한 매수세 언급.</t>
+          <t>보호예수 해제 후 물량 출회 가능성 언급. 마이크론 퀠테스트 통과 및 반도체 생산량 증가 기대.</t>
         </is>
       </c>
       <c r="U26" t="inlineStr"/>
       <c r="V26" t="n">
-        <v>0.1</v>
+        <v>0.4</v>
       </c>
       <c r="W26" t="inlineStr">
         <is>
-          <t>['보호예수', '퀠테스트', '매집']</t>
+          <t>['보호예수', '퀠테스트', '반도체']</t>
         </is>
       </c>
       <c r="X26" t="n">
@@ -2867,21 +2867,21 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>1851</v>
+        <v>1849</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>'-28.12%</t>
+          <t>'-28.19%</t>
         </is>
       </c>
       <c r="D27" t="n">
         <v>1.45</v>
       </c>
       <c r="E27" t="n">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="F27" t="n">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="G27" t="n">
         <v>27</v>
@@ -2910,7 +2910,7 @@
         <v>3.35</v>
       </c>
       <c r="O27" t="n">
-        <v>6517787721</v>
+        <v>6573429750</v>
       </c>
       <c r="P27" t="n">
         <v>5700</v>
@@ -2959,24 +2959,24 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>10290</v>
+        <v>10210</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>'-31.40%</t>
+          <t>'-31.93%</t>
         </is>
       </c>
       <c r="D28" t="n">
         <v>0</v>
       </c>
       <c r="E28" t="n">
-        <v>311</v>
+        <v>325</v>
       </c>
       <c r="F28" t="n">
-        <v>147</v>
+        <v>155</v>
       </c>
       <c r="G28" t="n">
-        <v>545</v>
+        <v>570</v>
       </c>
       <c r="H28" t="n">
         <v>3.05</v>
@@ -3002,7 +3002,7 @@
         <v>0</v>
       </c>
       <c r="O28" t="n">
-        <v>96671808405</v>
+        <v>97368732195</v>
       </c>
       <c r="P28" t="n">
         <v>12700</v>
@@ -3018,16 +3018,16 @@
       </c>
       <c r="T28" t="inlineStr">
         <is>
-          <t>신규 상장주로서 상한가 및 급등 기대감이 높으나, 주가 하락에 대한 우려도 존재.</t>
+          <t>상장 초기 급락 후 회복 기대감. 양호한 매출 및 영업이익, 유통물량 희소성 부각.</t>
         </is>
       </c>
       <c r="U28" t="inlineStr"/>
       <c r="V28" t="n">
-        <v>0.4</v>
+        <v>0.3</v>
       </c>
       <c r="W28" t="inlineStr">
         <is>
-          <t>['신규상장', '골프주', '급등']</t>
+          <t>['상장', '실적', '유통물량']</t>
         </is>
       </c>
       <c r="X28" t="n">

--- a/data/trending_integrated_20261030_11.xlsx
+++ b/data/trending_integrated_20261030_11.xlsx
@@ -567,24 +567,24 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>19690</v>
+        <v>21750</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>'+118.78%</t>
+          <t>'+141.67%</t>
         </is>
       </c>
       <c r="D2" t="n">
         <v>0</v>
       </c>
       <c r="E2" t="n">
-        <v>364</v>
+        <v>420</v>
       </c>
       <c r="F2" t="n">
-        <v>192</v>
+        <v>200</v>
       </c>
       <c r="G2" t="n">
-        <v>464</v>
+        <v>492</v>
       </c>
       <c r="H2" t="n">
         <v>1.98</v>
@@ -601,7 +601,7 @@
         <v>19290</v>
       </c>
       <c r="L2" t="n">
-        <v>21700</v>
+        <v>22450</v>
       </c>
       <c r="M2" t="n">
         <v>16450</v>
@@ -610,10 +610,10 @@
         <v>0</v>
       </c>
       <c r="O2" t="n">
-        <v>353568842325</v>
+        <v>398771669565</v>
       </c>
       <c r="P2" t="n">
-        <v>21700</v>
+        <v>22450</v>
       </c>
       <c r="Q2" t="n">
         <v>16450</v>
@@ -659,24 +659,24 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>19530</v>
+        <v>19360</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>'+17.30%</t>
+          <t>'+16.28%</t>
         </is>
       </c>
       <c r="D3" t="n">
         <v>-0.75</v>
       </c>
       <c r="E3" t="n">
-        <v>88</v>
+        <v>93</v>
       </c>
       <c r="F3" t="n">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="G3" t="n">
-        <v>132</v>
+        <v>137</v>
       </c>
       <c r="H3" t="n">
         <v>3.6</v>
@@ -702,7 +702,7 @@
         <v>4.35</v>
       </c>
       <c r="O3" t="n">
-        <v>93242337875</v>
+        <v>96670225175</v>
       </c>
       <c r="P3" t="n">
         <v>22450</v>
@@ -718,12 +718,12 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>양자 관련법 시행 및 국내외 해킹 사태에 따른 최대 수혜 기대. 보안 대장주로서의 주목.</t>
+          <t>양자 관련법 시행 및 보안 대장주로서의 기대감. 바이낸스, 빗썸 해킹 사태로 인한 수혜 전망. 장기적 관점에서의 보안주 투자 권유.</t>
         </is>
       </c>
       <c r="U3" t="inlineStr"/>
       <c r="V3" t="n">
-        <v>0.4</v>
+        <v>0.5</v>
       </c>
       <c r="W3" t="inlineStr">
         <is>
@@ -751,11 +751,11 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>2840</v>
+        <v>2790</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>'+15.92%</t>
+          <t>'+13.88%</t>
         </is>
       </c>
       <c r="D4" t="n">
@@ -768,7 +768,7 @@
         <v>38</v>
       </c>
       <c r="G4" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="H4" t="n">
         <v>0.79</v>
@@ -794,7 +794,7 @@
         <v>0.63</v>
       </c>
       <c r="O4" t="n">
-        <v>11344848077</v>
+        <v>11648168264</v>
       </c>
       <c r="P4" t="n">
         <v>3170</v>
@@ -843,24 +843,24 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>8740</v>
+        <v>8720</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>'+13.51%</t>
+          <t>'+13.25%</t>
         </is>
       </c>
       <c r="D5" t="n">
         <v>0.37</v>
       </c>
       <c r="E5" t="n">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="F5" t="n">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="G5" t="n">
-        <v>116</v>
+        <v>139</v>
       </c>
       <c r="H5" t="n">
         <v>13.29</v>
@@ -886,7 +886,7 @@
         <v>12.92</v>
       </c>
       <c r="O5" t="n">
-        <v>7235720815</v>
+        <v>7371462895</v>
       </c>
       <c r="P5" t="n">
         <v>13670</v>
@@ -935,24 +935,24 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>12550</v>
+        <v>12540</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>'+12.05%</t>
+          <t>'+11.96%</t>
         </is>
       </c>
       <c r="D6" t="n">
         <v>-0.04</v>
       </c>
       <c r="E6" t="n">
-        <v>250</v>
+        <v>255</v>
       </c>
       <c r="F6" t="n">
-        <v>158</v>
+        <v>161</v>
       </c>
       <c r="G6" t="n">
-        <v>726</v>
+        <v>744</v>
       </c>
       <c r="H6" t="n">
         <v>15.04</v>
@@ -978,7 +978,7 @@
         <v>15.08</v>
       </c>
       <c r="O6" t="n">
-        <v>39988822035</v>
+        <v>40876081915</v>
       </c>
       <c r="P6" t="n">
         <v>18960</v>
@@ -994,7 +994,7 @@
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>세계 최초 희토류 없는 백색 LED 개발 성공. 100억 달러 백색 LED 시장 석권 전망.</t>
+          <t>세계 최초 희토류 없는 백색 LED 개발 및 100억 달러 시장 석권 기대. 기술 개발 관련 긍정적 평가 및 저가 매수 기회 언급.</t>
         </is>
       </c>
       <c r="U6" t="inlineStr"/>
@@ -1003,7 +1003,7 @@
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>['LED', '희토류', '백색']</t>
+          <t>['백색 LED', '희토류', '시장 석권']</t>
         </is>
       </c>
       <c r="X6" t="n">
@@ -1027,24 +1027,24 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>6580</v>
+        <v>6690</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>'+5.45%</t>
+          <t>'+7.21%</t>
         </is>
       </c>
       <c r="D7" t="n">
         <v>0</v>
       </c>
       <c r="E7" t="n">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="F7" t="n">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="G7" t="n">
-        <v>130</v>
+        <v>135</v>
       </c>
       <c r="H7" t="n">
         <v>0</v>
@@ -1070,7 +1070,7 @@
         <v>0</v>
       </c>
       <c r="O7" t="n">
-        <v>15438264840</v>
+        <v>16027079645</v>
       </c>
       <c r="P7" t="n">
         <v>16620</v>
@@ -1119,24 +1119,24 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>29300</v>
+        <v>29150</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>'+4.46%</t>
+          <t>'+3.92%</t>
         </is>
       </c>
       <c r="D8" t="n">
         <v>-0.36</v>
       </c>
       <c r="E8" t="n">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="F8" t="n">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="G8" t="n">
-        <v>247</v>
+        <v>265</v>
       </c>
       <c r="H8" t="n">
         <v>4.69</v>
@@ -1162,7 +1162,7 @@
         <v>5.05</v>
       </c>
       <c r="O8" t="n">
-        <v>106944197750</v>
+        <v>108205596600</v>
       </c>
       <c r="P8" t="n">
         <v>50600</v>
@@ -1211,11 +1211,11 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>15550</v>
+        <v>15470</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>'+3.81%</t>
+          <t>'+3.27%</t>
         </is>
       </c>
       <c r="D9" t="n">
@@ -1228,7 +1228,7 @@
         <v>55</v>
       </c>
       <c r="G9" t="n">
-        <v>331</v>
+        <v>338</v>
       </c>
       <c r="H9" t="n">
         <v>7.15</v>
@@ -1254,7 +1254,7 @@
         <v>8.050000000000001</v>
       </c>
       <c r="O9" t="n">
-        <v>42693537305</v>
+        <v>43217718275</v>
       </c>
       <c r="P9" t="n">
         <v>49800</v>
@@ -1303,24 +1303,24 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>50200</v>
+        <v>50100</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>'+2.24%</t>
+          <t>'+2.04%</t>
         </is>
       </c>
       <c r="D10" t="n">
         <v>-0.82</v>
       </c>
       <c r="E10" t="n">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="F10" t="n">
         <v>59</v>
       </c>
       <c r="G10" t="n">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="H10" t="n">
         <v>23.82</v>
@@ -1346,7 +1346,7 @@
         <v>24.64</v>
       </c>
       <c r="O10" t="n">
-        <v>47778087600</v>
+        <v>48856936475</v>
       </c>
       <c r="P10" t="n">
         <v>97900</v>
@@ -1362,16 +1362,16 @@
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>사상 최대 실적 발표에도 불구하고 주가 부진. TC본더 매출 본격화 및 HBM 수요 기대.</t>
+          <t>한화비전, 사상 최대 실적 발표 및 TC본더 매출 본격화로 인한 실적 개선 전망. 사이버 해킹 보안 분야 수혜 기대.</t>
         </is>
       </c>
       <c r="U10" t="inlineStr"/>
       <c r="V10" t="n">
-        <v>0.3</v>
+        <v>0.6</v>
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>['실적', 'TC본더', 'HBM']</t>
+          <t>['실적', 'TC본더', '수혜']</t>
         </is>
       </c>
       <c r="X10" t="n">
@@ -1391,31 +1391,31 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>서울바이오시스</t>
+          <t>양지사</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>8680</v>
+        <v>6670</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>'+1.17%</t>
+          <t>'+0.45%</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>0.01</v>
+        <v>-0.05</v>
       </c>
       <c r="E11" t="n">
-        <v>80</v>
+        <v>63</v>
       </c>
       <c r="F11" t="n">
-        <v>50</v>
+        <v>35</v>
       </c>
       <c r="G11" t="n">
-        <v>219</v>
+        <v>68</v>
       </c>
       <c r="H11" t="n">
-        <v>2.67</v>
+        <v>0.85</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>
@@ -1423,47 +1423,47 @@
         </is>
       </c>
       <c r="J11" t="n">
-        <v>8580</v>
+        <v>6640</v>
       </c>
       <c r="K11" t="n">
-        <v>11090</v>
+        <v>7210</v>
       </c>
       <c r="L11" t="n">
-        <v>11150</v>
+        <v>7500</v>
       </c>
       <c r="M11" t="n">
-        <v>8400</v>
+        <v>6490</v>
       </c>
       <c r="N11" t="n">
-        <v>2.66</v>
+        <v>0.9</v>
       </c>
       <c r="O11" t="n">
-        <v>25811800180</v>
+        <v>30163479485</v>
       </c>
       <c r="P11" t="n">
-        <v>19270</v>
+        <v>9820</v>
       </c>
       <c r="Q11" t="n">
-        <v>2135</v>
+        <v>4000</v>
       </c>
       <c r="R11" t="n">
-        <v>-363000</v>
+        <v>-63000</v>
       </c>
       <c r="S11" t="n">
-        <v>-2000</v>
+        <v>0</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>서울반도체 대비 높은 영업이익과 세계 최고 기술력 보유. 내년 매출 조단위 및 광통신 사업 가세 전망.</t>
+          <t>미국 시장 급등에 따른 주가 상승 기대감. 594억 규모 공급 계약 사실 확인.</t>
         </is>
       </c>
       <c r="U11" t="inlineStr"/>
       <c r="V11" t="n">
-        <v>0.3</v>
+        <v>0</v>
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>['영업이익', '광통신', '기술력']</t>
+          <t>['공급 계약', '유통 물량', '주포']</t>
         </is>
       </c>
       <c r="X11" t="n">
@@ -1471,12 +1471,12 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>활성</t>
+          <t>추적</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>092190</t>
+          <t>030960</t>
         </is>
       </c>
     </row>
@@ -1487,24 +1487,24 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>15790</v>
+        <v>15750</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>'+0.45%</t>
+          <t>'+0.19%</t>
         </is>
       </c>
       <c r="D12" t="n">
         <v>0.06</v>
       </c>
       <c r="E12" t="n">
-        <v>92</v>
+        <v>99</v>
       </c>
       <c r="F12" t="n">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="G12" t="n">
-        <v>228</v>
+        <v>236</v>
       </c>
       <c r="H12" t="n">
         <v>28.13</v>
@@ -1530,7 +1530,7 @@
         <v>28.07</v>
       </c>
       <c r="O12" t="n">
-        <v>37007991950</v>
+        <v>38022077525</v>
       </c>
       <c r="P12" t="n">
         <v>35350</v>
@@ -1546,16 +1546,16 @@
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>미국 조선주 강세와 대비되는 국내 시장 상황. 자체 호재 및 증권사 리포트 기대.</t>
+          <t>미국 조선주 상승 속 국내 조선주 기회 모색. 자체 호재 및 증권사 리포트 쏟아지나, 신용 물량 및 야간 선물 하락세 부담.</t>
         </is>
       </c>
       <c r="U12" t="inlineStr"/>
       <c r="V12" t="n">
-        <v>0.2</v>
+        <v>0.3</v>
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>['조선주', '호재', '리포트']</t>
+          <t>['조선주', '자체 호재', '증권사 리포트']</t>
         </is>
       </c>
       <c r="X12" t="n">
@@ -1575,31 +1575,31 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>빛과전자</t>
+          <t>서울바이오시스</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>4040</v>
+        <v>8570</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>'+0.00%</t>
+          <t>'-0.12%</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>-0.77</v>
+        <v>0.01</v>
       </c>
       <c r="E13" t="n">
-        <v>64</v>
+        <v>81</v>
       </c>
       <c r="F13" t="n">
-        <v>43</v>
+        <v>50</v>
       </c>
       <c r="G13" t="n">
-        <v>142</v>
+        <v>236</v>
       </c>
       <c r="H13" t="n">
-        <v>1.43</v>
+        <v>2.67</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
@@ -1607,60 +1607,60 @@
         </is>
       </c>
       <c r="J13" t="n">
-        <v>4040</v>
+        <v>8580</v>
       </c>
       <c r="K13" t="n">
-        <v>3925</v>
+        <v>11090</v>
       </c>
       <c r="L13" t="n">
-        <v>4265</v>
+        <v>11150</v>
       </c>
       <c r="M13" t="n">
-        <v>3880</v>
+        <v>8400</v>
       </c>
       <c r="N13" t="n">
-        <v>2.2</v>
+        <v>2.66</v>
       </c>
       <c r="O13" t="n">
-        <v>70846932777</v>
+        <v>26199052920</v>
       </c>
       <c r="P13" t="n">
-        <v>8100</v>
+        <v>19270</v>
       </c>
       <c r="Q13" t="n">
-        <v>592</v>
+        <v>2135</v>
       </c>
       <c r="R13" t="n">
-        <v>-37000</v>
+        <v>-363000</v>
       </c>
       <c r="S13" t="n">
-        <v>0</v>
+        <v>-2000</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>상승 기대감과 함께 급등 가능성 언급. 외국인 및 프로그램 매수세 확인되나, '개잡주'라는 부정적 표현도 혼재.</t>
+          <t>서울반도체와의 시너지 및 제2의 한미반도체 기대감. 환기 사유로 인한 기관 투자 제한 및 역대급 신기술 대비 주가 부진 우려.</t>
         </is>
       </c>
       <c r="U13" t="inlineStr"/>
       <c r="V13" t="n">
-        <v>0</v>
+        <v>0.4</v>
       </c>
       <c r="W13" t="inlineStr">
         <is>
-          <t>['급등 기대', '외국인 매수', '개잡주']</t>
+          <t>['서울반도체', '신기술', '환기']</t>
         </is>
       </c>
       <c r="X13" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>추적</t>
+          <t>활성</t>
         </is>
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>069540</t>
+          <t>092190</t>
         </is>
       </c>
     </row>
@@ -1671,24 +1671,24 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>7310</v>
+        <v>7290</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>'-1.88%</t>
+          <t>'-2.15%</t>
         </is>
       </c>
       <c r="D14" t="n">
         <v>-0.02</v>
       </c>
       <c r="E14" t="n">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="F14" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="G14" t="n">
-        <v>169</v>
+        <v>179</v>
       </c>
       <c r="H14" t="n">
         <v>25.3</v>
@@ -1714,7 +1714,7 @@
         <v>25.32</v>
       </c>
       <c r="O14" t="n">
-        <v>7462337155</v>
+        <v>7636510555</v>
       </c>
       <c r="P14" t="n">
         <v>17950</v>
@@ -1759,70 +1759,70 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>삼성E&amp;A</t>
+          <t>빛과전자</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>61600</v>
+        <v>3940</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>'-1.91%</t>
+          <t>'-2.48%</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>0.21</v>
+        <v>-0.77</v>
       </c>
       <c r="E15" t="n">
-        <v>57</v>
+        <v>69</v>
       </c>
       <c r="F15" t="n">
-        <v>31</v>
+        <v>44</v>
       </c>
       <c r="G15" t="n">
-        <v>247</v>
+        <v>157</v>
       </c>
       <c r="H15" t="n">
-        <v>41.76</v>
+        <v>1.43</v>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J15" t="n">
-        <v>62800</v>
+        <v>4040</v>
       </c>
       <c r="K15" t="n">
-        <v>62300</v>
+        <v>3925</v>
       </c>
       <c r="L15" t="n">
-        <v>62800</v>
+        <v>4265</v>
       </c>
       <c r="M15" t="n">
-        <v>60700</v>
+        <v>3880</v>
       </c>
       <c r="N15" t="n">
-        <v>41.55</v>
+        <v>2.2</v>
       </c>
       <c r="O15" t="n">
-        <v>65337053800</v>
+        <v>72708128641</v>
       </c>
       <c r="P15" t="n">
-        <v>67300</v>
+        <v>8100</v>
       </c>
       <c r="Q15" t="n">
-        <v>23150</v>
+        <v>592</v>
       </c>
       <c r="R15" t="n">
-        <v>117000</v>
+        <v>-37000</v>
       </c>
       <c r="S15" t="n">
-        <v>-38000</v>
+        <v>0</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
-          <t>자사주 취득 및 중동 대규모 수주 공시 기대감. 외인/프매의 매수세와 함께 긍정적 전망이 일부 나타남.</t>
+          <t>상승 기대감과 함께 급등 가능성 언급. 외국인 및 프로그램 매수세 확인되나, '개잡주'라는 부정적 표현도 혼재.</t>
         </is>
       </c>
       <c r="U15" t="inlineStr"/>
@@ -1831,11 +1831,11 @@
       </c>
       <c r="W15" t="inlineStr">
         <is>
-          <t>['자사주 취득', '수주 공시', '외인 매수']</t>
+          <t>['급등 기대', '외국인 매수', '개잡주']</t>
         </is>
       </c>
       <c r="X15" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="Y15" t="inlineStr">
         <is>
@@ -1844,77 +1844,77 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>028050</t>
+          <t>069540</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>양지사</t>
+          <t>삼성E&amp;A</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>6510</v>
+        <v>61200</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>'-1.96%</t>
+          <t>'-2.55%</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>-0.05</v>
+        <v>0.21</v>
       </c>
       <c r="E16" t="n">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="F16" t="n">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="G16" t="n">
-        <v>65</v>
+        <v>262</v>
       </c>
       <c r="H16" t="n">
-        <v>0.85</v>
+        <v>41.76</v>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J16" t="n">
-        <v>6640</v>
+        <v>62800</v>
       </c>
       <c r="K16" t="n">
-        <v>7210</v>
+        <v>62300</v>
       </c>
       <c r="L16" t="n">
-        <v>7500</v>
+        <v>62800</v>
       </c>
       <c r="M16" t="n">
-        <v>6490</v>
+        <v>60700</v>
       </c>
       <c r="N16" t="n">
-        <v>0.9</v>
+        <v>41.55</v>
       </c>
       <c r="O16" t="n">
-        <v>29971885545</v>
+        <v>67219039150</v>
       </c>
       <c r="P16" t="n">
-        <v>9820</v>
+        <v>67300</v>
       </c>
       <c r="Q16" t="n">
-        <v>4000</v>
+        <v>23150</v>
       </c>
       <c r="R16" t="n">
-        <v>-63000</v>
+        <v>117000</v>
       </c>
       <c r="S16" t="n">
-        <v>0</v>
+        <v>-38000</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
-          <t>미국 시장 급등에 따른 주가 상승 기대감. 594억 규모 공급 계약 사실 확인.</t>
+          <t>자사주 취득 및 중동 대규모 수주 공시 기대감. 외인/프매의 매수세와 함께 긍정적 전망이 일부 나타남.</t>
         </is>
       </c>
       <c r="U16" t="inlineStr"/>
@@ -1923,11 +1923,11 @@
       </c>
       <c r="W16" t="inlineStr">
         <is>
-          <t>['공급 계약', '유통 물량', '주포']</t>
+          <t>['자사주 취득', '수주 공시', '외인 매수']</t>
         </is>
       </c>
       <c r="X16" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="Y16" t="inlineStr">
         <is>
@@ -1936,7 +1936,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>030960</t>
+          <t>028050</t>
         </is>
       </c>
     </row>
@@ -1947,24 +1947,24 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>54200</v>
+        <v>53900</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>'-4.41%</t>
+          <t>'-4.94%</t>
         </is>
       </c>
       <c r="D17" t="n">
         <v>-0.2</v>
       </c>
       <c r="E17" t="n">
-        <v>252</v>
+        <v>258</v>
       </c>
       <c r="F17" t="n">
-        <v>172</v>
+        <v>177</v>
       </c>
       <c r="G17" t="n">
-        <v>850</v>
+        <v>893</v>
       </c>
       <c r="H17" t="n">
         <v>22.14</v>
@@ -1984,13 +1984,13 @@
         <v>55900</v>
       </c>
       <c r="M17" t="n">
-        <v>54000</v>
+        <v>53800</v>
       </c>
       <c r="N17" t="n">
         <v>22.34</v>
       </c>
       <c r="O17" t="n">
-        <v>59762286500</v>
+        <v>65029627250</v>
       </c>
       <c r="P17" t="n">
         <v>139200</v>
@@ -2006,16 +2006,16 @@
       </c>
       <c r="T17" t="inlineStr">
         <is>
-          <t>미국 뉴스케일파워 SMR 원자로 수주 및 실적 호조. 체코 원전 사업 무산에 대한 아쉬움.</t>
+          <t>미국 뉴스케일파워 SMR 원자로 수주 및 실적 개선 뉴스. 체코 원전 관련 부정적 언급 및 무정부 금융 시장 상황 우려.</t>
         </is>
       </c>
       <c r="U17" t="inlineStr"/>
       <c r="V17" t="n">
-        <v>0.4</v>
+        <v>0.6</v>
       </c>
       <c r="W17" t="inlineStr">
         <is>
-          <t>['SMR', '수주', '실적']</t>
+          <t>['SMR', '뉴스케일파워', '수주']</t>
         </is>
       </c>
       <c r="X17" t="n">
@@ -2039,24 +2039,24 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>10990</v>
+        <v>10960</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>'-5.42%</t>
+          <t>'-5.68%</t>
         </is>
       </c>
       <c r="D18" t="n">
         <v>0.13</v>
       </c>
       <c r="E18" t="n">
-        <v>328</v>
+        <v>344</v>
       </c>
       <c r="F18" t="n">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="G18" t="n">
-        <v>1029</v>
+        <v>1073</v>
       </c>
       <c r="H18" t="n">
         <v>9.73</v>
@@ -2082,7 +2082,7 @@
         <v>9.6</v>
       </c>
       <c r="O18" t="n">
-        <v>43086272630</v>
+        <v>43936785635</v>
       </c>
       <c r="P18" t="n">
         <v>40350</v>
@@ -2131,11 +2131,11 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>219000</v>
+        <v>217750</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>'-5.60%</t>
+          <t>'-6.14%</t>
         </is>
       </c>
       <c r="D19" t="n">
@@ -2145,10 +2145,10 @@
         <v>800</v>
       </c>
       <c r="F19" t="n">
-        <v>551</v>
+        <v>556</v>
       </c>
       <c r="G19" t="n">
-        <v>1291</v>
+        <v>1317</v>
       </c>
       <c r="H19" t="n">
         <v>46.17</v>
@@ -2174,7 +2174,7 @@
         <v>46.19</v>
       </c>
       <c r="O19" t="n">
-        <v>1969988017250</v>
+        <v>2020025851000</v>
       </c>
       <c r="P19" t="n">
         <v>374500</v>
@@ -2190,7 +2190,7 @@
       </c>
       <c r="T19" t="inlineStr">
         <is>
-          <t>현 정부 및 경영진에 대한 비판과 함께 주주환원 발표 기대. 기관 연기금의 매도 물량 출회.</t>
+          <t>이재용 상속세 및 정치적 요인으로 인한 주가 하락 우려. 증여세 납부 시기까지 가격 누르기 전망.</t>
         </is>
       </c>
       <c r="U19" t="inlineStr"/>
@@ -2199,7 +2199,7 @@
       </c>
       <c r="W19" t="inlineStr">
         <is>
-          <t>['주주환원', '연기금', '매도']</t>
+          <t>['상속세', '주가 누르기', '증여세']</t>
         </is>
       </c>
       <c r="X19" t="n">
@@ -2219,31 +2219,31 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>삼성전자우</t>
+          <t>한화솔루션</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>170300</v>
+        <v>21850</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>'-7.40%</t>
+          <t>'-7.42%</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>-0.13</v>
+        <v>-0.63</v>
       </c>
       <c r="E20" t="n">
-        <v>51</v>
+        <v>209</v>
       </c>
       <c r="F20" t="n">
-        <v>43</v>
+        <v>157</v>
       </c>
       <c r="G20" t="n">
-        <v>161</v>
+        <v>499</v>
       </c>
       <c r="H20" t="n">
-        <v>74.87</v>
+        <v>11.6</v>
       </c>
       <c r="I20" t="inlineStr">
         <is>
@@ -2251,91 +2251,91 @@
         </is>
       </c>
       <c r="J20" t="n">
-        <v>183900</v>
+        <v>23600</v>
       </c>
       <c r="K20" t="n">
-        <v>176800</v>
+        <v>22650</v>
       </c>
       <c r="L20" t="n">
-        <v>179000</v>
+        <v>22700</v>
       </c>
       <c r="M20" t="n">
-        <v>168100</v>
+        <v>21100</v>
       </c>
       <c r="N20" t="n">
-        <v>75</v>
+        <v>12.23</v>
       </c>
       <c r="O20" t="n">
-        <v>457593359350</v>
+        <v>69577057550</v>
       </c>
       <c r="P20" t="n">
-        <v>243500</v>
+        <v>59300</v>
       </c>
       <c r="Q20" t="n">
-        <v>71000</v>
+        <v>21100</v>
       </c>
       <c r="R20" t="n">
-        <v>-416000</v>
+        <v>-580000</v>
       </c>
       <c r="S20" t="n">
-        <v>-18000</v>
+        <v>-192000</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
-          <t>주가 조작 및 증여세 관련 부정적 언급과 함께 시장 대폭락에 대한 우려가 존재. 우선주 소각 및 반등 기대도 일부.</t>
+          <t>김동원 부회장 주가 누르기 의혹 제기. RE100 승인, 카터스빌 모듈 완판 등 호재에도 불구하고 급락세 지속. 유증가 하회 및 적자 지속 우려.</t>
         </is>
       </c>
       <c r="U20" t="inlineStr"/>
       <c r="V20" t="n">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="W20" t="inlineStr">
         <is>
-          <t>['주가 조작', '증여세', '우선주 소각']</t>
+          <t>['주가 누르기', 'RE100', '카터스빌']</t>
         </is>
       </c>
       <c r="X20" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>추적</t>
+          <t>활성</t>
         </is>
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>005935</t>
+          <t>009830</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>한화솔루션</t>
+          <t>삼성전자우</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>21850</v>
+        <v>170150</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>'-7.42%</t>
+          <t>'-7.48%</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>-0.63</v>
+        <v>-0.13</v>
       </c>
       <c r="E21" t="n">
-        <v>205</v>
+        <v>56</v>
       </c>
       <c r="F21" t="n">
-        <v>151</v>
+        <v>47</v>
       </c>
       <c r="G21" t="n">
-        <v>471</v>
+        <v>170</v>
       </c>
       <c r="H21" t="n">
-        <v>11.6</v>
+        <v>74.87</v>
       </c>
       <c r="I21" t="inlineStr">
         <is>
@@ -2343,60 +2343,60 @@
         </is>
       </c>
       <c r="J21" t="n">
-        <v>23600</v>
+        <v>183900</v>
       </c>
       <c r="K21" t="n">
-        <v>22650</v>
+        <v>176800</v>
       </c>
       <c r="L21" t="n">
-        <v>22700</v>
+        <v>179000</v>
       </c>
       <c r="M21" t="n">
-        <v>21100</v>
+        <v>168100</v>
       </c>
       <c r="N21" t="n">
-        <v>12.23</v>
+        <v>75</v>
       </c>
       <c r="O21" t="n">
-        <v>67964864050</v>
+        <v>472213270250</v>
       </c>
       <c r="P21" t="n">
-        <v>59300</v>
+        <v>243500</v>
       </c>
       <c r="Q21" t="n">
-        <v>21100</v>
+        <v>71000</v>
       </c>
       <c r="R21" t="n">
-        <v>-580000</v>
+        <v>-416000</v>
       </c>
       <c r="S21" t="n">
-        <v>-192000</v>
+        <v>-18000</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
-          <t>태양광 물량 완판 뉴스가 있으나, 주가 누르기 의혹과 급락으로 인한 부정적 여론이 지배적.</t>
+          <t>주가 조작 및 증여세 관련 부정적 언급과 함께 시장 대폭락에 대한 우려가 존재. 우선주 소각 및 반등 기대도 일부.</t>
         </is>
       </c>
       <c r="U21" t="inlineStr"/>
       <c r="V21" t="n">
-        <v>0.2</v>
+        <v>0</v>
       </c>
       <c r="W21" t="inlineStr">
         <is>
-          <t>['태양광', '주가 누르기', '급락']</t>
+          <t>['주가 조작', '증여세', '우선주 소각']</t>
         </is>
       </c>
       <c r="X21" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>활성</t>
+          <t>추적</t>
         </is>
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>009830</t>
+          <t>005935</t>
         </is>
       </c>
     </row>
@@ -2407,24 +2407,24 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>13840</v>
+        <v>13790</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>'-7.92%</t>
+          <t>'-8.25%</t>
         </is>
       </c>
       <c r="D22" t="n">
         <v>-0.2</v>
       </c>
       <c r="E22" t="n">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="F22" t="n">
         <v>56</v>
       </c>
       <c r="G22" t="n">
-        <v>371</v>
+        <v>376</v>
       </c>
       <c r="H22" t="n">
         <v>3.13</v>
@@ -2450,7 +2450,7 @@
         <v>3.33</v>
       </c>
       <c r="O22" t="n">
-        <v>37289303285</v>
+        <v>37934397200</v>
       </c>
       <c r="P22" t="n">
         <v>31500</v>
@@ -2499,11 +2499,11 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>1403000</v>
+        <v>1394000</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>'-8.06%</t>
+          <t>'-8.65%</t>
         </is>
       </c>
       <c r="D23" t="n">
@@ -2513,10 +2513,10 @@
         <v>800</v>
       </c>
       <c r="F23" t="n">
-        <v>528</v>
+        <v>526</v>
       </c>
       <c r="G23" t="n">
-        <v>1346</v>
+        <v>1342</v>
       </c>
       <c r="H23" t="n">
         <v>48.72</v>
@@ -2542,7 +2542,7 @@
         <v>48.66</v>
       </c>
       <c r="O23" t="n">
-        <v>2441374946000</v>
+        <v>2502364288000</v>
       </c>
       <c r="P23" t="n">
         <v>2987000</v>
@@ -2558,7 +2558,7 @@
       </c>
       <c r="T23" t="inlineStr">
         <is>
-          <t>코스피 시장 전반의 급락 속 SK하이닉스 하락세. 개미 투자자들의 대규모 매수세 유입.</t>
+          <t>정치적 요인 및 전반적인 시장 하락 속 SK하이닉스 급락. 엔비디아 회복세에도 불구하고 대하락 우려 및 개미 투자자 대량 매수.</t>
         </is>
       </c>
       <c r="U23" t="inlineStr"/>
@@ -2567,7 +2567,7 @@
       </c>
       <c r="W23" t="inlineStr">
         <is>
-          <t>['코스피', '하락세', '개미']</t>
+          <t>['정치적 요인', '시장 하락', '엔비디아']</t>
         </is>
       </c>
       <c r="X23" t="n">
@@ -2591,11 +2591,11 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>7230</v>
+        <v>7140</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>'-8.48%</t>
+          <t>'-9.62%</t>
         </is>
       </c>
       <c r="D24" t="n">
@@ -2608,7 +2608,7 @@
         <v>30</v>
       </c>
       <c r="G24" t="n">
-        <v>110</v>
+        <v>123</v>
       </c>
       <c r="H24" t="n">
         <v>0.39</v>
@@ -2634,7 +2634,7 @@
         <v>0.42</v>
       </c>
       <c r="O24" t="n">
-        <v>14443691290</v>
+        <v>14633825560</v>
       </c>
       <c r="P24" t="n">
         <v>10300</v>
@@ -2683,24 +2683,24 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>117100</v>
+        <v>116200</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>'-15.27%</t>
+          <t>'-15.92%</t>
         </is>
       </c>
       <c r="D25" t="n">
         <v>-0.26</v>
       </c>
       <c r="E25" t="n">
-        <v>125</v>
+        <v>133</v>
       </c>
       <c r="F25" t="n">
-        <v>78</v>
+        <v>86</v>
       </c>
       <c r="G25" t="n">
-        <v>318</v>
+        <v>331</v>
       </c>
       <c r="H25" t="n">
         <v>14.2</v>
@@ -2720,13 +2720,13 @@
         <v>132900</v>
       </c>
       <c r="M25" t="n">
-        <v>116400</v>
+        <v>116100</v>
       </c>
       <c r="N25" t="n">
         <v>14.46</v>
       </c>
       <c r="O25" t="n">
-        <v>120516425800</v>
+        <v>124212185850</v>
       </c>
       <c r="P25" t="n">
         <v>198000</v>
@@ -2742,16 +2742,16 @@
       </c>
       <c r="T25" t="inlineStr">
         <is>
-          <t>급격한 주가 하락에도 불구하고 예상되는 호실적. 기관 및 외국인 매매 동향 주시.</t>
+          <t>대덕전자, 큰 폭의 하락에도 불구하고 실적 개선에 대한 기대감 존재. SK하이닉스 소부장 물량 확대 영향 분석.</t>
         </is>
       </c>
       <c r="U25" t="inlineStr"/>
       <c r="V25" t="n">
-        <v>0.2</v>
+        <v>0.4</v>
       </c>
       <c r="W25" t="inlineStr">
         <is>
-          <t>['실적', '주가 하락', '기관']</t>
+          <t>['실적', '기판주', '기관']</t>
         </is>
       </c>
       <c r="X25" t="n">
@@ -2775,24 +2775,24 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>13400</v>
+        <v>13250</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>'-21.18%</t>
+          <t>'-22.06%</t>
         </is>
       </c>
       <c r="D26" t="n">
         <v>0.01</v>
       </c>
       <c r="E26" t="n">
-        <v>162</v>
+        <v>168</v>
       </c>
       <c r="F26" t="n">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="G26" t="n">
-        <v>128</v>
+        <v>148</v>
       </c>
       <c r="H26" t="n">
         <v>0.66</v>
@@ -2818,7 +2818,7 @@
         <v>0.65</v>
       </c>
       <c r="O26" t="n">
-        <v>29850534500</v>
+        <v>30280262485</v>
       </c>
       <c r="P26" t="n">
         <v>28800</v>
@@ -2834,16 +2834,16 @@
       </c>
       <c r="T26" t="inlineStr">
         <is>
-          <t>보호예수 해제 후 물량 출회 가능성 언급. 마이크론 퀠테스트 통과 및 반도체 생산량 증가 기대.</t>
+          <t>마이크론 퀄테스트 통과 및 장비 수주 공시 기대. 보호예수 물량 출회로 인한 급락세 지속 및 저가 매수 기회 언급.</t>
         </is>
       </c>
       <c r="U26" t="inlineStr"/>
       <c r="V26" t="n">
-        <v>0.4</v>
+        <v>0.3</v>
       </c>
       <c r="W26" t="inlineStr">
         <is>
-          <t>['보호예수', '퀠테스트', '반도체']</t>
+          <t>['마이크론', '퀄테스트', '보호예수']</t>
         </is>
       </c>
       <c r="X26" t="n">
@@ -2867,24 +2867,24 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>1849</v>
+        <v>1824</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>'-28.19%</t>
+          <t>'-29.17%</t>
         </is>
       </c>
       <c r="D27" t="n">
         <v>1.45</v>
       </c>
       <c r="E27" t="n">
-        <v>58</v>
+        <v>65</v>
       </c>
       <c r="F27" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="G27" t="n">
-        <v>27</v>
+        <v>33</v>
       </c>
       <c r="H27" t="n">
         <v>4.8</v>
@@ -2904,13 +2904,13 @@
         <v>2005</v>
       </c>
       <c r="M27" t="n">
-        <v>1811</v>
+        <v>1805</v>
       </c>
       <c r="N27" t="n">
         <v>3.35</v>
       </c>
       <c r="O27" t="n">
-        <v>6573429750</v>
+        <v>6979341030</v>
       </c>
       <c r="P27" t="n">
         <v>5700</v>
@@ -2959,24 +2959,24 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>10210</v>
+        <v>10380</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>'-31.93%</t>
+          <t>'-30.80%</t>
         </is>
       </c>
       <c r="D28" t="n">
         <v>0</v>
       </c>
       <c r="E28" t="n">
-        <v>325</v>
+        <v>327</v>
       </c>
       <c r="F28" t="n">
-        <v>155</v>
+        <v>161</v>
       </c>
       <c r="G28" t="n">
-        <v>570</v>
+        <v>590</v>
       </c>
       <c r="H28" t="n">
         <v>3.05</v>
@@ -3002,7 +3002,7 @@
         <v>0</v>
       </c>
       <c r="O28" t="n">
-        <v>97368732195</v>
+        <v>99804775760</v>
       </c>
       <c r="P28" t="n">
         <v>12700</v>
@@ -3018,7 +3018,7 @@
       </c>
       <c r="T28" t="inlineStr">
         <is>
-          <t>상장 초기 급락 후 회복 기대감. 양호한 매출 및 영업이익, 유통물량 희소성 부각.</t>
+          <t>상장 직후 급락 후 반등 시도. 높은 당기순이익 및 매출, 영업이익 수치 제시. 기관 물량 소화 후 상승 기대.</t>
         </is>
       </c>
       <c r="U28" t="inlineStr"/>
@@ -3027,7 +3027,7 @@
       </c>
       <c r="W28" t="inlineStr">
         <is>
-          <t>['상장', '실적', '유통물량']</t>
+          <t>['상장', '반등', '기관 물량']</t>
         </is>
       </c>
       <c r="X28" t="n">
